--- a/Trials/nse500_Nifty_500_2025_Apr_nse500_nse500_nse500_nse500_nse500_returns.xlsx
+++ b/Trials/nse500_Nifty_500_2025_Apr_nse500_nse500_nse500_nse500_nse500_returns.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C699"/>
+  <dimension ref="A1:C732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,10 +454,10 @@
         <v>45019</v>
       </c>
       <c r="B2" t="n">
-        <v>14601.95</v>
+        <v>23226.81</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003029293473967742</v>
+        <v>0.002884282001605509</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         <v>45021</v>
       </c>
       <c r="B3" t="n">
-        <v>14709.4</v>
+        <v>23397.11</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007358606213553553</v>
+        <v>0.007332044305696783</v>
       </c>
     </row>
     <row r="4">
@@ -476,10 +476,10 @@
         <v>45022</v>
       </c>
       <c r="B4" t="n">
-        <v>14759.2</v>
+        <v>23475.05</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003385590166832264</v>
+        <v>0.003331180645814724</v>
       </c>
     </row>
     <row r="5">
@@ -487,10 +487,10 @@
         <v>45026</v>
       </c>
       <c r="B5" t="n">
-        <v>14790.55</v>
+        <v>23526.36</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002124098867147151</v>
+        <v>0.002185724844036674</v>
       </c>
     </row>
     <row r="6">
@@ -498,10 +498,10 @@
         <v>45027</v>
       </c>
       <c r="B6" t="n">
-        <v>14867.25</v>
+        <v>23652.45</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00518574359979862</v>
+        <v>0.005359520129760931</v>
       </c>
     </row>
     <row r="7">
@@ -509,10 +509,10 @@
         <v>45028</v>
       </c>
       <c r="B7" t="n">
-        <v>14941.55</v>
+        <v>23768.47</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004997561754863877</v>
+        <v>0.004905200095550288</v>
       </c>
     </row>
     <row r="8">
@@ -520,10 +520,10 @@
         <v>45029</v>
       </c>
       <c r="B8" t="n">
-        <v>14954.25</v>
+        <v>23789.46</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0008499787505313883</v>
+        <v>0.0008831026986590995</v>
       </c>
     </row>
     <row r="9">
@@ -531,10 +531,10 @@
         <v>45033</v>
       </c>
       <c r="B9" t="n">
-        <v>14904.3</v>
+        <v>23706</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.003340187572094977</v>
+        <v>-0.003508276354318274</v>
       </c>
     </row>
     <row r="10">
@@ -542,10 +542,10 @@
         <v>45034</v>
       </c>
       <c r="B10" t="n">
-        <v>14897</v>
+        <v>23693.71</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.000489791536670614</v>
+        <v>-0.0005184341516916158</v>
       </c>
     </row>
     <row r="11">
@@ -553,10 +553,10 @@
         <v>45035</v>
       </c>
       <c r="B11" t="n">
-        <v>14856.9</v>
+        <v>23629.61</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.002691817144391484</v>
+        <v>-0.00270535935486671</v>
       </c>
     </row>
     <row r="12">
@@ -564,10 +564,10 @@
         <v>45036</v>
       </c>
       <c r="B12" t="n">
-        <v>14861.75</v>
+        <v>23638.12</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0003264476438558095</v>
+        <v>0.0003601413650076157</v>
       </c>
     </row>
     <row r="13">
@@ -575,10 +575,10 @@
         <v>45037</v>
       </c>
       <c r="B13" t="n">
-        <v>14847.1</v>
+        <v>23611.55</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0009857520143993215</v>
+        <v>-0.001124031860401775</v>
       </c>
     </row>
     <row r="14">
@@ -586,10 +586,10 @@
         <v>45040</v>
       </c>
       <c r="B14" t="n">
-        <v>14930.15</v>
+        <v>23745.87</v>
       </c>
       <c r="C14" t="n">
-        <v>0.005593684962046375</v>
+        <v>0.005688741315161394</v>
       </c>
     </row>
     <row r="15">
@@ -597,10 +597,10 @@
         <v>45041</v>
       </c>
       <c r="B15" t="n">
-        <v>14955.7</v>
+        <v>23787.08</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001711302297699779</v>
+        <v>0.001735459682041585</v>
       </c>
     </row>
     <row r="16">
@@ -608,10 +608,10 @@
         <v>45042</v>
       </c>
       <c r="B16" t="n">
-        <v>14994.4</v>
+        <v>23851.41</v>
       </c>
       <c r="C16" t="n">
-        <v>0.002587642169874949</v>
+        <v>0.00270440928436777</v>
       </c>
     </row>
     <row r="17">
@@ -619,10 +619,10 @@
         <v>45043</v>
       </c>
       <c r="B17" t="n">
-        <v>15075.05</v>
+        <v>23983.88</v>
       </c>
       <c r="C17" t="n">
-        <v>0.005378674705223352</v>
+        <v>0.005553969346047127</v>
       </c>
     </row>
     <row r="18">
@@ -630,10 +630,10 @@
         <v>45044</v>
       </c>
       <c r="B18" t="n">
-        <v>15219.55</v>
+        <v>24209.37</v>
       </c>
       <c r="C18" t="n">
-        <v>0.009585374509537337</v>
+        <v>0.009401731496321508</v>
       </c>
     </row>
     <row r="19">
@@ -641,10 +641,10 @@
         <v>45048</v>
       </c>
       <c r="B19" t="n">
-        <v>15300.75</v>
+        <v>24344.14</v>
       </c>
       <c r="C19" t="n">
-        <v>0.005335243157649217</v>
+        <v>0.005566852834253844</v>
       </c>
     </row>
     <row r="20">
@@ -652,10 +652,10 @@
         <v>45049</v>
       </c>
       <c r="B20" t="n">
-        <v>15276.4</v>
+        <v>24304.65</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0015914252569319</v>
+        <v>-0.001622156297162225</v>
       </c>
     </row>
     <row r="21">
@@ -663,10 +663,10 @@
         <v>45050</v>
       </c>
       <c r="B21" t="n">
-        <v>15405.5</v>
+        <v>24506.33</v>
       </c>
       <c r="C21" t="n">
-        <v>0.008450943939671607</v>
+        <v>0.008298000588364829</v>
       </c>
     </row>
     <row r="22">
@@ -674,10 +674,10 @@
         <v>45051</v>
       </c>
       <c r="B22" t="n">
-        <v>15278.6</v>
+        <v>24306.42</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.008237317841030767</v>
+        <v>-0.008157484209182053</v>
       </c>
     </row>
     <row r="23">
@@ -685,10 +685,10 @@
         <v>45054</v>
       </c>
       <c r="B23" t="n">
-        <v>15427.1</v>
+        <v>24543.58</v>
       </c>
       <c r="C23" t="n">
-        <v>0.009719476915424297</v>
+        <v>0.009757092982018989</v>
       </c>
     </row>
     <row r="24">
@@ -696,10 +696,10 @@
         <v>45055</v>
       </c>
       <c r="B24" t="n">
-        <v>15420.6</v>
+        <v>24528.82</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0004213364793124175</v>
+        <v>-0.0006013792608903223</v>
       </c>
     </row>
     <row r="25">
@@ -707,10 +707,10 @@
         <v>45056</v>
       </c>
       <c r="B25" t="n">
-        <v>15466.05</v>
+        <v>24603.76</v>
       </c>
       <c r="C25" t="n">
-        <v>0.002947356134002543</v>
+        <v>0.003055181619009639</v>
       </c>
     </row>
     <row r="26">
@@ -718,10 +718,10 @@
         <v>45057</v>
       </c>
       <c r="B26" t="n">
-        <v>15484.05</v>
+        <v>24631.35</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001163839506532094</v>
+        <v>0.001121373318549779</v>
       </c>
     </row>
     <row r="27">
@@ -729,10 +729,10 @@
         <v>45058</v>
       </c>
       <c r="B27" t="n">
-        <v>15477.35</v>
+        <v>24622.46</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0004327033302009564</v>
+        <v>-0.0003609221581439837</v>
       </c>
     </row>
     <row r="28">
@@ -740,10 +740,10 @@
         <v>45061</v>
       </c>
       <c r="B28" t="n">
-        <v>15549.7</v>
+        <v>24733.55</v>
       </c>
       <c r="C28" t="n">
-        <v>0.004674572843542446</v>
+        <v>0.004511734408340962</v>
       </c>
     </row>
     <row r="29">
@@ -751,10 +751,10 @@
         <v>45062</v>
       </c>
       <c r="B29" t="n">
-        <v>15492.4</v>
+        <v>24639.78</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.003684958552255146</v>
+        <v>-0.003791206680804016</v>
       </c>
     </row>
     <row r="30">
@@ -762,10 +762,10 @@
         <v>45063</v>
       </c>
       <c r="B30" t="n">
-        <v>15426.35</v>
+        <v>24536.52</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.004263380754434332</v>
+        <v>-0.004190784170962525</v>
       </c>
     </row>
     <row r="31">
@@ -773,10 +773,10 @@
         <v>45064</v>
       </c>
       <c r="B31" t="n">
-        <v>15361.6</v>
+        <v>24429.35</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.004197363601888937</v>
+        <v>-0.00436777505530539</v>
       </c>
     </row>
     <row r="32">
@@ -784,10 +784,10 @@
         <v>45065</v>
       </c>
       <c r="B32" t="n">
-        <v>15407.55</v>
+        <v>24504.07</v>
       </c>
       <c r="C32" t="n">
-        <v>0.002991224872409104</v>
+        <v>0.003058615968087652</v>
       </c>
     </row>
     <row r="33">
@@ -795,10 +795,10 @@
         <v>45068</v>
       </c>
       <c r="B33" t="n">
-        <v>15504</v>
+        <v>24655.58</v>
       </c>
       <c r="C33" t="n">
-        <v>0.006259918027200939</v>
+        <v>0.006183054488499318</v>
       </c>
     </row>
     <row r="34">
@@ -806,10 +806,10 @@
         <v>45069</v>
       </c>
       <c r="B34" t="n">
-        <v>15544.75</v>
+        <v>24716.45</v>
       </c>
       <c r="C34" t="n">
-        <v>0.002628353973168185</v>
+        <v>0.002468812333759729</v>
       </c>
     </row>
     <row r="35">
@@ -817,10 +817,10 @@
         <v>45070</v>
       </c>
       <c r="B35" t="n">
-        <v>15515.95</v>
+        <v>24673.29</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.001852715547049577</v>
+        <v>-0.001746205462354045</v>
       </c>
     </row>
     <row r="36">
@@ -828,10 +828,10 @@
         <v>45071</v>
       </c>
       <c r="B36" t="n">
-        <v>15555.25</v>
+        <v>24739.67</v>
       </c>
       <c r="C36" t="n">
-        <v>0.002532877458357286</v>
+        <v>0.002690358683418381</v>
       </c>
     </row>
     <row r="37">
@@ -839,10 +839,10 @@
         <v>45072</v>
       </c>
       <c r="B37" t="n">
-        <v>15696.75</v>
+        <v>24962.81</v>
       </c>
       <c r="C37" t="n">
-        <v>0.009096607254785338</v>
+        <v>0.009019522087400533</v>
       </c>
     </row>
     <row r="38">
@@ -850,10 +850,10 @@
         <v>45075</v>
       </c>
       <c r="B38" t="n">
-        <v>15772.35</v>
+        <v>25080.82</v>
       </c>
       <c r="C38" t="n">
-        <v>0.004816283625591389</v>
+        <v>0.004727432528629505</v>
       </c>
     </row>
     <row r="39">
@@ -861,10 +861,10 @@
         <v>45076</v>
       </c>
       <c r="B39" t="n">
-        <v>15799.45</v>
+        <v>25109.52</v>
       </c>
       <c r="C39" t="n">
-        <v>0.001718196717673592</v>
+        <v>0.001144300704681855</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         <v>45077</v>
       </c>
       <c r="B40" t="n">
-        <v>15766.4</v>
+        <v>25059.67</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.002091844969286938</v>
+        <v>-0.001985302785557086</v>
       </c>
     </row>
     <row r="41">
@@ -883,10 +883,10 @@
         <v>45078</v>
       </c>
       <c r="B41" t="n">
-        <v>15760.35</v>
+        <v>25042.42</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.0003837274203368768</v>
+        <v>-0.0006883570294421437</v>
       </c>
     </row>
     <row r="42">
@@ -894,10 +894,10 @@
         <v>45079</v>
       </c>
       <c r="B42" t="n">
-        <v>15811.2</v>
+        <v>25122.99</v>
       </c>
       <c r="C42" t="n">
-        <v>0.003226451189218604</v>
+        <v>0.003217340816103365</v>
       </c>
     </row>
     <row r="43">
@@ -905,10 +905,10 @@
         <v>45082</v>
       </c>
       <c r="B43" t="n">
-        <v>15859.5</v>
+        <v>25201.2</v>
       </c>
       <c r="C43" t="n">
-        <v>0.003054796599878618</v>
+        <v>0.003113084867684801</v>
       </c>
     </row>
     <row r="44">
@@ -916,10 +916,10 @@
         <v>45083</v>
       </c>
       <c r="B44" t="n">
-        <v>15878.4</v>
+        <v>25233.59</v>
       </c>
       <c r="C44" t="n">
-        <v>0.001191714745105488</v>
+        <v>0.001285256257638423</v>
       </c>
     </row>
     <row r="45">
@@ -927,10 +927,10 @@
         <v>45084</v>
       </c>
       <c r="B45" t="n">
-        <v>16006.7</v>
+        <v>25431.1</v>
       </c>
       <c r="C45" t="n">
-        <v>0.008080159209995941</v>
+        <v>0.007827265165202268</v>
       </c>
     </row>
     <row r="46">
@@ -938,10 +938,10 @@
         <v>45085</v>
       </c>
       <c r="B46" t="n">
-        <v>15921.05</v>
+        <v>25296.57</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.005350884317192217</v>
+        <v>-0.005289979591916905</v>
       </c>
     </row>
     <row r="47">
@@ -949,10 +949,10 @@
         <v>45086</v>
       </c>
       <c r="B47" t="n">
-        <v>15877.4</v>
+        <v>25224.55</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.002741653345727846</v>
+        <v>-0.002847026296450506</v>
       </c>
     </row>
     <row r="48">
@@ -960,10 +960,10 @@
         <v>45089</v>
       </c>
       <c r="B48" t="n">
-        <v>15929.1</v>
+        <v>25302.89</v>
       </c>
       <c r="C48" t="n">
-        <v>0.003256200637383966</v>
+        <v>0.003105704561627398</v>
       </c>
     </row>
     <row r="49">
@@ -971,10 +971,10 @@
         <v>45090</v>
       </c>
       <c r="B49" t="n">
-        <v>16048.2</v>
+        <v>25496.65</v>
       </c>
       <c r="C49" t="n">
-        <v>0.007476881933065949</v>
+        <v>0.007657623299156757</v>
       </c>
     </row>
     <row r="50">
@@ -982,10 +982,10 @@
         <v>45091</v>
       </c>
       <c r="B50" t="n">
-        <v>16084.05</v>
+        <v>25549.04</v>
       </c>
       <c r="C50" t="n">
-        <v>0.002233895390137075</v>
+        <v>0.002054779745574331</v>
       </c>
     </row>
     <row r="51">
@@ -993,10 +993,10 @@
         <v>45092</v>
       </c>
       <c r="B51" t="n">
-        <v>16058.25</v>
+        <v>25502.55</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.001604073600865452</v>
+        <v>-0.001819637841578459</v>
       </c>
     </row>
     <row r="52">
@@ -1004,10 +1004,10 @@
         <v>45093</v>
       </c>
       <c r="B52" t="n">
-        <v>16181.45</v>
+        <v>25698.79</v>
       </c>
       <c r="C52" t="n">
-        <v>0.007672068874254645</v>
+        <v>0.007694916782831518</v>
       </c>
     </row>
     <row r="53">
@@ -1015,10 +1015,10 @@
         <v>45096</v>
       </c>
       <c r="B53" t="n">
-        <v>16142.15</v>
+        <v>25631.66</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.002428706945298509</v>
+        <v>-0.002612185242962806</v>
       </c>
     </row>
     <row r="54">
@@ -1026,10 +1026,10 @@
         <v>45097</v>
       </c>
       <c r="B54" t="n">
-        <v>16199.95</v>
+        <v>25716.36</v>
       </c>
       <c r="C54" t="n">
-        <v>0.003580687826590712</v>
+        <v>0.003304507004228352</v>
       </c>
     </row>
     <row r="55">
@@ -1037,10 +1037,10 @@
         <v>45098</v>
       </c>
       <c r="B55" t="n">
-        <v>16240.95</v>
+        <v>25789.55</v>
       </c>
       <c r="C55" t="n">
-        <v>0.002530872008864149</v>
+        <v>0.002846048196556428</v>
       </c>
     </row>
     <row r="56">
@@ -1048,10 +1048,10 @@
         <v>45099</v>
       </c>
       <c r="B56" t="n">
-        <v>16140.8</v>
+        <v>25621.85</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.006166511195465851</v>
+        <v>-0.006502633818736725</v>
       </c>
     </row>
     <row r="57">
@@ -1059,10 +1059,10 @@
         <v>45100</v>
       </c>
       <c r="B57" t="n">
-        <v>16011.8</v>
+        <v>25419.56</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.007992168913560693</v>
+        <v>-0.00789521443611596</v>
       </c>
     </row>
     <row r="58">
@@ -1070,10 +1070,10 @@
         <v>45103</v>
       </c>
       <c r="B58" t="n">
-        <v>16066.15</v>
+        <v>25506.62</v>
       </c>
       <c r="C58" t="n">
-        <v>0.003394371650907502</v>
+        <v>0.003424921595810426</v>
       </c>
     </row>
     <row r="59">
@@ -1081,10 +1081,10 @@
         <v>45104</v>
       </c>
       <c r="B59" t="n">
-        <v>16163.5</v>
+        <v>25660.64</v>
       </c>
       <c r="C59" t="n">
-        <v>0.006059323484469026</v>
+        <v>0.006038432375595093</v>
       </c>
     </row>
     <row r="60">
@@ -1092,10 +1092,10 @@
         <v>45105</v>
       </c>
       <c r="B60" t="n">
-        <v>16277.2</v>
+        <v>25841.24</v>
       </c>
       <c r="C60" t="n">
-        <v>0.00703436755653164</v>
+        <v>0.007038016199128361</v>
       </c>
     </row>
     <row r="61">
@@ -1103,10 +1103,10 @@
         <v>45107</v>
       </c>
       <c r="B61" t="n">
-        <v>16430</v>
+        <v>26078.65</v>
       </c>
       <c r="C61" t="n">
-        <v>0.009387363920084546</v>
+        <v>0.00918725262410014</v>
       </c>
     </row>
     <row r="62">
@@ -1114,10 +1114,10 @@
         <v>45110</v>
       </c>
       <c r="B62" t="n">
-        <v>16527.95</v>
+        <v>26230.37</v>
       </c>
       <c r="C62" t="n">
-        <v>0.005961655508216701</v>
+        <v>0.005817785813299281</v>
       </c>
     </row>
     <row r="63">
@@ -1125,10 +1125,10 @@
         <v>45111</v>
       </c>
       <c r="B63" t="n">
-        <v>16556.05</v>
+        <v>26278.33</v>
       </c>
       <c r="C63" t="n">
-        <v>0.001700150351374496</v>
+        <v>0.001828414925142186</v>
       </c>
     </row>
     <row r="64">
@@ -1136,10 +1136,10 @@
         <v>45112</v>
       </c>
       <c r="B64" t="n">
-        <v>16597.2</v>
+        <v>26343.66</v>
       </c>
       <c r="C64" t="n">
-        <v>0.002485496238535223</v>
+        <v>0.002486078833776606</v>
       </c>
     </row>
     <row r="65">
@@ -1147,10 +1147,10 @@
         <v>45113</v>
       </c>
       <c r="B65" t="n">
-        <v>16695.05</v>
+        <v>26497.12</v>
       </c>
       <c r="C65" t="n">
-        <v>0.005895572747210309</v>
+        <v>0.005825310530123806</v>
       </c>
     </row>
     <row r="66">
@@ -1158,10 +1158,10 @@
         <v>45114</v>
       </c>
       <c r="B66" t="n">
-        <v>16564.9</v>
+        <v>26294.33</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.007795723882228489</v>
+        <v>-0.007653284583380993</v>
       </c>
     </row>
     <row r="67">
@@ -1169,10 +1169,10 @@
         <v>45117</v>
       </c>
       <c r="B67" t="n">
-        <v>16553.75</v>
+        <v>26276.81</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.0006731100097194798</v>
+        <v>-0.0006663033437246391</v>
       </c>
     </row>
     <row r="68">
@@ -1180,10 +1180,10 @@
         <v>45118</v>
       </c>
       <c r="B68" t="n">
-        <v>16648</v>
+        <v>26422.79</v>
       </c>
       <c r="C68" t="n">
-        <v>0.005693573963603482</v>
+        <v>0.005555468871601965</v>
       </c>
     </row>
     <row r="69">
@@ -1191,10 +1191,10 @@
         <v>45119</v>
       </c>
       <c r="B69" t="n">
-        <v>16641.05</v>
+        <v>26408</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.0004174675636713365</v>
+        <v>-0.0005597440694189437</v>
       </c>
     </row>
     <row r="70">
@@ -1202,10 +1202,10 @@
         <v>45120</v>
       </c>
       <c r="B70" t="n">
-        <v>16623.9</v>
+        <v>26391.97</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.001030584007619573</v>
+        <v>-0.000607013026355574</v>
       </c>
     </row>
     <row r="71">
@@ -1213,10 +1213,10 @@
         <v>45121</v>
       </c>
       <c r="B71" t="n">
-        <v>16765.45</v>
+        <v>26612.59</v>
       </c>
       <c r="C71" t="n">
-        <v>0.008514849102797761</v>
+        <v>0.008359360820734407</v>
       </c>
     </row>
     <row r="72">
@@ -1224,10 +1224,10 @@
         <v>45124</v>
       </c>
       <c r="B72" t="n">
-        <v>16872.05</v>
+        <v>26780.18</v>
       </c>
       <c r="C72" t="n">
-        <v>0.006358314271313725</v>
+        <v>0.006297395330556066</v>
       </c>
     </row>
     <row r="73">
@@ -1235,10 +1235,10 @@
         <v>45125</v>
       </c>
       <c r="B73" t="n">
-        <v>16872</v>
+        <v>26786.23</v>
       </c>
       <c r="C73" t="n">
-        <v>-2.963481023354753e-06</v>
+        <v>0.0002259133433755167</v>
       </c>
     </row>
     <row r="74">
@@ -1246,10 +1246,10 @@
         <v>45126</v>
       </c>
       <c r="B74" t="n">
-        <v>16953.5</v>
+        <v>26910.77</v>
       </c>
       <c r="C74" t="n">
-        <v>0.004830488383120057</v>
+        <v>0.004649403816811892</v>
       </c>
     </row>
     <row r="75">
@@ -1257,10 +1257,10 @@
         <v>45127</v>
       </c>
       <c r="B75" t="n">
-        <v>17042.55</v>
+        <v>27045.09</v>
       </c>
       <c r="C75" t="n">
-        <v>0.005252602707405574</v>
+        <v>0.004991310170612051</v>
       </c>
     </row>
     <row r="76">
@@ -1268,10 +1268,10 @@
         <v>45128</v>
       </c>
       <c r="B76" t="n">
-        <v>16904.3</v>
+        <v>26816.71</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.008112048959809437</v>
+        <v>-0.008444416343225347</v>
       </c>
     </row>
     <row r="77">
@@ -1279,10 +1279,10 @@
         <v>45131</v>
       </c>
       <c r="B77" t="n">
-        <v>16865.15</v>
+        <v>26758.33</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.002315978774631189</v>
+        <v>-0.002177000832689679</v>
       </c>
     </row>
     <row r="78">
@@ -1290,10 +1290,10 @@
         <v>45132</v>
       </c>
       <c r="B78" t="n">
-        <v>16896.9</v>
+        <v>26808.31</v>
       </c>
       <c r="C78" t="n">
-        <v>0.001882580350604623</v>
+        <v>0.001867829569334178</v>
       </c>
     </row>
     <row r="79">
@@ -1301,10 +1301,10 @@
         <v>45133</v>
       </c>
       <c r="B79" t="n">
-        <v>16975</v>
+        <v>26934.87</v>
       </c>
       <c r="C79" t="n">
-        <v>0.004622149625079119</v>
+        <v>0.004720924220885214</v>
       </c>
     </row>
     <row r="80">
@@ -1312,10 +1312,10 @@
         <v>45134</v>
       </c>
       <c r="B80" t="n">
-        <v>16919.2</v>
+        <v>26851.51</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.003287187039764272</v>
+        <v>-0.003094872928660952</v>
       </c>
     </row>
     <row r="81">
@@ -1323,10 +1323,10 @@
         <v>45135</v>
       </c>
       <c r="B81" t="n">
-        <v>16948.35</v>
+        <v>26893.17</v>
       </c>
       <c r="C81" t="n">
-        <v>0.001722894699512922</v>
+        <v>0.001551495614213083</v>
       </c>
     </row>
     <row r="82">
@@ -1334,10 +1334,10 @@
         <v>45138</v>
       </c>
       <c r="B82" t="n">
-        <v>17059</v>
+        <v>27069.01</v>
       </c>
       <c r="C82" t="n">
-        <v>0.006528659132009951</v>
+        <v>0.006538463111637638</v>
       </c>
     </row>
     <row r="83">
@@ -1345,10 +1345,10 @@
         <v>45139</v>
       </c>
       <c r="B83" t="n">
-        <v>17051.15</v>
+        <v>27054.6</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.0004601676534380372</v>
+        <v>-0.0005323430742387725</v>
       </c>
     </row>
     <row r="84">
@@ -1356,10 +1356,10 @@
         <v>45140</v>
       </c>
       <c r="B84" t="n">
-        <v>16858.95</v>
+        <v>26752.71</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.01127196699342858</v>
+        <v>-0.01115854605131839</v>
       </c>
     </row>
     <row r="85">
@@ -1367,10 +1367,10 @@
         <v>45141</v>
       </c>
       <c r="B85" t="n">
-        <v>16772.3</v>
+        <v>26617.02</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.00513970324367774</v>
+        <v>-0.005072009527259058</v>
       </c>
     </row>
     <row r="86">
@@ -1378,10 +1378,10 @@
         <v>45142</v>
       </c>
       <c r="B86" t="n">
-        <v>16890.6</v>
+        <v>26800.55</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0070532962086296</v>
+        <v>0.006895212161241115</v>
       </c>
     </row>
     <row r="87">
@@ -1389,10 +1389,10 @@
         <v>45145</v>
       </c>
       <c r="B87" t="n">
-        <v>16956.35</v>
+        <v>26800.55</v>
       </c>
       <c r="C87" t="n">
-        <v>0.003892697713521187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -1400,10 +1400,10 @@
         <v>45146</v>
       </c>
       <c r="B88" t="n">
-        <v>16949.25</v>
+        <v>26888.29</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.0004187221896221338</v>
+        <v>0.003273813410545667</v>
       </c>
     </row>
     <row r="89">
@@ -1411,10 +1411,10 @@
         <v>45147</v>
       </c>
       <c r="B89" t="n">
-        <v>17003.85</v>
+        <v>26969.85</v>
       </c>
       <c r="C89" t="n">
-        <v>0.003221381477056529</v>
+        <v>0.003033290700152236</v>
       </c>
     </row>
     <row r="90">
@@ -1422,10 +1422,10 @@
         <v>45148</v>
       </c>
       <c r="B90" t="n">
-        <v>16939.85</v>
+        <v>26875.85</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.003763853480241219</v>
+        <v>-0.003485373481869614</v>
       </c>
     </row>
     <row r="91">
@@ -1433,10 +1433,10 @@
         <v>45149</v>
       </c>
       <c r="B91" t="n">
-        <v>16860.15</v>
+        <v>26747.06</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.00470488227463628</v>
+        <v>-0.004792034484490615</v>
       </c>
     </row>
     <row r="92">
@@ -1444,10 +1444,10 @@
         <v>45152</v>
       </c>
       <c r="B92" t="n">
-        <v>16825.55</v>
+        <v>26692.04</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.002052176285501695</v>
+        <v>-0.002057048512995485</v>
       </c>
     </row>
     <row r="93">
@@ -1455,10 +1455,10 @@
         <v>45154</v>
       </c>
       <c r="B93" t="n">
-        <v>16853.05</v>
+        <v>26740.32</v>
       </c>
       <c r="C93" t="n">
-        <v>0.001634419082882976</v>
+        <v>0.001808778946831957</v>
       </c>
     </row>
     <row r="94">
@@ -1466,10 +1466,10 @@
         <v>45155</v>
       </c>
       <c r="B94" t="n">
-        <v>16802.25</v>
+        <v>26655.59</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.003014291181714812</v>
+        <v>-0.003168623262548853</v>
       </c>
     </row>
     <row r="95">
@@ -1477,10 +1477,10 @@
         <v>45156</v>
       </c>
       <c r="B95" t="n">
-        <v>16757.7</v>
+        <v>26584.59</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.002651430611971595</v>
+        <v>-0.002663606395506557</v>
       </c>
     </row>
     <row r="96">
@@ -1488,10 +1488,10 @@
         <v>45159</v>
       </c>
       <c r="B96" t="n">
-        <v>16852.05</v>
+        <v>26735.62</v>
       </c>
       <c r="C96" t="n">
-        <v>0.005630247587675941</v>
+        <v>0.005681110748745777</v>
       </c>
     </row>
     <row r="97">
@@ -1499,10 +1499,10 @@
         <v>45160</v>
       </c>
       <c r="B97" t="n">
-        <v>16905.25</v>
+        <v>26821.65</v>
       </c>
       <c r="C97" t="n">
-        <v>0.003156885957494859</v>
+        <v>0.003217804561854276</v>
       </c>
     </row>
     <row r="98">
@@ -1510,10 +1510,10 @@
         <v>45161</v>
       </c>
       <c r="B98" t="n">
-        <v>16950.25</v>
+        <v>26892.81</v>
       </c>
       <c r="C98" t="n">
-        <v>0.002661894973454926</v>
+        <v>0.002653080627030846</v>
       </c>
     </row>
     <row r="99">
@@ -1521,10 +1521,10 @@
         <v>45162</v>
       </c>
       <c r="B99" t="n">
-        <v>16930.15</v>
+        <v>26858.29</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.00118582321794658</v>
+        <v>-0.001283614467956329</v>
       </c>
     </row>
     <row r="100">
@@ -1532,10 +1532,10 @@
         <v>45163</v>
       </c>
       <c r="B100" t="n">
-        <v>16820.85</v>
+        <v>26690.68</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.006455938074972911</v>
+        <v>-0.006240531321986653</v>
       </c>
     </row>
     <row r="101">
@@ -1543,10 +1543,10 @@
         <v>45166</v>
       </c>
       <c r="B101" t="n">
-        <v>16875.3</v>
+        <v>26774.43</v>
       </c>
       <c r="C101" t="n">
-        <v>0.00323705401332286</v>
+        <v>0.003137799411629727</v>
       </c>
     </row>
     <row r="102">
@@ -1554,10 +1554,10 @@
         <v>45167</v>
       </c>
       <c r="B102" t="n">
-        <v>16927.3</v>
+        <v>26859.95</v>
       </c>
       <c r="C102" t="n">
-        <v>0.003081426700562329</v>
+        <v>0.003194092273859805</v>
       </c>
     </row>
     <row r="103">
@@ -1565,10 +1565,10 @@
         <v>45168</v>
       </c>
       <c r="B103" t="n">
-        <v>16968.95</v>
+        <v>26923.17</v>
       </c>
       <c r="C103" t="n">
-        <v>0.002460522351467764</v>
+        <v>0.002353690159512478</v>
       </c>
     </row>
     <row r="104">
@@ -1576,10 +1576,10 @@
         <v>45169</v>
       </c>
       <c r="B104" t="n">
-        <v>16924.3</v>
+        <v>26848.76</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.002631276537440552</v>
+        <v>-0.002763790445181602</v>
       </c>
     </row>
     <row r="105">
@@ -1587,10 +1587,10 @@
         <v>45170</v>
       </c>
       <c r="B105" t="n">
-        <v>17074.55</v>
+        <v>27079.48</v>
       </c>
       <c r="C105" t="n">
-        <v>0.008877767470441889</v>
+        <v>0.008593320510891456</v>
       </c>
     </row>
     <row r="106">
@@ -1598,10 +1598,10 @@
         <v>45173</v>
       </c>
       <c r="B106" t="n">
-        <v>17180.95</v>
+        <v>27237.14</v>
       </c>
       <c r="C106" t="n">
-        <v>0.006231496584097496</v>
+        <v>0.005822120661105767</v>
       </c>
     </row>
     <row r="107">
@@ -1609,10 +1609,10 @@
         <v>45174</v>
       </c>
       <c r="B107" t="n">
-        <v>17252.1</v>
+        <v>27353.85</v>
       </c>
       <c r="C107" t="n">
-        <v>0.004141214542851213</v>
+        <v>0.004284957965483782</v>
       </c>
     </row>
     <row r="108">
@@ -1620,10 +1620,10 @@
         <v>45175</v>
       </c>
       <c r="B108" t="n">
-        <v>17284.6</v>
+        <v>27401.79</v>
       </c>
       <c r="C108" t="n">
-        <v>0.001883828635354634</v>
+        <v>0.001752586930176214</v>
       </c>
     </row>
     <row r="109">
@@ -1631,10 +1631,10 @@
         <v>45176</v>
       </c>
       <c r="B109" t="n">
-        <v>17385.5</v>
+        <v>27558.08</v>
       </c>
       <c r="C109" t="n">
-        <v>0.005837566388577242</v>
+        <v>0.005703641988351826</v>
       </c>
     </row>
     <row r="110">
@@ -1642,10 +1642,10 @@
         <v>45177</v>
       </c>
       <c r="B110" t="n">
-        <v>17487.45</v>
+        <v>27718.99</v>
       </c>
       <c r="C110" t="n">
-        <v>0.005864082137413407</v>
+        <v>0.00583894088412551</v>
       </c>
     </row>
     <row r="111">
@@ -1653,10 +1653,10 @@
         <v>45180</v>
       </c>
       <c r="B111" t="n">
-        <v>17653.35</v>
+        <v>27976.63</v>
       </c>
       <c r="C111" t="n">
-        <v>0.009486803393290444</v>
+        <v>0.009294710954475649</v>
       </c>
     </row>
     <row r="112">
@@ -1664,10 +1664,10 @@
         <v>45181</v>
       </c>
       <c r="B112" t="n">
-        <v>17460.55</v>
+        <v>27677.59</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.01092143984003036</v>
+        <v>-0.01068892143192379</v>
       </c>
     </row>
     <row r="113">
@@ -1675,10 +1675,10 @@
         <v>45182</v>
       </c>
       <c r="B113" t="n">
-        <v>17526.75</v>
+        <v>27781.84</v>
       </c>
       <c r="C113" t="n">
-        <v>0.003791404050845992</v>
+        <v>0.003766585168723191</v>
       </c>
     </row>
     <row r="114">
@@ -1686,10 +1686,10 @@
         <v>45183</v>
       </c>
       <c r="B114" t="n">
-        <v>17603.5</v>
+        <v>27904.05</v>
       </c>
       <c r="C114" t="n">
-        <v>0.00437902063987905</v>
+        <v>0.004398916702421429</v>
       </c>
     </row>
     <row r="115">
@@ -1697,10 +1697,10 @@
         <v>45184</v>
       </c>
       <c r="B115" t="n">
-        <v>17665.8</v>
+        <v>28008.55</v>
       </c>
       <c r="C115" t="n">
-        <v>0.003539068935154877</v>
+        <v>0.003744976087700636</v>
       </c>
     </row>
     <row r="116">
@@ -1708,10 +1708,10 @@
         <v>45187</v>
       </c>
       <c r="B116" t="n">
-        <v>17613.6</v>
+        <v>27917.97</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.00295486193662331</v>
+        <v>-0.003234012471191816</v>
       </c>
     </row>
     <row r="117">
@@ -1719,10 +1719,10 @@
         <v>45189</v>
       </c>
       <c r="B117" t="n">
-        <v>17449.35</v>
+        <v>27661.22</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.009325180542308242</v>
+        <v>-0.009196585568363336</v>
       </c>
     </row>
     <row r="118">
@@ -1730,10 +1730,10 @@
         <v>45190</v>
       </c>
       <c r="B118" t="n">
-        <v>17303.5</v>
+        <v>27428.96</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.008358477536412501</v>
+        <v>-0.00839659277501148</v>
       </c>
     </row>
     <row r="119">
@@ -1741,10 +1741,10 @@
         <v>45191</v>
       </c>
       <c r="B119" t="n">
-        <v>17260.8</v>
+        <v>27356.12</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.002467708845031447</v>
+        <v>-0.002655587379178814</v>
       </c>
     </row>
     <row r="120">
@@ -1752,10 +1752,10 @@
         <v>45194</v>
       </c>
       <c r="B120" t="n">
-        <v>17272.55</v>
+        <v>27373.48</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0006807332220986062</v>
+        <v>0.0006345929174167431</v>
       </c>
     </row>
     <row r="121">
@@ -1763,10 +1763,10 @@
         <v>45195</v>
       </c>
       <c r="B121" t="n">
-        <v>17276.75</v>
+        <v>27374.02</v>
       </c>
       <c r="C121" t="n">
-        <v>0.0002431603903303436</v>
+        <v>1.972712274800337e-05</v>
       </c>
     </row>
     <row r="122">
@@ -1774,10 +1774,10 @@
         <v>45196</v>
       </c>
       <c r="B122" t="n">
-        <v>17341.6</v>
+        <v>27479.02</v>
       </c>
       <c r="C122" t="n">
-        <v>0.003753599490644799</v>
+        <v>0.00383575375483769</v>
       </c>
     </row>
     <row r="123">
@@ -1785,10 +1785,10 @@
         <v>45197</v>
       </c>
       <c r="B123" t="n">
-        <v>17170.45</v>
+        <v>27213.53</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.009869331549568594</v>
+        <v>-0.009661552704572474</v>
       </c>
     </row>
     <row r="124">
@@ -1796,10 +1796,10 @@
         <v>45198</v>
       </c>
       <c r="B124" t="n">
-        <v>17292.6</v>
+        <v>27407.75</v>
       </c>
       <c r="C124" t="n">
-        <v>0.007113966145325223</v>
+        <v>0.007136891097920817</v>
       </c>
     </row>
     <row r="125">
@@ -1807,10 +1807,10 @@
         <v>45202</v>
       </c>
       <c r="B125" t="n">
-        <v>17254.4</v>
+        <v>27341.58</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.002209037391716517</v>
+        <v>-0.002414280632302868</v>
       </c>
     </row>
     <row r="126">
@@ -1818,10 +1818,10 @@
         <v>45203</v>
       </c>
       <c r="B126" t="n">
-        <v>17123.1</v>
+        <v>27138.62</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.007609653189911136</v>
+        <v>-0.007423126242155798</v>
       </c>
     </row>
     <row r="127">
@@ -1829,10 +1829,10 @@
         <v>45204</v>
       </c>
       <c r="B127" t="n">
-        <v>17195.8</v>
+        <v>27251.23</v>
       </c>
       <c r="C127" t="n">
-        <v>0.004245726533162797</v>
+        <v>0.004149437222673802</v>
       </c>
     </row>
     <row r="128">
@@ -1840,10 +1840,10 @@
         <v>45205</v>
       </c>
       <c r="B128" t="n">
-        <v>17293.6</v>
+        <v>27401.7</v>
       </c>
       <c r="C128" t="n">
-        <v>0.005687435303969535</v>
+        <v>0.00552158563118077</v>
       </c>
     </row>
     <row r="129">
@@ -1851,10 +1851,10 @@
         <v>45208</v>
       </c>
       <c r="B129" t="n">
-        <v>17127.7</v>
+        <v>27133.98</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.009593144284590682</v>
+        <v>-0.009770196739618431</v>
       </c>
     </row>
     <row r="130">
@@ -1862,10 +1862,10 @@
         <v>45209</v>
       </c>
       <c r="B130" t="n">
-        <v>17303.35</v>
+        <v>27414.77</v>
       </c>
       <c r="C130" t="n">
-        <v>0.01025531740980967</v>
+        <v>0.01034827916877656</v>
       </c>
     </row>
     <row r="131">
@@ -1873,10 +1873,10 @@
         <v>45210</v>
       </c>
       <c r="B131" t="n">
-        <v>17407.35</v>
+        <v>27579.17</v>
       </c>
       <c r="C131" t="n">
-        <v>0.006010396830671505</v>
+        <v>0.005996767435947792</v>
       </c>
     </row>
     <row r="132">
@@ -1884,10 +1884,10 @@
         <v>45211</v>
       </c>
       <c r="B132" t="n">
-        <v>17419.7</v>
+        <v>27603.17</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0007094704248493677</v>
+        <v>0.0008702219827501079</v>
       </c>
     </row>
     <row r="133">
@@ -1895,10 +1895,10 @@
         <v>45212</v>
       </c>
       <c r="B133" t="n">
-        <v>17390.35</v>
+        <v>27560.74</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.001684874021940841</v>
+        <v>-0.001537142291990201</v>
       </c>
     </row>
     <row r="134">
@@ -1906,10 +1906,10 @@
         <v>45215</v>
       </c>
       <c r="B134" t="n">
-        <v>17393</v>
+        <v>27556.58</v>
       </c>
       <c r="C134" t="n">
-        <v>0.0001523833620371562</v>
+        <v>-0.0001509393434283579</v>
       </c>
     </row>
     <row r="135">
@@ -1917,10 +1917,10 @@
         <v>45216</v>
       </c>
       <c r="B135" t="n">
-        <v>17467.7</v>
+        <v>27677.66</v>
       </c>
       <c r="C135" t="n">
-        <v>0.004294831253952802</v>
+        <v>0.004393868905357534</v>
       </c>
     </row>
     <row r="136">
@@ -1928,10 +1928,10 @@
         <v>45217</v>
       </c>
       <c r="B136" t="n">
-        <v>17344</v>
+        <v>27478.04</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.007081642116592346</v>
+        <v>-0.007212314913905282</v>
       </c>
     </row>
     <row r="137">
@@ -1939,10 +1939,10 @@
         <v>45218</v>
       </c>
       <c r="B137" t="n">
-        <v>17310.5</v>
+        <v>27417.67</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.001931503690036918</v>
+        <v>-0.002197027153319597</v>
       </c>
     </row>
     <row r="138">
@@ -1950,10 +1950,10 @@
         <v>45219</v>
       </c>
       <c r="B138" t="n">
-        <v>17208.75</v>
+        <v>27261.48</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.005877935357153197</v>
+        <v>-0.005696691221391159</v>
       </c>
     </row>
     <row r="139">
@@ -1961,10 +1961,10 @@
         <v>45222</v>
       </c>
       <c r="B139" t="n">
-        <v>16888.7</v>
+        <v>26746.23</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.0185980968983801</v>
+        <v>-0.01890029448144415</v>
       </c>
     </row>
     <row r="140">
@@ -1972,10 +1972,10 @@
         <v>45224</v>
       </c>
       <c r="B140" t="n">
-        <v>16760.8</v>
+        <v>26550.02</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.007573111015057532</v>
+        <v>-0.007335987165293933</v>
       </c>
     </row>
     <row r="141">
@@ -1983,10 +1983,10 @@
         <v>45225</v>
       </c>
       <c r="B141" t="n">
-        <v>16555.45</v>
+        <v>26221.4</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.01225180182330188</v>
+        <v>-0.01237739180610786</v>
       </c>
     </row>
     <row r="142">
@@ -1994,10 +1994,10 @@
         <v>45226</v>
       </c>
       <c r="B142" t="n">
-        <v>16765.45</v>
+        <v>26548.45</v>
       </c>
       <c r="C142" t="n">
-        <v>0.01268464463364039</v>
+        <v>0.01247263685386746</v>
       </c>
     </row>
     <row r="143">
@@ -2005,10 +2005,10 @@
         <v>45229</v>
       </c>
       <c r="B143" t="n">
-        <v>16826.1</v>
+        <v>26644.35</v>
       </c>
       <c r="C143" t="n">
-        <v>0.003617558729410719</v>
+        <v>0.003612263616143307</v>
       </c>
     </row>
     <row r="144">
@@ -2016,10 +2016,10 @@
         <v>45230</v>
       </c>
       <c r="B144" t="n">
-        <v>16801.1</v>
+        <v>26605.19</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.001485786961922253</v>
+        <v>-0.001469729980277279</v>
       </c>
     </row>
     <row r="145">
@@ -2027,10 +2027,10 @@
         <v>45231</v>
       </c>
       <c r="B145" t="n">
-        <v>16732.95</v>
+        <v>26494.41</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.004056282029152758</v>
+        <v>-0.004163849233927652</v>
       </c>
     </row>
     <row r="146">
@@ -2038,10 +2038,10 @@
         <v>45232</v>
       </c>
       <c r="B146" t="n">
-        <v>16890.8</v>
+        <v>26745.39</v>
       </c>
       <c r="C146" t="n">
-        <v>0.009433483037957879</v>
+        <v>0.009472941650710442</v>
       </c>
     </row>
     <row r="147">
@@ -2049,10 +2049,10 @@
         <v>45233</v>
       </c>
       <c r="B147" t="n">
-        <v>17000.95</v>
+        <v>26917.85</v>
       </c>
       <c r="C147" t="n">
-        <v>0.006521301536931423</v>
+        <v>0.006448214066050229</v>
       </c>
     </row>
     <row r="148">
@@ -2060,10 +2060,10 @@
         <v>45236</v>
       </c>
       <c r="B148" t="n">
-        <v>17159.4</v>
+        <v>27168.96</v>
       </c>
       <c r="C148" t="n">
-        <v>0.009320067407997845</v>
+        <v>0.009328753968091741</v>
       </c>
     </row>
     <row r="149">
@@ -2071,10 +2071,10 @@
         <v>45237</v>
       </c>
       <c r="B149" t="n">
-        <v>17187.8</v>
+        <v>27210.7</v>
       </c>
       <c r="C149" t="n">
-        <v>0.001655069524575392</v>
+        <v>0.00153631202666582</v>
       </c>
     </row>
     <row r="150">
@@ -2082,10 +2082,10 @@
         <v>45238</v>
       </c>
       <c r="B150" t="n">
-        <v>17259.7</v>
+        <v>27315.13</v>
       </c>
       <c r="C150" t="n">
-        <v>0.004183199711423224</v>
+        <v>0.00383782850128811</v>
       </c>
     </row>
     <row r="151">
@@ -2093,10 +2093,10 @@
         <v>45239</v>
       </c>
       <c r="B151" t="n">
-        <v>17218.9</v>
+        <v>27262.45</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.002363888132470349</v>
+        <v>-0.001928601474713854</v>
       </c>
     </row>
     <row r="152">
@@ -2104,10 +2104,10 @@
         <v>45240</v>
       </c>
       <c r="B152" t="n">
-        <v>17256.6</v>
+        <v>27307.15</v>
       </c>
       <c r="C152" t="n">
-        <v>0.002189454610921571</v>
+        <v>0.001639617862664533</v>
       </c>
     </row>
     <row r="153">
@@ -2115,10 +2115,10 @@
         <v>45242</v>
       </c>
       <c r="B153" t="n">
-        <v>17361.1</v>
+        <v>27472.3</v>
       </c>
       <c r="C153" t="n">
-        <v>0.006055654068588323</v>
+        <v>0.006047866584392603</v>
       </c>
     </row>
     <row r="154">
@@ -2126,10 +2126,10 @@
         <v>45243</v>
       </c>
       <c r="B154" t="n">
-        <v>17318.6</v>
+        <v>27397.03</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.002448001566720981</v>
+        <v>-0.002739850685963718</v>
       </c>
     </row>
     <row r="155">
@@ -2137,10 +2137,10 @@
         <v>45245</v>
       </c>
       <c r="B155" t="n">
-        <v>17508.05</v>
+        <v>27696.7</v>
       </c>
       <c r="C155" t="n">
-        <v>0.01093910593235026</v>
+        <v>0.01093804693428457</v>
       </c>
     </row>
     <row r="156">
@@ -2148,10 +2148,10 @@
         <v>45246</v>
       </c>
       <c r="B156" t="n">
-        <v>17593.1</v>
+        <v>27830.55</v>
       </c>
       <c r="C156" t="n">
-        <v>0.004857765427903171</v>
+        <v>0.004832705701401263</v>
       </c>
     </row>
     <row r="157">
@@ -2159,10 +2159,10 @@
         <v>45247</v>
       </c>
       <c r="B157" t="n">
-        <v>17600.5</v>
+        <v>27841.96</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0004206194473970193</v>
+        <v>0.0004099811178721602</v>
       </c>
     </row>
     <row r="158">
@@ -2170,10 +2170,10 @@
         <v>45250</v>
       </c>
       <c r="B158" t="n">
-        <v>17573.65</v>
+        <v>27803.07</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.001525524843044135</v>
+        <v>-0.001396812580723439</v>
       </c>
     </row>
     <row r="159">
@@ -2181,10 +2181,10 @@
         <v>45251</v>
       </c>
       <c r="B159" t="n">
-        <v>17627.6</v>
+        <v>27878.73</v>
       </c>
       <c r="C159" t="n">
-        <v>0.003069937093318487</v>
+        <v>0.002721282218114851</v>
       </c>
     </row>
     <row r="160">
@@ -2192,10 +2192,10 @@
         <v>45252</v>
       </c>
       <c r="B160" t="n">
-        <v>17627.7</v>
+        <v>27880.71</v>
       </c>
       <c r="C160" t="n">
-        <v>5.672922008814751e-06</v>
+        <v>7.102188657803765e-05</v>
       </c>
     </row>
     <row r="161">
@@ -2203,10 +2203,10 @@
         <v>45253</v>
       </c>
       <c r="B161" t="n">
-        <v>17639.4</v>
+        <v>27900.93</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0006637281097363612</v>
+        <v>0.0007252326070605886</v>
       </c>
     </row>
     <row r="162">
@@ -2214,10 +2214,10 @@
         <v>45254</v>
       </c>
       <c r="B162" t="n">
-        <v>17643.5</v>
+        <v>27903.66</v>
       </c>
       <c r="C162" t="n">
-        <v>0.0002324342097803633</v>
+        <v>9.784620082564643e-05</v>
       </c>
     </row>
     <row r="163">
@@ -2225,10 +2225,10 @@
         <v>45258</v>
       </c>
       <c r="B163" t="n">
-        <v>17741.8</v>
+        <v>28057.77</v>
       </c>
       <c r="C163" t="n">
-        <v>0.005571456910477002</v>
+        <v>0.005522931400397058</v>
       </c>
     </row>
     <row r="164">
@@ -2236,10 +2236,10 @@
         <v>45259</v>
       </c>
       <c r="B164" t="n">
-        <v>17904.1</v>
+        <v>28305.34</v>
       </c>
       <c r="C164" t="n">
-        <v>0.009147888038417706</v>
+        <v>0.008823580776376794</v>
       </c>
     </row>
     <row r="165">
@@ -2247,10 +2247,10 @@
         <v>45260</v>
       </c>
       <c r="B165" t="n">
-        <v>17987.95</v>
+        <v>28442.43</v>
       </c>
       <c r="C165" t="n">
-        <v>0.004683284834200219</v>
+        <v>0.004843255724891415</v>
       </c>
     </row>
     <row r="166">
@@ -2258,10 +2258,10 @@
         <v>45261</v>
       </c>
       <c r="B166" t="n">
-        <v>18115.35</v>
+        <v>28639.22</v>
       </c>
       <c r="C166" t="n">
-        <v>0.007082519130862552</v>
+        <v>0.006918888435341275</v>
       </c>
     </row>
     <row r="167">
@@ -2269,10 +2269,10 @@
         <v>45264</v>
       </c>
       <c r="B167" t="n">
-        <v>18448.5</v>
+        <v>29164.88</v>
       </c>
       <c r="C167" t="n">
-        <v>0.01839048100091922</v>
+        <v>0.01835455015883802</v>
       </c>
     </row>
     <row r="168">
@@ -2280,10 +2280,10 @@
         <v>45265</v>
       </c>
       <c r="B168" t="n">
-        <v>18588.55</v>
+        <v>29393.89</v>
       </c>
       <c r="C168" t="n">
-        <v>0.007591403095102534</v>
+        <v>0.007852252435120555</v>
       </c>
     </row>
     <row r="169">
@@ -2291,10 +2291,10 @@
         <v>45266</v>
       </c>
       <c r="B169" t="n">
-        <v>18680</v>
+        <v>29540.16</v>
       </c>
       <c r="C169" t="n">
-        <v>0.004919695188704942</v>
+        <v>0.004976204238363868</v>
       </c>
     </row>
     <row r="170">
@@ -2302,10 +2302,10 @@
         <v>45267</v>
       </c>
       <c r="B170" t="n">
-        <v>18703.85</v>
+        <v>29584.41</v>
       </c>
       <c r="C170" t="n">
-        <v>0.001276766595289081</v>
+        <v>0.001497960742257387</v>
       </c>
     </row>
     <row r="171">
@@ -2313,10 +2313,10 @@
         <v>45268</v>
       </c>
       <c r="B171" t="n">
-        <v>18703.5</v>
+        <v>29581</v>
       </c>
       <c r="C171" t="n">
-        <v>-1.871272492015574e-05</v>
+        <v>-0.0001152634106950101</v>
       </c>
     </row>
     <row r="172">
@@ -2324,10 +2324,10 @@
         <v>45271</v>
       </c>
       <c r="B172" t="n">
-        <v>18770.2</v>
+        <v>29686.17</v>
       </c>
       <c r="C172" t="n">
-        <v>0.003566177453417918</v>
+        <v>0.00355532267333758</v>
       </c>
     </row>
     <row r="173">
@@ -2335,10 +2335,10 @@
         <v>45272</v>
       </c>
       <c r="B173" t="n">
-        <v>18686.8</v>
+        <v>29547.24</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.004443213178335959</v>
+        <v>-0.004679957030495951</v>
       </c>
     </row>
     <row r="174">
@@ -2346,10 +2346,10 @@
         <v>45273</v>
       </c>
       <c r="B174" t="n">
-        <v>18751.45</v>
+        <v>29646.19</v>
       </c>
       <c r="C174" t="n">
-        <v>0.003459661365241784</v>
+        <v>0.003348874548011915</v>
       </c>
     </row>
     <row r="175">
@@ -2357,10 +2357,10 @@
         <v>45274</v>
       </c>
       <c r="B175" t="n">
-        <v>18973.85</v>
+        <v>29999.07</v>
       </c>
       <c r="C175" t="n">
-        <v>0.0118604161278193</v>
+        <v>0.01190304723811053</v>
       </c>
     </row>
     <row r="176">
@@ -2368,10 +2368,10 @@
         <v>45275</v>
       </c>
       <c r="B176" t="n">
-        <v>19145.05</v>
+        <v>30266.81</v>
       </c>
       <c r="C176" t="n">
-        <v>0.009022944737098637</v>
+        <v>0.008924943339910341</v>
       </c>
     </row>
     <row r="177">
@@ -2379,10 +2379,10 @@
         <v>45278</v>
       </c>
       <c r="B177" t="n">
-        <v>19155.55</v>
+        <v>30279.67</v>
       </c>
       <c r="C177" t="n">
-        <v>0.0005484446371255558</v>
+        <v>0.0004248878557071567</v>
       </c>
     </row>
     <row r="178">
@@ -2390,10 +2390,10 @@
         <v>45279</v>
       </c>
       <c r="B178" t="n">
-        <v>19169.25</v>
+        <v>30303.95</v>
       </c>
       <c r="C178" t="n">
-        <v>0.0007151974232011415</v>
+        <v>0.0008018581444251272</v>
       </c>
     </row>
     <row r="179">
@@ -2401,10 +2401,10 @@
         <v>45280</v>
       </c>
       <c r="B179" t="n">
-        <v>18779.45</v>
+        <v>29685.12</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.02033465054710015</v>
+        <v>-0.02042077022962363</v>
       </c>
     </row>
     <row r="180">
@@ -2412,10 +2412,10 @@
         <v>45281</v>
       </c>
       <c r="B180" t="n">
-        <v>18941.8</v>
+        <v>29949.13</v>
       </c>
       <c r="C180" t="n">
-        <v>0.00864508811493403</v>
+        <v>0.008893681413449039</v>
       </c>
     </row>
     <row r="181">
@@ -2423,10 +2423,10 @@
         <v>45282</v>
       </c>
       <c r="B181" t="n">
-        <v>19054.7</v>
+        <v>30123.53</v>
       </c>
       <c r="C181" t="n">
-        <v>0.005960362795510488</v>
+        <v>0.005823207552272835</v>
       </c>
     </row>
     <row r="182">
@@ -2434,10 +2434,10 @@
         <v>45286</v>
       </c>
       <c r="B182" t="n">
-        <v>19148.85</v>
+        <v>30277.19</v>
       </c>
       <c r="C182" t="n">
-        <v>0.004941038169060441</v>
+        <v>0.005100995799629082</v>
       </c>
     </row>
     <row r="183">
@@ -2445,10 +2445,10 @@
         <v>45287</v>
       </c>
       <c r="B183" t="n">
-        <v>19296.95</v>
+        <v>30502.3</v>
       </c>
       <c r="C183" t="n">
-        <v>0.007734145914767732</v>
+        <v>0.007434970021986897</v>
       </c>
     </row>
     <row r="184">
@@ -2456,10 +2456,10 @@
         <v>45288</v>
       </c>
       <c r="B184" t="n">
-        <v>19399.25</v>
+        <v>30671.72</v>
       </c>
       <c r="C184" t="n">
-        <v>0.005301355913758243</v>
+        <v>0.005554335246850339</v>
       </c>
     </row>
     <row r="185">
@@ -2467,10 +2467,10 @@
         <v>45289</v>
       </c>
       <c r="B185" t="n">
-        <v>19429.15</v>
+        <v>30720.28</v>
       </c>
       <c r="C185" t="n">
-        <v>0.001541296699614669</v>
+        <v>0.001583217374180546</v>
       </c>
     </row>
     <row r="186">
@@ -2478,10 +2478,10 @@
         <v>45292</v>
       </c>
       <c r="B186" t="n">
-        <v>19469.5</v>
+        <v>30785.67</v>
       </c>
       <c r="C186" t="n">
-        <v>0.002076776390114832</v>
+        <v>0.002128561328217149</v>
       </c>
     </row>
     <row r="187">
@@ -2489,10 +2489,10 @@
         <v>45293</v>
       </c>
       <c r="B187" t="n">
-        <v>19418.4</v>
+        <v>30702.07</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.002624617992244227</v>
+        <v>-0.002715549149977847</v>
       </c>
     </row>
     <row r="188">
@@ -2500,10 +2500,10 @@
         <v>45294</v>
       </c>
       <c r="B188" t="n">
-        <v>19367.15</v>
+        <v>30621.23</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.002639249371729879</v>
+        <v>-0.002633047217988849</v>
       </c>
     </row>
     <row r="189">
@@ -2511,10 +2511,10 @@
         <v>45295</v>
       </c>
       <c r="B189" t="n">
-        <v>19541.25</v>
+        <v>30891.8</v>
       </c>
       <c r="C189" t="n">
-        <v>0.008989448628218266</v>
+        <v>0.008836026508405981</v>
       </c>
     </row>
     <row r="190">
@@ -2522,10 +2522,10 @@
         <v>45296</v>
       </c>
       <c r="B190" t="n">
-        <v>19590.6</v>
+        <v>30971.04</v>
       </c>
       <c r="C190" t="n">
-        <v>0.00252542698138547</v>
+        <v>0.002565081995869578</v>
       </c>
     </row>
     <row r="191">
@@ -2533,10 +2533,10 @@
         <v>45299</v>
       </c>
       <c r="B191" t="n">
-        <v>19417.7</v>
+        <v>30694.41</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.00882566128653528</v>
+        <v>-0.008931892503448391</v>
       </c>
     </row>
     <row r="192">
@@ -2544,10 +2544,10 @@
         <v>45300</v>
       </c>
       <c r="B192" t="n">
-        <v>19459.55</v>
+        <v>30761.38</v>
       </c>
       <c r="C192" t="n">
-        <v>0.002155250106861129</v>
+        <v>0.00218183050268772</v>
       </c>
     </row>
     <row r="193">
@@ -2555,10 +2555,10 @@
         <v>45301</v>
       </c>
       <c r="B193" t="n">
-        <v>19517.85</v>
+        <v>30858.6</v>
       </c>
       <c r="C193" t="n">
-        <v>0.002995958282694167</v>
+        <v>0.00316045639044793</v>
       </c>
     </row>
     <row r="194">
@@ -2566,10 +2566,10 @@
         <v>45302</v>
       </c>
       <c r="B194" t="n">
-        <v>19584.35</v>
+        <v>30961.04</v>
       </c>
       <c r="C194" t="n">
-        <v>0.003407137568943286</v>
+        <v>0.003319658053184682</v>
       </c>
     </row>
     <row r="195">
@@ -2577,10 +2577,10 @@
         <v>45303</v>
       </c>
       <c r="B195" t="n">
-        <v>19745.6</v>
+        <v>31215.69</v>
       </c>
       <c r="C195" t="n">
-        <v>0.008233615105939229</v>
+        <v>0.008224852911917546</v>
       </c>
     </row>
     <row r="196">
@@ -2588,10 +2588,10 @@
         <v>45306</v>
       </c>
       <c r="B196" t="n">
-        <v>19885.55</v>
+        <v>31440.7</v>
       </c>
       <c r="C196" t="n">
-        <v>0.007087654971234203</v>
+        <v>0.00720823406434401</v>
       </c>
     </row>
     <row r="197">
@@ -2599,10 +2599,10 @@
         <v>45307</v>
       </c>
       <c r="B197" t="n">
-        <v>19827.55</v>
+        <v>31346.19</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.002916690762890695</v>
+        <v>-0.003005976330043625</v>
       </c>
     </row>
     <row r="198">
@@ -2610,10 +2610,10 @@
         <v>45308</v>
       </c>
       <c r="B198" t="n">
-        <v>19487.6</v>
+        <v>30808.23</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.01714533565669996</v>
+        <v>-0.01716189431634274</v>
       </c>
     </row>
     <row r="199">
@@ -2621,10 +2621,10 @@
         <v>45309</v>
       </c>
       <c r="B199" t="n">
-        <v>19414.8</v>
+        <v>30693.11</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.00373570886101926</v>
+        <v>-0.003736663871958812</v>
       </c>
     </row>
     <row r="200">
@@ -2632,10 +2632,10 @@
         <v>45310</v>
       </c>
       <c r="B200" t="n">
-        <v>19606.4</v>
+        <v>31000.47</v>
       </c>
       <c r="C200" t="n">
-        <v>0.009868759915116376</v>
+        <v>0.01001397382018321</v>
       </c>
     </row>
     <row r="201">
@@ -2643,10 +2643,10 @@
         <v>45311</v>
       </c>
       <c r="B201" t="n">
-        <v>19601.9</v>
+        <v>30992.54</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.0002295168924433266</v>
+        <v>-0.0002558025733158109</v>
       </c>
     </row>
     <row r="202">
@@ -2654,10 +2654,10 @@
         <v>45314</v>
       </c>
       <c r="B202" t="n">
-        <v>19206.45</v>
+        <v>30370.48</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.0201740647590285</v>
+        <v>-0.02007128166971794</v>
       </c>
     </row>
     <row r="203">
@@ -2665,10 +2665,10 @@
         <v>45315</v>
       </c>
       <c r="B203" t="n">
-        <v>19451</v>
+        <v>30756.68</v>
       </c>
       <c r="C203" t="n">
-        <v>0.01273270177466412</v>
+        <v>0.01271629556068921</v>
       </c>
     </row>
     <row r="204">
@@ -2676,10 +2676,10 @@
         <v>45316</v>
       </c>
       <c r="B204" t="n">
-        <v>19393</v>
+        <v>30669.27</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.002981851832810634</v>
+        <v>-0.00284198424537363</v>
       </c>
     </row>
     <row r="205">
@@ -2687,10 +2687,10 @@
         <v>45320</v>
       </c>
       <c r="B205" t="n">
-        <v>19711.65</v>
+        <v>31175.72</v>
       </c>
       <c r="C205" t="n">
-        <v>0.01643118651059661</v>
+        <v>0.01651327207983755</v>
       </c>
     </row>
     <row r="206">
@@ -2698,10 +2698,10 @@
         <v>45321</v>
       </c>
       <c r="B206" t="n">
-        <v>19574.2</v>
+        <v>30948.54</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.006973033713565391</v>
+        <v>-0.007287081100292192</v>
       </c>
     </row>
     <row r="207">
@@ -2709,10 +2709,10 @@
         <v>45322</v>
       </c>
       <c r="B207" t="n">
-        <v>19802.1</v>
+        <v>31303.35</v>
       </c>
       <c r="C207" t="n">
-        <v>0.01164287684809584</v>
+        <v>0.01146451496581102</v>
       </c>
     </row>
     <row r="208">
@@ -2720,10 +2720,10 @@
         <v>45323</v>
       </c>
       <c r="B208" t="n">
-        <v>19777.35</v>
+        <v>31254.33</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.001249867438302021</v>
+        <v>-0.001565966581851375</v>
       </c>
     </row>
     <row r="209">
@@ -2731,10 +2731,10 @@
         <v>45324</v>
       </c>
       <c r="B209" t="n">
-        <v>19910.8</v>
+        <v>31471.57</v>
       </c>
       <c r="C209" t="n">
-        <v>0.006747617855779486</v>
+        <v>0.006950716908665111</v>
       </c>
     </row>
     <row r="210">
@@ -2742,10 +2742,10 @@
         <v>45327</v>
       </c>
       <c r="B210" t="n">
-        <v>19853.5</v>
+        <v>31374.18</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.002877835144745489</v>
+        <v>-0.003094538975971006</v>
       </c>
     </row>
     <row r="211">
@@ -2753,10 +2753,10 @@
         <v>45328</v>
       </c>
       <c r="B211" t="n">
-        <v>20033.75</v>
+        <v>31661.8</v>
       </c>
       <c r="C211" t="n">
-        <v>0.009079003702118005</v>
+        <v>0.009167410909225238</v>
       </c>
     </row>
     <row r="212">
@@ -2764,10 +2764,10 @@
         <v>45329</v>
       </c>
       <c r="B212" t="n">
-        <v>20109.55</v>
+        <v>31776.4</v>
       </c>
       <c r="C212" t="n">
-        <v>0.00378361514943526</v>
+        <v>0.003619503628978782</v>
       </c>
     </row>
     <row r="213">
@@ -2775,10 +2775,10 @@
         <v>45330</v>
       </c>
       <c r="B213" t="n">
-        <v>19987.55</v>
+        <v>31590.02</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.00606676927131633</v>
+        <v>-0.00586535919739184</v>
       </c>
     </row>
     <row r="214">
@@ -2786,10 +2786,10 @@
         <v>45331</v>
       </c>
       <c r="B214" t="n">
-        <v>19961.5</v>
+        <v>31540.02</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.001303311311291244</v>
+        <v>-0.001582778358481529</v>
       </c>
     </row>
     <row r="215">
@@ -2797,10 +2797,10 @@
         <v>45334</v>
       </c>
       <c r="B215" t="n">
-        <v>19675.2</v>
+        <v>31097.18</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.01434260952333233</v>
+        <v>-0.01404057448283169</v>
       </c>
     </row>
     <row r="216">
@@ -2808,10 +2808,10 @@
         <v>45335</v>
       </c>
       <c r="B216" t="n">
-        <v>19782.9</v>
+        <v>31273.51</v>
       </c>
       <c r="C216" t="n">
-        <v>0.005473896072212714</v>
+        <v>0.005670289074443335</v>
       </c>
     </row>
     <row r="217">
@@ -2819,10 +2819,10 @@
         <v>45336</v>
       </c>
       <c r="B217" t="n">
-        <v>19922.3</v>
+        <v>31494.22</v>
       </c>
       <c r="C217" t="n">
-        <v>0.007046489645097465</v>
+        <v>0.007057410568880984</v>
       </c>
     </row>
     <row r="218">
@@ -2830,10 +2830,10 @@
         <v>45337</v>
       </c>
       <c r="B218" t="n">
-        <v>20037</v>
+        <v>31678.93</v>
       </c>
       <c r="C218" t="n">
-        <v>0.005757367372241085</v>
+        <v>0.005864885683785737</v>
       </c>
     </row>
     <row r="219">
@@ -2841,10 +2841,10 @@
         <v>45338</v>
       </c>
       <c r="B219" t="n">
-        <v>20164.9</v>
+        <v>31880.95</v>
       </c>
       <c r="C219" t="n">
-        <v>0.006383191096471563</v>
+        <v>0.006377109327871944</v>
       </c>
     </row>
     <row r="220">
@@ -2852,10 +2852,10 @@
         <v>45341</v>
       </c>
       <c r="B220" t="n">
-        <v>20241.1</v>
+        <v>31997.65</v>
       </c>
       <c r="C220" t="n">
-        <v>0.003778843435871204</v>
+        <v>0.003660493178528235</v>
       </c>
     </row>
     <row r="221">
@@ -2863,10 +2863,10 @@
         <v>45342</v>
       </c>
       <c r="B221" t="n">
-        <v>20271.9</v>
+        <v>32046.82</v>
       </c>
       <c r="C221" t="n">
-        <v>0.001521656431715757</v>
+        <v>0.001536675349596006</v>
       </c>
     </row>
     <row r="222">
@@ -2874,10 +2874,10 @@
         <v>45343</v>
       </c>
       <c r="B222" t="n">
-        <v>20128.3</v>
+        <v>31818.7</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.007083697137416967</v>
+        <v>-0.007118334986123354</v>
       </c>
     </row>
     <row r="223">
@@ -2885,10 +2885,10 @@
         <v>45344</v>
       </c>
       <c r="B223" t="n">
-        <v>20283.95</v>
+        <v>32072.1</v>
       </c>
       <c r="C223" t="n">
-        <v>0.007732893488272774</v>
+        <v>0.00796387030268364</v>
       </c>
     </row>
     <row r="224">
@@ -2896,10 +2896,10 @@
         <v>45345</v>
       </c>
       <c r="B224" t="n">
-        <v>20313.5</v>
+        <v>32115.37</v>
       </c>
       <c r="C224" t="n">
-        <v>0.001456816842873243</v>
+        <v>0.001349147701584785</v>
       </c>
     </row>
     <row r="225">
@@ -2907,10 +2907,10 @@
         <v>45348</v>
       </c>
       <c r="B225" t="n">
-        <v>20255.8</v>
+        <v>32025.05</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.002840475545819343</v>
+        <v>-0.002812360561313731</v>
       </c>
     </row>
     <row r="226">
@@ -2918,10 +2918,10 @@
         <v>45349</v>
       </c>
       <c r="B226" t="n">
-        <v>20292.85</v>
+        <v>32079.15</v>
       </c>
       <c r="C226" t="n">
-        <v>0.001829105737615855</v>
+        <v>0.00168930259281419</v>
       </c>
     </row>
     <row r="227">
@@ -2929,10 +2929,10 @@
         <v>45350</v>
       </c>
       <c r="B227" t="n">
-        <v>20020.4</v>
+        <v>31639.8</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.0134259110967655</v>
+        <v>-0.0136958117655861</v>
       </c>
     </row>
     <row r="228">
@@ -2940,10 +2940,10 @@
         <v>45351</v>
       </c>
       <c r="B228" t="n">
-        <v>20090.05</v>
+        <v>31777.02</v>
       </c>
       <c r="C228" t="n">
-        <v>0.003478951469501057</v>
+        <v>0.004336942711395286</v>
       </c>
     </row>
     <row r="229">
@@ -2951,10 +2951,10 @@
         <v>45352</v>
       </c>
       <c r="B229" t="n">
-        <v>20349.8</v>
+        <v>32180.25</v>
       </c>
       <c r="C229" t="n">
-        <v>0.01292928589027897</v>
+        <v>0.01268935853645181</v>
       </c>
     </row>
     <row r="230">
@@ -2962,10 +2962,10 @@
         <v>45353</v>
       </c>
       <c r="B230" t="n">
-        <v>20421.35</v>
+        <v>32285.63</v>
       </c>
       <c r="C230" t="n">
-        <v>0.003516005071302786</v>
+        <v>0.003274679345250719</v>
       </c>
     </row>
     <row r="231">
@@ -2973,10 +2973,10 @@
         <v>45355</v>
       </c>
       <c r="B231" t="n">
-        <v>20432.05</v>
+        <v>32299.06</v>
       </c>
       <c r="C231" t="n">
-        <v>0.000523961442314036</v>
+        <v>0.0004159745372787071</v>
       </c>
     </row>
     <row r="232">
@@ -2984,10 +2984,10 @@
         <v>45356</v>
       </c>
       <c r="B232" t="n">
-        <v>20382</v>
+        <v>32226.64</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.002449582885711399</v>
+        <v>-0.002242170515179165</v>
       </c>
     </row>
     <row r="233">
@@ -2995,10 +2995,10 @@
         <v>45357</v>
       </c>
       <c r="B233" t="n">
-        <v>20379.55</v>
+        <v>32220.89</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.000120204101658361</v>
+        <v>-0.000178423813341988</v>
       </c>
     </row>
     <row r="234">
@@ -3006,10 +3006,10 @@
         <v>45358</v>
       </c>
       <c r="B234" t="n">
-        <v>20434.8</v>
+        <v>32311.54</v>
       </c>
       <c r="C234" t="n">
-        <v>0.002711051029095302</v>
+        <v>0.002813392181283625</v>
       </c>
     </row>
     <row r="235">
@@ -3017,10 +3017,10 @@
         <v>45362</v>
       </c>
       <c r="B235" t="n">
-        <v>20288.75</v>
+        <v>32079.33</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.00714712157691777</v>
+        <v>-0.007186596491532082</v>
       </c>
     </row>
     <row r="236">
@@ -3028,10 +3028,10 @@
         <v>45363</v>
       </c>
       <c r="B236" t="n">
-        <v>20171.4</v>
+        <v>31899.19</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.005783993592508141</v>
+        <v>-0.005615453938720094</v>
       </c>
     </row>
     <row r="237">
@@ -3039,10 +3039,10 @@
         <v>45364</v>
       </c>
       <c r="B237" t="n">
-        <v>19646.3</v>
+        <v>31073.54</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.02603190656077425</v>
+        <v>-0.0258831023609063</v>
       </c>
     </row>
     <row r="238">
@@ -3050,10 +3050,10 @@
         <v>45365</v>
       </c>
       <c r="B238" t="n">
-        <v>19916.35</v>
+        <v>31509.46</v>
       </c>
       <c r="C238" t="n">
-        <v>0.01374559077281723</v>
+        <v>0.01402865589179725</v>
       </c>
     </row>
     <row r="239">
@@ -3061,10 +3061,10 @@
         <v>45366</v>
       </c>
       <c r="B239" t="n">
-        <v>19825.2</v>
+        <v>31360.67</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.004576641804346582</v>
+        <v>-0.004722073942238336</v>
       </c>
     </row>
     <row r="240">
@@ -3072,10 +3072,10 @@
         <v>45369</v>
       </c>
       <c r="B240" t="n">
-        <v>19843.1</v>
+        <v>31387.34</v>
       </c>
       <c r="C240" t="n">
-        <v>0.0009028912696971148</v>
+        <v>0.0008504282593453372</v>
       </c>
     </row>
     <row r="241">
@@ -3083,10 +3083,10 @@
         <v>45370</v>
       </c>
       <c r="B241" t="n">
-        <v>19610.55</v>
+        <v>31023.13</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.01171943899894667</v>
+        <v>-0.01160372302973112</v>
       </c>
     </row>
     <row r="242">
@@ -3094,10 +3094,10 @@
         <v>45371</v>
       </c>
       <c r="B242" t="n">
-        <v>19632.05</v>
+        <v>31058.15</v>
       </c>
       <c r="C242" t="n">
-        <v>0.001096348649068934</v>
+        <v>0.001128835162667263</v>
       </c>
     </row>
     <row r="243">
@@ -3105,10 +3105,10 @@
         <v>45372</v>
       </c>
       <c r="B243" t="n">
-        <v>19897.4</v>
+        <v>31469.62</v>
       </c>
       <c r="C243" t="n">
-        <v>0.0135161636202028</v>
+        <v>0.01324837442024074</v>
       </c>
     </row>
     <row r="244">
@@ -3116,10 +3116,10 @@
         <v>45373</v>
       </c>
       <c r="B244" t="n">
-        <v>19994.6</v>
+        <v>31622.7</v>
       </c>
       <c r="C244" t="n">
-        <v>0.004885060359644866</v>
+        <v>0.004864373958122226</v>
       </c>
     </row>
     <row r="245">
@@ -3127,10 +3127,10 @@
         <v>45377</v>
       </c>
       <c r="B245" t="n">
-        <v>20005.25</v>
+        <v>31635.97</v>
       </c>
       <c r="C245" t="n">
-        <v>0.0005326438138297807</v>
+        <v>0.0004196352620111643</v>
       </c>
     </row>
     <row r="246">
@@ -3138,10 +3138,10 @@
         <v>45378</v>
       </c>
       <c r="B246" t="n">
-        <v>20087.8</v>
+        <v>31765.52</v>
       </c>
       <c r="C246" t="n">
-        <v>0.004126416815585898</v>
+        <v>0.004095022216799471</v>
       </c>
     </row>
     <row r="247">
@@ -3149,10 +3149,10 @@
         <v>45379</v>
       </c>
       <c r="B247" t="n">
-        <v>20255.15</v>
+        <v>32043.2</v>
       </c>
       <c r="C247" t="n">
-        <v>0.008330927229462715</v>
+        <v>0.008741553734993079</v>
       </c>
     </row>
     <row r="248">
@@ -3160,10 +3160,10 @@
         <v>45383</v>
       </c>
       <c r="B248" t="n">
-        <v>20492.55</v>
+        <v>32393.59</v>
       </c>
       <c r="C248" t="n">
-        <v>0.01172047602708437</v>
+        <v>0.01093492535077645</v>
       </c>
     </row>
     <row r="249">
@@ -3171,10 +3171,10 @@
         <v>45384</v>
       </c>
       <c r="B249" t="n">
-        <v>20569.75</v>
+        <v>32513.29</v>
       </c>
       <c r="C249" t="n">
-        <v>0.003767222722403929</v>
+        <v>0.003695175496139846</v>
       </c>
     </row>
     <row r="250">
@@ -3182,10 +3182,10 @@
         <v>45385</v>
       </c>
       <c r="B250" t="n">
-        <v>20605.7</v>
+        <v>32567.82</v>
       </c>
       <c r="C250" t="n">
-        <v>0.001747712052893258</v>
+        <v>0.001677160324285776</v>
       </c>
     </row>
     <row r="251">
@@ -3193,10 +3193,10 @@
         <v>45386</v>
       </c>
       <c r="B251" t="n">
-        <v>20664.65</v>
+        <v>32655.68</v>
       </c>
       <c r="C251" t="n">
-        <v>0.002860858888559914</v>
+        <v>0.002697755023210124</v>
       </c>
     </row>
     <row r="252">
@@ -3204,10 +3204,10 @@
         <v>45387</v>
       </c>
       <c r="B252" t="n">
-        <v>20715.1</v>
+        <v>32723.97</v>
       </c>
       <c r="C252" t="n">
-        <v>0.002441367262450367</v>
+        <v>0.002091213534674452</v>
       </c>
     </row>
     <row r="253">
@@ -3215,10 +3215,10 @@
         <v>45390</v>
       </c>
       <c r="B253" t="n">
-        <v>20819.1</v>
+        <v>32890.84</v>
       </c>
       <c r="C253" t="n">
-        <v>0.005020492297888923</v>
+        <v>0.005099320161948473</v>
       </c>
     </row>
     <row r="254">
@@ -3226,10 +3226,10 @@
         <v>45391</v>
       </c>
       <c r="B254" t="n">
-        <v>20790.7</v>
+        <v>32848.16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.00136413197496521</v>
+        <v>-0.00129762572193326</v>
       </c>
     </row>
     <row r="255">
@@ -3237,10 +3237,10 @@
         <v>45392</v>
       </c>
       <c r="B255" t="n">
-        <v>20915.2</v>
+        <v>33045.8</v>
       </c>
       <c r="C255" t="n">
-        <v>0.005988254363729961</v>
+        <v>0.006016775368848704</v>
       </c>
     </row>
     <row r="256">
@@ -3248,10 +3248,10 @@
         <v>45394</v>
       </c>
       <c r="B256" t="n">
-        <v>20745.5</v>
+        <v>32772.26</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.008113716340269361</v>
+        <v>-0.008277602600027856</v>
       </c>
     </row>
     <row r="257">
@@ -3259,10 +3259,10 @@
         <v>45397</v>
       </c>
       <c r="B257" t="n">
-        <v>20478.75</v>
+        <v>32365.11</v>
       </c>
       <c r="C257" t="n">
-        <v>-0.01285821021426337</v>
+        <v>-0.01242361680274728</v>
       </c>
     </row>
     <row r="258">
@@ -3270,10 +3270,10 @@
         <v>45398</v>
       </c>
       <c r="B258" t="n">
-        <v>20423</v>
+        <v>32269.59</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.002722334126838755</v>
+        <v>-0.00295132628932826</v>
       </c>
     </row>
     <row r="259">
@@ -3281,10 +3281,10 @@
         <v>45400</v>
       </c>
       <c r="B259" t="n">
-        <v>20324.7</v>
+        <v>32097.36</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.004813200803016171</v>
+        <v>-0.00533722306357165</v>
       </c>
     </row>
     <row r="260">
@@ -3292,10 +3292,10 @@
         <v>45401</v>
       </c>
       <c r="B260" t="n">
-        <v>20385.2</v>
+        <v>32199.48</v>
       </c>
       <c r="C260" t="n">
-        <v>0.002976673702440813</v>
+        <v>0.003181570073052642</v>
       </c>
     </row>
     <row r="261">
@@ -3303,10 +3303,10 @@
         <v>45404</v>
       </c>
       <c r="B261" t="n">
-        <v>20574.85</v>
+        <v>32489.88</v>
       </c>
       <c r="C261" t="n">
-        <v>0.009303318093518698</v>
+        <v>0.009018779185254067</v>
       </c>
     </row>
     <row r="262">
@@ -3314,10 +3314,10 @@
         <v>45405</v>
       </c>
       <c r="B262" t="n">
-        <v>20652.65</v>
+        <v>32589.5</v>
       </c>
       <c r="C262" t="n">
-        <v>0.00378131553814498</v>
+        <v>0.003066185532233368</v>
       </c>
     </row>
     <row r="263">
@@ -3325,10 +3325,10 @@
         <v>45406</v>
       </c>
       <c r="B263" t="n">
-        <v>20730.65</v>
+        <v>32716.27</v>
       </c>
       <c r="C263" t="n">
-        <v>0.003776755041120738</v>
+        <v>0.003889903189677746</v>
       </c>
     </row>
     <row r="264">
@@ -3336,10 +3336,10 @@
         <v>45407</v>
       </c>
       <c r="B264" t="n">
-        <v>20867.9</v>
+        <v>32929.34</v>
       </c>
       <c r="C264" t="n">
-        <v>0.00662063176986738</v>
+        <v>0.006512661742918535</v>
       </c>
     </row>
     <row r="265">
@@ -3347,10 +3347,10 @@
         <v>45408</v>
       </c>
       <c r="B265" t="n">
-        <v>20839.35</v>
+        <v>32877.25</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.00136812999870628</v>
+        <v>-0.001581871971925275</v>
       </c>
     </row>
     <row r="266">
@@ -3358,10 +3358,10 @@
         <v>45411</v>
       </c>
       <c r="B266" t="n">
-        <v>20992.2</v>
+        <v>33139.16</v>
       </c>
       <c r="C266" t="n">
-        <v>0.007334681743912386</v>
+        <v>0.007966298884487077</v>
       </c>
     </row>
     <row r="267">
@@ -3369,10 +3369,10 @@
         <v>45412</v>
       </c>
       <c r="B267" t="n">
-        <v>20997.2</v>
+        <v>33142.57</v>
       </c>
       <c r="C267" t="n">
-        <v>0.0002381837063289982</v>
+        <v>0.0001028994096410329</v>
       </c>
     </row>
     <row r="268">
@@ -3380,10 +3380,10 @@
         <v>45414</v>
       </c>
       <c r="B268" t="n">
-        <v>21083.6</v>
+        <v>33282.09</v>
       </c>
       <c r="C268" t="n">
-        <v>0.004114834358866837</v>
+        <v>0.004209691644311064</v>
       </c>
     </row>
     <row r="269">
@@ -3391,10 +3391,10 @@
         <v>45415</v>
       </c>
       <c r="B269" t="n">
-        <v>20959.55</v>
+        <v>33078.63</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.005883720047809682</v>
+        <v>-0.006113197819007099</v>
       </c>
     </row>
     <row r="270">
@@ -3402,10 +3402,10 @@
         <v>45418</v>
       </c>
       <c r="B270" t="n">
-        <v>20864.95</v>
+        <v>32940.93</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.004513455680107525</v>
+        <v>-0.004162808435536736</v>
       </c>
     </row>
     <row r="271">
@@ -3413,10 +3413,10 @@
         <v>45419</v>
       </c>
       <c r="B271" t="n">
-        <v>20636.05</v>
+        <v>32590.07</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.01097055109166334</v>
+        <v>-0.01065118683655863</v>
       </c>
     </row>
     <row r="272">
@@ -3424,10 +3424,10 @@
         <v>45420</v>
       </c>
       <c r="B272" t="n">
-        <v>20704.9</v>
+        <v>32701.87</v>
       </c>
       <c r="C272" t="n">
-        <v>0.003336394319649383</v>
+        <v>0.003430492785072348</v>
       </c>
     </row>
     <row r="273">
@@ -3435,10 +3435,10 @@
         <v>45421</v>
       </c>
       <c r="B273" t="n">
-        <v>20344.8</v>
+        <v>32131.88</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.01739201831450532</v>
+        <v>-0.01742989009497009</v>
       </c>
     </row>
     <row r="274">
@@ -3446,10 +3446,10 @@
         <v>45422</v>
       </c>
       <c r="B274" t="n">
-        <v>20469.1</v>
+        <v>32334.65</v>
       </c>
       <c r="C274" t="n">
-        <v>0.006109669301246567</v>
+        <v>0.006310555124692474</v>
       </c>
     </row>
     <row r="275">
@@ -3457,10 +3457,10 @@
         <v>45425</v>
       </c>
       <c r="B275" t="n">
-        <v>20511</v>
+        <v>32412.12</v>
       </c>
       <c r="C275" t="n">
-        <v>0.002046987898832953</v>
+        <v>0.002395881817183643</v>
       </c>
     </row>
     <row r="276">
@@ -3468,10 +3468,10 @@
         <v>45426</v>
       </c>
       <c r="B276" t="n">
-        <v>20683.8</v>
+        <v>32674.67</v>
       </c>
       <c r="C276" t="n">
-        <v>0.008424747696357926</v>
+        <v>0.008100364925219372</v>
       </c>
     </row>
     <row r="277">
@@ -3479,10 +3479,10 @@
         <v>45427</v>
       </c>
       <c r="B277" t="n">
-        <v>20741.85</v>
+        <v>32755.09</v>
       </c>
       <c r="C277" t="n">
-        <v>0.002806544252023313</v>
+        <v>0.002461233732429458</v>
       </c>
     </row>
     <row r="278">
@@ -3490,10 +3490,10 @@
         <v>45428</v>
       </c>
       <c r="B278" t="n">
-        <v>20929.05</v>
+        <v>33056.88</v>
       </c>
       <c r="C278" t="n">
-        <v>0.009025231596988759</v>
+        <v>0.009213529866655801</v>
       </c>
     </row>
     <row r="279">
@@ -3501,10 +3501,10 @@
         <v>45429</v>
       </c>
       <c r="B279" t="n">
-        <v>21064.55</v>
+        <v>33267.49</v>
       </c>
       <c r="C279" t="n">
-        <v>0.006474254684278646</v>
+        <v>0.006371139684083982</v>
       </c>
     </row>
     <row r="280">
@@ -3512,10 +3512,10 @@
         <v>45430</v>
       </c>
       <c r="B280" t="n">
-        <v>21144.45</v>
+        <v>33379.66</v>
       </c>
       <c r="C280" t="n">
-        <v>0.003793102629773726</v>
+        <v>0.003371760237998345</v>
       </c>
     </row>
     <row r="281">
@@ -3523,10 +3523,10 @@
         <v>45433</v>
       </c>
       <c r="B281" t="n">
-        <v>21173.8</v>
+        <v>33456.67</v>
       </c>
       <c r="C281" t="n">
-        <v>0.001388071101400046</v>
+        <v>0.00230709360131276</v>
       </c>
     </row>
     <row r="282">
@@ -3534,10 +3534,10 @@
         <v>45434</v>
       </c>
       <c r="B282" t="n">
-        <v>21237.75</v>
+        <v>33547.23</v>
       </c>
       <c r="C282" t="n">
-        <v>0.003020241997185202</v>
+        <v>0.002706784626204772</v>
       </c>
     </row>
     <row r="283">
@@ -3545,10 +3545,10 @@
         <v>45435</v>
       </c>
       <c r="B283" t="n">
-        <v>21489.55</v>
+        <v>33941.03</v>
       </c>
       <c r="C283" t="n">
-        <v>0.01185624654212436</v>
+        <v>0.01173867410215368</v>
       </c>
     </row>
     <row r="284">
@@ -3556,10 +3556,10 @@
         <v>45436</v>
       </c>
       <c r="B284" t="n">
-        <v>21483.75</v>
+        <v>33931.48</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.0002698986251457036</v>
+        <v>-0.0002813703650124122</v>
       </c>
     </row>
     <row r="285">
@@ -3567,10 +3567,10 @@
         <v>45439</v>
       </c>
       <c r="B285" t="n">
-        <v>21493.95</v>
+        <v>33947.66</v>
       </c>
       <c r="C285" t="n">
-        <v>0.0004747774480713396</v>
+        <v>0.0004768433325041954</v>
       </c>
     </row>
     <row r="286">
@@ -3578,10 +3578,10 @@
         <v>45440</v>
       </c>
       <c r="B286" t="n">
-        <v>21387.35</v>
+        <v>33782.89</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.004959535125000358</v>
+        <v>-0.004853648233781205</v>
       </c>
     </row>
     <row r="287">
@@ -3589,10 +3589,10 @@
         <v>45441</v>
       </c>
       <c r="B287" t="n">
-        <v>21256.3</v>
+        <v>33584.03</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.006127453845380493</v>
+        <v>-0.005886411730908758</v>
       </c>
     </row>
     <row r="288">
@@ -3600,10 +3600,10 @@
         <v>45442</v>
       </c>
       <c r="B288" t="n">
-        <v>21038.55</v>
+        <v>33247.27</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.01024402177236872</v>
+        <v>-0.01002738503985379</v>
       </c>
     </row>
     <row r="289">
@@ -3611,10 +3611,10 @@
         <v>45443</v>
       </c>
       <c r="B289" t="n">
-        <v>21103.3</v>
+        <v>33344.28</v>
       </c>
       <c r="C289" t="n">
-        <v>0.003077683585608337</v>
+        <v>0.002917833554454408</v>
       </c>
     </row>
     <row r="290">
@@ -3622,10 +3622,10 @@
         <v>45446</v>
       </c>
       <c r="B290" t="n">
-        <v>21797.4</v>
+        <v>34449.55</v>
       </c>
       <c r="C290" t="n">
-        <v>0.03289059057114296</v>
+        <v>0.03314721445477309</v>
       </c>
     </row>
     <row r="291">
@@ -3633,10 +3633,10 @@
         <v>45447</v>
       </c>
       <c r="B291" t="n">
-        <v>20323.85</v>
+        <v>32132.96</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.06760209933294814</v>
+        <v>-0.06724587113619784</v>
       </c>
     </row>
     <row r="292">
@@ -3644,10 +3644,10 @@
         <v>45448</v>
       </c>
       <c r="B292" t="n">
-        <v>21054.4</v>
+        <v>33289.72</v>
       </c>
       <c r="C292" t="n">
-        <v>0.03594545324827747</v>
+        <v>0.0359991734343803</v>
       </c>
     </row>
     <row r="293">
@@ -3655,10 +3655,10 @@
         <v>45449</v>
       </c>
       <c r="B293" t="n">
-        <v>21365</v>
+        <v>33779.99</v>
       </c>
       <c r="C293" t="n">
-        <v>0.01475226081009184</v>
+        <v>0.01472736928997898</v>
       </c>
     </row>
     <row r="294">
@@ -3666,10 +3666,10 @@
         <v>45450</v>
       </c>
       <c r="B294" t="n">
-        <v>21748.55</v>
+        <v>34402.7</v>
       </c>
       <c r="C294" t="n">
-        <v>0.01795225836648728</v>
+        <v>0.01843428609659137</v>
       </c>
     </row>
     <row r="295">
@@ -3677,10 +3677,10 @@
         <v>45453</v>
       </c>
       <c r="B295" t="n">
-        <v>21808.25</v>
+        <v>34463.5</v>
       </c>
       <c r="C295" t="n">
-        <v>0.002745010586912677</v>
+        <v>0.001767303147718113</v>
       </c>
     </row>
     <row r="296">
@@ -3688,10 +3688,10 @@
         <v>45454</v>
       </c>
       <c r="B296" t="n">
-        <v>21852</v>
+        <v>34539.46</v>
       </c>
       <c r="C296" t="n">
-        <v>0.002006121536574534</v>
+        <v>0.002204070973638839</v>
       </c>
     </row>
     <row r="297">
@@ -3699,10 +3699,10 @@
         <v>45455</v>
       </c>
       <c r="B297" t="n">
-        <v>21960.95</v>
+        <v>34704.05</v>
       </c>
       <c r="C297" t="n">
-        <v>0.00498581365550077</v>
+        <v>0.004765274268908826</v>
       </c>
     </row>
     <row r="298">
@@ -3710,10 +3710,10 @@
         <v>45456</v>
       </c>
       <c r="B298" t="n">
-        <v>22080.25</v>
+        <v>34884.01</v>
       </c>
       <c r="C298" t="n">
-        <v>0.005432369728996189</v>
+        <v>0.0051855619156842</v>
       </c>
     </row>
     <row r="299">
@@ -3721,10 +3721,10 @@
         <v>45457</v>
       </c>
       <c r="B299" t="n">
-        <v>22214.3</v>
+        <v>35099.19</v>
       </c>
       <c r="C299" t="n">
-        <v>0.006071036333374913</v>
+        <v>0.006168442217508785</v>
       </c>
     </row>
     <row r="300">
@@ -3732,10 +3732,10 @@
         <v>45461</v>
       </c>
       <c r="B300" t="n">
-        <v>22329.6</v>
+        <v>35276.03</v>
       </c>
       <c r="C300" t="n">
-        <v>0.00519035035990334</v>
+        <v>0.005038292906474284</v>
       </c>
     </row>
     <row r="301">
@@ -3743,10 +3743,10 @@
         <v>45462</v>
       </c>
       <c r="B301" t="n">
-        <v>22224.9</v>
+        <v>35111.45</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.00468884350816845</v>
+        <v>-0.004665490986372367</v>
       </c>
     </row>
     <row r="302">
@@ -3754,10 +3754,10 @@
         <v>45463</v>
       </c>
       <c r="B302" t="n">
-        <v>22305.1</v>
+        <v>35240.94</v>
       </c>
       <c r="C302" t="n">
-        <v>0.003608565167897204</v>
+        <v>0.003687970733194046</v>
       </c>
     </row>
     <row r="303">
@@ -3765,10 +3765,10 @@
         <v>45464</v>
       </c>
       <c r="B303" t="n">
-        <v>22236.2</v>
+        <v>35112.57</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.003088979650393786</v>
+        <v>-0.003642638363221984</v>
       </c>
     </row>
     <row r="304">
@@ -3776,10 +3776,10 @@
         <v>45467</v>
       </c>
       <c r="B304" t="n">
-        <v>22289.1</v>
+        <v>35206.43</v>
       </c>
       <c r="C304" t="n">
-        <v>0.002379003606731267</v>
+        <v>0.002673116778407314</v>
       </c>
     </row>
     <row r="305">
@@ -3787,10 +3787,10 @@
         <v>45468</v>
       </c>
       <c r="B305" t="n">
-        <v>22370.65</v>
+        <v>35334.24</v>
       </c>
       <c r="C305" t="n">
-        <v>0.003658739024904767</v>
+        <v>0.003630302760035509</v>
       </c>
     </row>
     <row r="306">
@@ -3798,10 +3798,10 @@
         <v>45469</v>
       </c>
       <c r="B306" t="n">
-        <v>22436.8</v>
+        <v>35440.26</v>
       </c>
       <c r="C306" t="n">
-        <v>0.002956999461347642</v>
+        <v>0.003000489044054921</v>
       </c>
     </row>
     <row r="307">
@@ -3809,10 +3809,10 @@
         <v>45470</v>
       </c>
       <c r="B307" t="n">
-        <v>22537.4</v>
+        <v>35601.65</v>
       </c>
       <c r="C307" t="n">
-        <v>0.004483705341225219</v>
+        <v>0.004553860496508744</v>
       </c>
     </row>
     <row r="308">
@@ -3820,10 +3820,10 @@
         <v>45471</v>
       </c>
       <c r="B308" t="n">
-        <v>22559.7</v>
+        <v>35633.91</v>
       </c>
       <c r="C308" t="n">
-        <v>0.0009894663980760665</v>
+        <v>0.0009061377773220691</v>
       </c>
     </row>
     <row r="309">
@@ -3831,10 +3831,10 @@
         <v>45474</v>
       </c>
       <c r="B309" t="n">
-        <v>22727.6</v>
+        <v>35894.4</v>
       </c>
       <c r="C309" t="n">
-        <v>0.00744247485560523</v>
+        <v>0.007310171687586298</v>
       </c>
     </row>
     <row r="310">
@@ -3842,10 +3842,10 @@
         <v>45475</v>
       </c>
       <c r="B310" t="n">
-        <v>22675</v>
+        <v>35821.13</v>
       </c>
       <c r="C310" t="n">
-        <v>-0.002314366673119794</v>
+        <v>-0.002041265489881594</v>
       </c>
     </row>
     <row r="311">
@@ -3853,10 +3853,10 @@
         <v>45476</v>
       </c>
       <c r="B311" t="n">
-        <v>22851.2</v>
+        <v>36096.07</v>
       </c>
       <c r="C311" t="n">
-        <v>0.007770672546857815</v>
+        <v>0.007675358091718598</v>
       </c>
     </row>
     <row r="312">
@@ -3864,10 +3864,10 @@
         <v>45477</v>
       </c>
       <c r="B312" t="n">
-        <v>22914.2</v>
+        <v>36195.72</v>
       </c>
       <c r="C312" t="n">
-        <v>0.002756966811370942</v>
+        <v>0.002760688351945317</v>
       </c>
     </row>
     <row r="313">
@@ -3875,10 +3875,10 @@
         <v>45478</v>
       </c>
       <c r="B313" t="n">
-        <v>22987.65</v>
+        <v>36315.81</v>
       </c>
       <c r="C313" t="n">
-        <v>0.003205435930558442</v>
+        <v>0.003317795584671268</v>
       </c>
     </row>
     <row r="314">
@@ -3886,10 +3886,10 @@
         <v>45481</v>
       </c>
       <c r="B314" t="n">
-        <v>22971.15</v>
+        <v>36281.82</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.0007177767192383389</v>
+        <v>-0.0009359559927204497</v>
       </c>
     </row>
     <row r="315">
@@ -3897,10 +3897,10 @@
         <v>45482</v>
       </c>
       <c r="B315" t="n">
-        <v>23067.35</v>
+        <v>36444.29</v>
       </c>
       <c r="C315" t="n">
-        <v>0.004187861730910125</v>
+        <v>0.004478000276722627</v>
       </c>
     </row>
     <row r="316">
@@ -3908,10 +3908,10 @@
         <v>45483</v>
       </c>
       <c r="B316" t="n">
-        <v>22973.15</v>
+        <v>36308.37</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.004083694052415932</v>
+        <v>-0.003729528000133819</v>
       </c>
     </row>
     <row r="317">
@@ -3919,10 +3919,10 @@
         <v>45484</v>
       </c>
       <c r="B317" t="n">
-        <v>23005.25</v>
+        <v>36357.56</v>
       </c>
       <c r="C317" t="n">
-        <v>0.001397283350345946</v>
+        <v>0.001354784034645284</v>
       </c>
     </row>
     <row r="318">
@@ -3930,10 +3930,10 @@
         <v>45485</v>
       </c>
       <c r="B318" t="n">
-        <v>23095.45</v>
+        <v>36485.93</v>
       </c>
       <c r="C318" t="n">
-        <v>0.003920844155138603</v>
+        <v>0.003530764990830049</v>
       </c>
     </row>
     <row r="319">
@@ -3941,10 +3941,10 @@
         <v>45488</v>
       </c>
       <c r="B319" t="n">
-        <v>23209.85</v>
+        <v>36662.6</v>
       </c>
       <c r="C319" t="n">
-        <v>0.004953356613532023</v>
+        <v>0.004842140518276361</v>
       </c>
     </row>
     <row r="320">
@@ -3952,10 +3952,10 @@
         <v>45489</v>
       </c>
       <c r="B320" t="n">
-        <v>23204.25</v>
+        <v>36656.1</v>
       </c>
       <c r="C320" t="n">
-        <v>-0.0002412768716729685</v>
+        <v>-0.000177292390610595</v>
       </c>
     </row>
     <row r="321">
@@ -3963,10 +3963,10 @@
         <v>45491</v>
       </c>
       <c r="B321" t="n">
-        <v>23199.55</v>
+        <v>36662.75</v>
       </c>
       <c r="C321" t="n">
-        <v>-0.0002025491019964631</v>
+        <v>0.0001814159171324992</v>
       </c>
     </row>
     <row r="322">
@@ -3974,10 +3974,10 @@
         <v>45492</v>
       </c>
       <c r="B322" t="n">
-        <v>22853.6</v>
+        <v>36100.97</v>
       </c>
       <c r="C322" t="n">
-        <v>-0.0149119271710012</v>
+        <v>-0.01532290949260484</v>
       </c>
     </row>
     <row r="323">
@@ -3985,10 +3985,10 @@
         <v>45495</v>
       </c>
       <c r="B323" t="n">
-        <v>22942.65</v>
+        <v>36241.36</v>
       </c>
       <c r="C323" t="n">
-        <v>0.003896541463926928</v>
+        <v>0.003888815175880245</v>
       </c>
     </row>
     <row r="324">
@@ -3996,10 +3996,10 @@
         <v>45496</v>
       </c>
       <c r="B324" t="n">
-        <v>22865.2</v>
+        <v>36120.05</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.003375808810229031</v>
+        <v>-0.00334728056562994</v>
       </c>
     </row>
     <row r="325">
@@ -4007,10 +4007,10 @@
         <v>45497</v>
       </c>
       <c r="B325" t="n">
-        <v>22921.45</v>
+        <v>36204.55</v>
       </c>
       <c r="C325" t="n">
-        <v>0.002460070325210451</v>
+        <v>0.00233942090334871</v>
       </c>
     </row>
     <row r="326">
@@ -4018,10 +4018,10 @@
         <v>45498</v>
       </c>
       <c r="B326" t="n">
-        <v>22932.35</v>
+        <v>36199.79</v>
       </c>
       <c r="C326" t="n">
-        <v>0.0004755371060729541</v>
+        <v>-0.0001314751875109987</v>
       </c>
     </row>
     <row r="327">
@@ -4029,10 +4029,10 @@
         <v>45499</v>
       </c>
       <c r="B327" t="n">
-        <v>23292.05</v>
+        <v>36795.89</v>
       </c>
       <c r="C327" t="n">
-        <v>0.01568526557461403</v>
+        <v>0.01646694635521362</v>
       </c>
     </row>
     <row r="328">
@@ -4040,10 +4040,10 @@
         <v>45502</v>
       </c>
       <c r="B328" t="n">
-        <v>23401.7</v>
+        <v>36963.28</v>
       </c>
       <c r="C328" t="n">
-        <v>0.004707614829952744</v>
+        <v>0.004549149375106865</v>
       </c>
     </row>
     <row r="329">
@@ -4051,10 +4051,10 @@
         <v>45503</v>
       </c>
       <c r="B329" t="n">
-        <v>23440.9</v>
+        <v>37033.62</v>
       </c>
       <c r="C329" t="n">
-        <v>0.00167509198049709</v>
+        <v>0.001902969649879571</v>
       </c>
     </row>
     <row r="330">
@@ -4062,10 +4062,10 @@
         <v>45504</v>
       </c>
       <c r="B330" t="n">
-        <v>23530.8</v>
+        <v>37172.81</v>
       </c>
       <c r="C330" t="n">
-        <v>0.003835176976993093</v>
+        <v>0.003758476757065532</v>
       </c>
     </row>
     <row r="331">
@@ -4073,10 +4073,10 @@
         <v>45505</v>
       </c>
       <c r="B331" t="n">
-        <v>23506.6</v>
+        <v>37132.84</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.001028439322080077</v>
+        <v>-0.00107524827958938</v>
       </c>
     </row>
     <row r="332">
@@ -4084,10 +4084,10 @@
         <v>45506</v>
       </c>
       <c r="B332" t="n">
-        <v>23259.45</v>
+        <v>36747.98</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.01051406838930335</v>
+        <v>-0.01036441058642412</v>
       </c>
     </row>
     <row r="333">
@@ -4095,10 +4095,10 @@
         <v>45509</v>
       </c>
       <c r="B333" t="n">
-        <v>22542.45</v>
+        <v>35615.95</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.03082618032670592</v>
+        <v>-0.03080523065485519</v>
       </c>
     </row>
     <row r="334">
@@ -4106,10 +4106,10 @@
         <v>45510</v>
       </c>
       <c r="B334" t="n">
-        <v>22443.3</v>
+        <v>35461.87</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.004398368411596798</v>
+        <v>-0.004326151625886565</v>
       </c>
     </row>
     <row r="335">
@@ -4117,10 +4117,10 @@
         <v>45511</v>
       </c>
       <c r="B335" t="n">
-        <v>22848.9</v>
+        <v>36117.84</v>
       </c>
       <c r="C335" t="n">
-        <v>0.01807220863242054</v>
+        <v>0.01849789647302846</v>
       </c>
     </row>
     <row r="336">
@@ -4128,10 +4128,10 @@
         <v>45512</v>
       </c>
       <c r="B336" t="n">
-        <v>22705.7</v>
+        <v>35872.01</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.006267260130684682</v>
+        <v>-0.006806331718618663</v>
       </c>
     </row>
     <row r="337">
@@ -4139,10 +4139,10 @@
         <v>45513</v>
       </c>
       <c r="B337" t="n">
-        <v>22923.5</v>
+        <v>36210.76</v>
       </c>
       <c r="C337" t="n">
-        <v>0.00959230501592101</v>
+        <v>0.009443295761793147</v>
       </c>
     </row>
     <row r="338">
@@ -4150,10 +4150,10 @@
         <v>45516</v>
       </c>
       <c r="B338" t="n">
-        <v>22915.85</v>
+        <v>36201.68</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.0003337186729776009</v>
+        <v>-0.0002507541957142978</v>
       </c>
     </row>
     <row r="339">
@@ -4161,10 +4161,10 @@
         <v>45517</v>
       </c>
       <c r="B339" t="n">
-        <v>22705.8</v>
+        <v>35861.57</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.009166144829888423</v>
+        <v>-0.009394867862486</v>
       </c>
     </row>
     <row r="340">
@@ -4172,10 +4172,10 @@
         <v>45518</v>
       </c>
       <c r="B340" t="n">
-        <v>22672.65</v>
+        <v>35810.03</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.001459979388526156</v>
+        <v>-0.001437193073253629</v>
       </c>
     </row>
     <row r="341">
@@ -4183,10 +4183,10 @@
         <v>45520</v>
       </c>
       <c r="B341" t="n">
-        <v>23056.5</v>
+        <v>36416.03</v>
       </c>
       <c r="C341" t="n">
-        <v>0.01693008977777177</v>
+        <v>0.01692263312820463</v>
       </c>
     </row>
     <row r="342">
@@ -4194,10 +4194,10 @@
         <v>45523</v>
       </c>
       <c r="B342" t="n">
-        <v>23139.75</v>
+        <v>36543.64</v>
       </c>
       <c r="C342" t="n">
-        <v>0.003610695465486868</v>
+        <v>0.003504226023539614</v>
       </c>
     </row>
     <row r="343">
@@ -4205,10 +4205,10 @@
         <v>45524</v>
       </c>
       <c r="B343" t="n">
-        <v>23280.35</v>
+        <v>36766.36</v>
       </c>
       <c r="C343" t="n">
-        <v>0.006076124417938811</v>
+        <v>0.006094630967249159</v>
       </c>
     </row>
     <row r="344">
@@ -4216,10 +4216,10 @@
         <v>45525</v>
       </c>
       <c r="B344" t="n">
-        <v>23368.65</v>
+        <v>36903.21</v>
       </c>
       <c r="C344" t="n">
-        <v>0.003792898302645842</v>
+        <v>0.003722152532913192</v>
       </c>
     </row>
     <row r="345">
@@ -4227,10 +4227,10 @@
         <v>45526</v>
       </c>
       <c r="B345" t="n">
-        <v>23440.7</v>
+        <v>37012.52</v>
       </c>
       <c r="C345" t="n">
-        <v>0.003083190513786693</v>
+        <v>0.00296207294704165</v>
       </c>
     </row>
     <row r="346">
@@ -4238,10 +4238,10 @@
         <v>45527</v>
       </c>
       <c r="B346" t="n">
-        <v>23418.65</v>
+        <v>36972.8</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.0009406715669753041</v>
+        <v>-0.001073150382627119</v>
       </c>
     </row>
     <row r="347">
@@ -4249,10 +4249,10 @@
         <v>45530</v>
       </c>
       <c r="B347" t="n">
-        <v>23561.75</v>
+        <v>37195.12</v>
       </c>
       <c r="C347" t="n">
-        <v>0.006110514483114837</v>
+        <v>0.006013069066989729</v>
       </c>
     </row>
     <row r="348">
@@ -4260,10 +4260,10 @@
         <v>45531</v>
       </c>
       <c r="B348" t="n">
-        <v>23604.85</v>
+        <v>37257.85</v>
       </c>
       <c r="C348" t="n">
-        <v>0.00182923594384965</v>
+        <v>0.001686511563882442</v>
       </c>
     </row>
     <row r="349">
@@ -4271,10 +4271,10 @@
         <v>45532</v>
       </c>
       <c r="B349" t="n">
-        <v>23615.95</v>
+        <v>37276.16</v>
       </c>
       <c r="C349" t="n">
-        <v>0.0004702423442641823</v>
+        <v>0.0004914400589406398</v>
       </c>
     </row>
     <row r="350">
@@ -4282,10 +4282,10 @@
         <v>45533</v>
       </c>
       <c r="B350" t="n">
-        <v>23631.4</v>
+        <v>37302.5</v>
       </c>
       <c r="C350" t="n">
-        <v>0.0006542188647926661</v>
+        <v>0.0007066178490486852</v>
       </c>
     </row>
     <row r="351">
@@ -4293,10 +4293,10 @@
         <v>45534</v>
       </c>
       <c r="B351" t="n">
-        <v>23734.55</v>
+        <v>37459.06</v>
       </c>
       <c r="C351" t="n">
-        <v>0.00436495510210988</v>
+        <v>0.004197037732055486</v>
       </c>
     </row>
     <row r="352">
@@ -4304,10 +4304,10 @@
         <v>45537</v>
       </c>
       <c r="B352" t="n">
-        <v>23760.7</v>
+        <v>37502.59</v>
       </c>
       <c r="C352" t="n">
-        <v>0.001101769361542715</v>
+        <v>0.001162068669101624</v>
       </c>
     </row>
     <row r="353">
@@ -4315,10 +4315,10 @@
         <v>45538</v>
       </c>
       <c r="B353" t="n">
-        <v>23788.45</v>
+        <v>37548.28</v>
       </c>
       <c r="C353" t="n">
-        <v>0.001167894885251597</v>
+        <v>0.001218315854984997</v>
       </c>
     </row>
     <row r="354">
@@ -4326,10 +4326,10 @@
         <v>45539</v>
       </c>
       <c r="B354" t="n">
-        <v>23748.9</v>
+        <v>37487.02</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.001662571542071833</v>
+        <v>-0.001631499498778721</v>
       </c>
     </row>
     <row r="355">
@@ -4337,10 +4337,10 @@
         <v>45540</v>
       </c>
       <c r="B355" t="n">
-        <v>23762.8</v>
+        <v>37496.8</v>
       </c>
       <c r="C355" t="n">
-        <v>0.0005852902660754555</v>
+        <v>0.0002608903028302745</v>
       </c>
     </row>
     <row r="356">
@@ -4348,10 +4348,10 @@
         <v>45541</v>
       </c>
       <c r="B356" t="n">
-        <v>23477.7</v>
+        <v>37054.24</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.01199774437355861</v>
+        <v>-0.01180260715581072</v>
       </c>
     </row>
     <row r="357">
@@ -4359,10 +4359,10 @@
         <v>45544</v>
       </c>
       <c r="B357" t="n">
-        <v>23502.15</v>
+        <v>37097.47</v>
       </c>
       <c r="C357" t="n">
-        <v>0.001041413767106647</v>
+        <v>0.001166668105998303</v>
       </c>
     </row>
     <row r="358">
@@ -4370,10 +4370,10 @@
         <v>45545</v>
       </c>
       <c r="B358" t="n">
-        <v>23643.65</v>
+        <v>37313.25</v>
       </c>
       <c r="C358" t="n">
-        <v>0.006020725763387524</v>
+        <v>0.005816569162263585</v>
       </c>
     </row>
     <row r="359">
@@ -4381,10 +4381,10 @@
         <v>45546</v>
       </c>
       <c r="B359" t="n">
-        <v>23531.25</v>
+        <v>37140.18</v>
       </c>
       <c r="C359" t="n">
-        <v>-0.004753919128391848</v>
+        <v>-0.004638298727663748</v>
       </c>
     </row>
     <row r="360">
@@ -4392,10 +4392,10 @@
         <v>45547</v>
       </c>
       <c r="B360" t="n">
-        <v>23907.35</v>
+        <v>37720.89</v>
       </c>
       <c r="C360" t="n">
-        <v>0.01598300132802111</v>
+        <v>0.01563562696788212</v>
       </c>
     </row>
     <row r="361">
@@ -4403,10 +4403,10 @@
         <v>45548</v>
       </c>
       <c r="B361" t="n">
-        <v>23928.2</v>
+        <v>37757.29</v>
       </c>
       <c r="C361" t="n">
-        <v>0.0008721167339751368</v>
+        <v>0.0009649825335511508</v>
       </c>
     </row>
     <row r="362">
@@ -4414,10 +4414,10 @@
         <v>45551</v>
       </c>
       <c r="B362" t="n">
-        <v>23968.2</v>
+        <v>37804.18</v>
       </c>
       <c r="C362" t="n">
-        <v>0.001671667739320037</v>
+        <v>0.001241879382762878</v>
       </c>
     </row>
     <row r="363">
@@ -4425,10 +4425,10 @@
         <v>45552</v>
       </c>
       <c r="B363" t="n">
-        <v>23969.9</v>
+        <v>37806.44</v>
       </c>
       <c r="C363" t="n">
-        <v>7.092731202185121e-05</v>
+        <v>5.978174900245214e-05</v>
       </c>
     </row>
     <row r="364">
@@ -4436,10 +4436,10 @@
         <v>45553</v>
       </c>
       <c r="B364" t="n">
-        <v>23898.65</v>
+        <v>37668.29</v>
       </c>
       <c r="C364" t="n">
-        <v>-0.002972477982803423</v>
+        <v>-0.003654139347687879</v>
       </c>
     </row>
     <row r="365">
@@ -4447,10 +4447,10 @@
         <v>45554</v>
       </c>
       <c r="B365" t="n">
-        <v>23853.95</v>
+        <v>37616.67</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.001870398537155871</v>
+        <v>-0.001370383417989007</v>
       </c>
     </row>
     <row r="366">
@@ -4458,10 +4458,10 @@
         <v>45555</v>
       </c>
       <c r="B366" t="n">
-        <v>24193.8</v>
+        <v>38157.5</v>
       </c>
       <c r="C366" t="n">
-        <v>0.0142471163056852</v>
+        <v>0.01437740235911367</v>
       </c>
     </row>
     <row r="367">
@@ -4469,10 +4469,10 @@
         <v>45558</v>
       </c>
       <c r="B367" t="n">
-        <v>24379.2</v>
+        <v>38433.92</v>
       </c>
       <c r="C367" t="n">
-        <v>0.007663120303548876</v>
+        <v>0.007244185284675408</v>
       </c>
     </row>
     <row r="368">
@@ -4480,10 +4480,10 @@
         <v>45559</v>
       </c>
       <c r="B368" t="n">
-        <v>24389.7</v>
+        <v>38445.64</v>
       </c>
       <c r="C368" t="n">
-        <v>0.0004306950187045189</v>
+        <v>0.0003049389705760408</v>
       </c>
     </row>
     <row r="369">
@@ -4491,10 +4491,10 @@
         <v>45560</v>
       </c>
       <c r="B369" t="n">
-        <v>24372.9</v>
+        <v>38415.65</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.0006888153605825176</v>
+        <v>-0.0007800624466128836</v>
       </c>
     </row>
     <row r="370">
@@ -4502,10 +4502,10 @@
         <v>45561</v>
       </c>
       <c r="B370" t="n">
-        <v>24478.8</v>
+        <v>38620.05</v>
       </c>
       <c r="C370" t="n">
-        <v>0.004344989722191439</v>
+        <v>0.005320748184659108</v>
       </c>
     </row>
     <row r="371">
@@ -4513,10 +4513,10 @@
         <v>45562</v>
       </c>
       <c r="B371" t="n">
-        <v>24489.55</v>
+        <v>38614.95</v>
       </c>
       <c r="C371" t="n">
-        <v>0.0004391555141591841</v>
+        <v>-0.0001320557586022009</v>
       </c>
     </row>
     <row r="372">
@@ -4524,10 +4524,10 @@
         <v>45565</v>
       </c>
       <c r="B372" t="n">
-        <v>24245.2</v>
+        <v>38227.64</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.00997772519299045</v>
+        <v>-0.01003005312709193</v>
       </c>
     </row>
     <row r="373">
@@ -4535,10 +4535,10 @@
         <v>45566</v>
       </c>
       <c r="B373" t="n">
-        <v>24271.3</v>
+        <v>38265.16</v>
       </c>
       <c r="C373" t="n">
-        <v>0.001076501740550739</v>
+        <v>0.0009814887866477218</v>
       </c>
     </row>
     <row r="374">
@@ -4546,10 +4546,10 @@
         <v>45568</v>
       </c>
       <c r="B374" t="n">
-        <v>23755.45</v>
+        <v>37452.29</v>
       </c>
       <c r="C374" t="n">
-        <v>-0.02125349692847101</v>
+        <v>-0.02124308378692263</v>
       </c>
     </row>
     <row r="375">
@@ -4557,10 +4557,10 @@
         <v>45569</v>
       </c>
       <c r="B375" t="n">
-        <v>23534.95</v>
+        <v>37092.33</v>
       </c>
       <c r="C375" t="n">
-        <v>-0.009282080533098758</v>
+        <v>-0.009611161293474946</v>
       </c>
     </row>
     <row r="376">
@@ -4568,10 +4568,10 @@
         <v>45572</v>
       </c>
       <c r="B376" t="n">
-        <v>23181.95</v>
+        <v>36550.05</v>
       </c>
       <c r="C376" t="n">
-        <v>-0.01499896961752623</v>
+        <v>-0.01461973405283512</v>
       </c>
     </row>
     <row r="377">
@@ -4579,10 +4579,10 @@
         <v>45573</v>
       </c>
       <c r="B377" t="n">
-        <v>23512.55</v>
+        <v>37066.19</v>
       </c>
       <c r="C377" t="n">
-        <v>0.01426109537808506</v>
+        <v>0.01412145811018051</v>
       </c>
     </row>
     <row r="378">
@@ -4590,10 +4590,10 @@
         <v>45574</v>
       </c>
       <c r="B378" t="n">
-        <v>23599.6</v>
+        <v>37200.99</v>
       </c>
       <c r="C378" t="n">
-        <v>0.003702278145075732</v>
+        <v>0.003636737414878466</v>
       </c>
     </row>
     <row r="379">
@@ -4601,10 +4601,10 @@
         <v>45575</v>
       </c>
       <c r="B379" t="n">
-        <v>23598.15</v>
+        <v>37190.94</v>
       </c>
       <c r="C379" t="n">
-        <v>-6.144171935107412e-05</v>
+        <v>-0.0002701541007374963</v>
       </c>
     </row>
     <row r="380">
@@ -4612,10 +4612,10 @@
         <v>45576</v>
       </c>
       <c r="B380" t="n">
-        <v>23611.25</v>
+        <v>37203.52</v>
       </c>
       <c r="C380" t="n">
-        <v>0.0005551282621729658</v>
+        <v>0.0003382544243299979</v>
       </c>
     </row>
     <row r="381">
@@ -4623,10 +4623,10 @@
         <v>45579</v>
       </c>
       <c r="B381" t="n">
-        <v>23727.05</v>
+        <v>37374.44</v>
       </c>
       <c r="C381" t="n">
-        <v>0.004904441738577958</v>
+        <v>0.004594188936960952</v>
       </c>
     </row>
     <row r="382">
@@ -4634,10 +4634,10 @@
         <v>45580</v>
       </c>
       <c r="B382" t="n">
-        <v>23735.7</v>
+        <v>37392.36</v>
       </c>
       <c r="C382" t="n">
-        <v>0.0003645628091144548</v>
+        <v>0.0004794720670062702</v>
       </c>
     </row>
     <row r="383">
@@ -4645,10 +4645,10 @@
         <v>45581</v>
       </c>
       <c r="B383" t="n">
-        <v>23673.15</v>
+        <v>37290.96</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.002635270921017674</v>
+        <v>-0.002711783904519538</v>
       </c>
     </row>
     <row r="384">
@@ -4656,10 +4656,10 @@
         <v>45582</v>
       </c>
       <c r="B384" t="n">
-        <v>23377</v>
+        <v>36841.12</v>
       </c>
       <c r="C384" t="n">
-        <v>-0.01250995325928328</v>
+        <v>-0.0120629771934001</v>
       </c>
     </row>
     <row r="385">
@@ -4667,10 +4667,10 @@
         <v>45583</v>
       </c>
       <c r="B385" t="n">
-        <v>23440.7</v>
+        <v>36927</v>
       </c>
       <c r="C385" t="n">
-        <v>0.002724900543269015</v>
+        <v>0.002331090911459777</v>
       </c>
     </row>
     <row r="386">
@@ -4678,10 +4678,10 @@
         <v>45586</v>
       </c>
       <c r="B386" t="n">
-        <v>23263.25</v>
+        <v>36661.79</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.00757016641994479</v>
+        <v>-0.007182007745010432</v>
       </c>
     </row>
     <row r="387">
@@ -4689,10 +4689,10 @@
         <v>45587</v>
       </c>
       <c r="B387" t="n">
-        <v>22814.45</v>
+        <v>35961.33</v>
       </c>
       <c r="C387" t="n">
-        <v>-0.0192922313090389</v>
+        <v>-0.01910599564287507</v>
       </c>
     </row>
     <row r="388">
@@ -4700,10 +4700,10 @@
         <v>45588</v>
       </c>
       <c r="B388" t="n">
-        <v>22841.1</v>
+        <v>35994.45</v>
       </c>
       <c r="C388" t="n">
-        <v>0.001168119327882078</v>
+        <v>0.0009209892960020394</v>
       </c>
     </row>
     <row r="389">
@@ -4711,10 +4711,10 @@
         <v>45589</v>
       </c>
       <c r="B389" t="n">
-        <v>22787.85</v>
+        <v>35917.15</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.002331323797890694</v>
+        <v>-0.002147553303356364</v>
       </c>
     </row>
     <row r="390">
@@ -4722,10 +4722,10 @@
         <v>45590</v>
       </c>
       <c r="B390" t="n">
-        <v>22499.05</v>
+        <v>35458.88</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.01267342026562401</v>
+        <v>-0.01275908584060825</v>
       </c>
     </row>
     <row r="391">
@@ -4733,10 +4733,10 @@
         <v>45593</v>
       </c>
       <c r="B391" t="n">
-        <v>22649.95</v>
+        <v>35698.13</v>
       </c>
       <c r="C391" t="n">
-        <v>0.006706949848993782</v>
+        <v>0.006747252028264761</v>
       </c>
     </row>
     <row r="392">
@@ -4744,10 +4744,10 @@
         <v>45594</v>
       </c>
       <c r="B392" t="n">
-        <v>22795.05</v>
+        <v>35921.51</v>
       </c>
       <c r="C392" t="n">
-        <v>0.006406195157163674</v>
+        <v>0.006257470629414064</v>
       </c>
     </row>
     <row r="393">
@@ -4755,10 +4755,10 @@
         <v>45595</v>
       </c>
       <c r="B393" t="n">
-        <v>22749.8</v>
+        <v>35845.27</v>
       </c>
       <c r="C393" t="n">
-        <v>-0.001985080094143221</v>
+        <v>-0.002122405210694289</v>
       </c>
     </row>
     <row r="394">
@@ -4766,10 +4766,10 @@
         <v>45596</v>
       </c>
       <c r="B394" t="n">
-        <v>22689.35</v>
+        <v>35738.11</v>
       </c>
       <c r="C394" t="n">
-        <v>-0.002657166216845863</v>
+        <v>-0.002989515771536833</v>
       </c>
     </row>
     <row r="395">
@@ -4777,10 +4777,10 @@
         <v>45597</v>
       </c>
       <c r="B395" t="n">
-        <v>22823.55</v>
+        <v>35951.72</v>
       </c>
       <c r="C395" t="n">
-        <v>0.005914669217055524</v>
+        <v>0.005977092800934392</v>
       </c>
     </row>
     <row r="396">
@@ -4788,10 +4788,10 @@
         <v>45600</v>
       </c>
       <c r="B396" t="n">
-        <v>22518.3</v>
+        <v>35474.13</v>
       </c>
       <c r="C396" t="n">
-        <v>-0.01337434360561784</v>
+        <v>-0.01328420448312362</v>
       </c>
     </row>
     <row r="397">
@@ -4799,10 +4799,10 @@
         <v>45601</v>
       </c>
       <c r="B397" t="n">
-        <v>22679.85</v>
+        <v>35712.44</v>
       </c>
       <c r="C397" t="n">
-        <v>0.007174165012456601</v>
+        <v>0.006717853263772833</v>
       </c>
     </row>
     <row r="398">
@@ -4810,10 +4810,10 @@
         <v>45602</v>
       </c>
       <c r="B398" t="n">
-        <v>23031.2</v>
+        <v>36271.2</v>
       </c>
       <c r="C398" t="n">
-        <v>0.01549172503345497</v>
+        <v>0.01564608858985816</v>
       </c>
     </row>
     <row r="399">
@@ -4821,10 +4821,10 @@
         <v>45603</v>
       </c>
       <c r="B399" t="n">
-        <v>22806.25</v>
+        <v>35903.63</v>
       </c>
       <c r="C399" t="n">
-        <v>-0.009767185383306121</v>
+        <v>-0.01013393546394936</v>
       </c>
     </row>
     <row r="400">
@@ -4832,10 +4832,10 @@
         <v>45604</v>
       </c>
       <c r="B400" t="n">
-        <v>22645.65</v>
+        <v>35663.87</v>
       </c>
       <c r="C400" t="n">
-        <v>-0.007041929295697358</v>
+        <v>-0.006677876303872177</v>
       </c>
     </row>
     <row r="401">
@@ -4843,10 +4843,10 @@
         <v>45607</v>
       </c>
       <c r="B401" t="n">
-        <v>22591.4</v>
+        <v>35580.38</v>
       </c>
       <c r="C401" t="n">
-        <v>-0.002395603570663707</v>
+        <v>-0.002341024684085147</v>
       </c>
     </row>
     <row r="402">
@@ -4854,10 +4854,10 @@
         <v>45608</v>
       </c>
       <c r="B402" t="n">
-        <v>22331.05</v>
+        <v>35161.57</v>
       </c>
       <c r="C402" t="n">
-        <v>-0.01152429685632594</v>
+        <v>-0.01177081301548766</v>
       </c>
     </row>
     <row r="403">
@@ -4865,10 +4865,10 @@
         <v>45609</v>
       </c>
       <c r="B403" t="n">
-        <v>21914.95</v>
+        <v>34533.58</v>
       </c>
       <c r="C403" t="n">
-        <v>-0.01863324832464208</v>
+        <v>-0.01786012399332559</v>
       </c>
     </row>
     <row r="404">
@@ -4876,10 +4876,10 @@
         <v>45610</v>
       </c>
       <c r="B404" t="n">
-        <v>21963.1</v>
+        <v>34600.01</v>
       </c>
       <c r="C404" t="n">
-        <v>0.002197130269519176</v>
+        <v>0.001923634908399308</v>
       </c>
     </row>
     <row r="405">
@@ -4887,10 +4887,10 @@
         <v>45614</v>
       </c>
       <c r="B405" t="n">
-        <v>21899.4</v>
+        <v>34497.01</v>
       </c>
       <c r="C405" t="n">
-        <v>-0.002900319171701526</v>
+        <v>-0.002976877752347451</v>
       </c>
     </row>
     <row r="406">
@@ -4898,10 +4898,10 @@
         <v>45615</v>
       </c>
       <c r="B406" t="n">
-        <v>22004.35</v>
+        <v>34650.83</v>
       </c>
       <c r="C406" t="n">
-        <v>0.004792368740695885</v>
+        <v>0.004458937165858767</v>
       </c>
     </row>
     <row r="407">
@@ -4909,10 +4909,10 @@
         <v>45617</v>
       </c>
       <c r="B407" t="n">
-        <v>21820.85</v>
+        <v>34361.41</v>
       </c>
       <c r="C407" t="n">
-        <v>-0.00833926019173481</v>
+        <v>-0.008352469479085967</v>
       </c>
     </row>
     <row r="408">
@@ -4920,10 +4920,10 @@
         <v>45618</v>
       </c>
       <c r="B408" t="n">
-        <v>22225.55</v>
+        <v>35009.77</v>
       </c>
       <c r="C408" t="n">
-        <v>0.01854648191981534</v>
+        <v>0.01886884152891266</v>
       </c>
     </row>
     <row r="409">
@@ -4931,10 +4931,10 @@
         <v>45621</v>
       </c>
       <c r="B409" t="n">
-        <v>22553.5</v>
+        <v>35528.25</v>
       </c>
       <c r="C409" t="n">
-        <v>0.01475554035783144</v>
+        <v>0.01480958029715707</v>
       </c>
     </row>
     <row r="410">
@@ -4942,10 +4942,10 @@
         <v>45622</v>
       </c>
       <c r="B410" t="n">
-        <v>22562.45</v>
+        <v>35530.27</v>
       </c>
       <c r="C410" t="n">
-        <v>0.0003968341942492959</v>
+        <v>5.685616375683544e-05</v>
       </c>
     </row>
     <row r="411">
@@ -4953,10 +4953,10 @@
         <v>45623</v>
       </c>
       <c r="B411" t="n">
-        <v>22691.7</v>
+        <v>35732.57</v>
       </c>
       <c r="C411" t="n">
-        <v>0.005728544550791304</v>
+        <v>0.005693736636394942</v>
       </c>
     </row>
     <row r="412">
@@ -4964,10 +4964,10 @@
         <v>45624</v>
       </c>
       <c r="B412" t="n">
-        <v>22514.35</v>
+        <v>35453.79</v>
       </c>
       <c r="C412" t="n">
-        <v>-0.007815633028816826</v>
+        <v>-0.007801845767041127</v>
       </c>
     </row>
     <row r="413">
@@ -4975,10 +4975,10 @@
         <v>45625</v>
       </c>
       <c r="B413" t="n">
-        <v>22687</v>
+        <v>35726.11</v>
       </c>
       <c r="C413" t="n">
-        <v>0.007668442571071354</v>
+        <v>0.007680984176867911</v>
       </c>
     </row>
     <row r="414">
@@ -4986,10 +4986,10 @@
         <v>45628</v>
       </c>
       <c r="B414" t="n">
-        <v>22835.85</v>
+        <v>35957.4</v>
       </c>
       <c r="C414" t="n">
-        <v>0.006561026138317105</v>
+        <v>0.006473976595828601</v>
       </c>
     </row>
     <row r="415">
@@ -4997,10 +4997,10 @@
         <v>45629</v>
       </c>
       <c r="B415" t="n">
-        <v>23020.85</v>
+        <v>36246.75</v>
       </c>
       <c r="C415" t="n">
-        <v>0.008101296864360119</v>
+        <v>0.008047022309733087</v>
       </c>
     </row>
     <row r="416">
@@ -5008,10 +5008,10 @@
         <v>45630</v>
       </c>
       <c r="B416" t="n">
-        <v>23099.5</v>
+        <v>36370.69</v>
       </c>
       <c r="C416" t="n">
-        <v>0.003416468114774363</v>
+        <v>0.003419341044369473</v>
       </c>
     </row>
     <row r="417">
@@ -5019,10 +5019,10 @@
         <v>45631</v>
       </c>
       <c r="B417" t="n">
-        <v>23277.95</v>
+        <v>36619.24</v>
       </c>
       <c r="C417" t="n">
-        <v>0.007725275438862367</v>
+        <v>0.006833799413758612</v>
       </c>
     </row>
     <row r="418">
@@ -5030,10 +5030,10 @@
         <v>45632</v>
       </c>
       <c r="B418" t="n">
-        <v>23312.1</v>
+        <v>36675.82</v>
       </c>
       <c r="C418" t="n">
-        <v>0.001467053585044953</v>
+        <v>0.001545089412014145</v>
       </c>
     </row>
     <row r="419">
@@ -5041,10 +5041,10 @@
         <v>45635</v>
       </c>
       <c r="B419" t="n">
-        <v>23292</v>
+        <v>36639.05</v>
       </c>
       <c r="C419" t="n">
-        <v>-0.0008622131854272297</v>
+        <v>-0.001002567904412111</v>
       </c>
     </row>
     <row r="420">
@@ -5052,10 +5052,10 @@
         <v>45636</v>
       </c>
       <c r="B420" t="n">
-        <v>23314.9</v>
+        <v>36675.82</v>
       </c>
       <c r="C420" t="n">
-        <v>0.0009831701871887422</v>
+        <v>0.00100357405554985</v>
       </c>
     </row>
     <row r="421">
@@ -5063,10 +5063,10 @@
         <v>45637</v>
       </c>
       <c r="B421" t="n">
-        <v>23358.15</v>
+        <v>36736.37</v>
       </c>
       <c r="C421" t="n">
-        <v>0.001855036907728591</v>
+        <v>0.001650951498834985</v>
       </c>
     </row>
     <row r="422">
@@ -5074,10 +5074,10 @@
         <v>45638</v>
       </c>
       <c r="B422" t="n">
-        <v>23256.4</v>
+        <v>36579.3</v>
       </c>
       <c r="C422" t="n">
-        <v>-0.00435608128212206</v>
+        <v>-0.004275599358347093</v>
       </c>
     </row>
     <row r="423">
@@ -5085,10 +5085,10 @@
         <v>45639</v>
       </c>
       <c r="B423" t="n">
-        <v>23358.95</v>
+        <v>36746.91</v>
       </c>
       <c r="C423" t="n">
-        <v>0.004409538879620145</v>
+        <v>0.004582099712132193</v>
       </c>
     </row>
     <row r="424">
@@ -5096,10 +5096,10 @@
         <v>45642</v>
       </c>
       <c r="B424" t="n">
-        <v>23352.45</v>
+        <v>36720.34</v>
       </c>
       <c r="C424" t="n">
-        <v>-0.0002782659323300463</v>
+        <v>-0.0007230539928393398</v>
       </c>
     </row>
     <row r="425">
@@ -5107,10 +5107,10 @@
         <v>45643</v>
       </c>
       <c r="B425" t="n">
-        <v>23095.75</v>
+        <v>36304.88</v>
       </c>
       <c r="C425" t="n">
-        <v>-0.01099242263659705</v>
+        <v>-0.01131416539171481</v>
       </c>
     </row>
     <row r="426">
@@ -5118,10 +5118,10 @@
         <v>45644</v>
       </c>
       <c r="B426" t="n">
-        <v>22934.4</v>
+        <v>36061.25</v>
       </c>
       <c r="C426" t="n">
-        <v>-0.006986133812497908</v>
+        <v>-0.006710668097511863</v>
       </c>
     </row>
     <row r="427">
@@ -5129,10 +5129,10 @@
         <v>45645</v>
       </c>
       <c r="B427" t="n">
-        <v>22752.15</v>
+        <v>35762.67</v>
       </c>
       <c r="C427" t="n">
-        <v>-0.007946578066136412</v>
+        <v>-0.008279801726229774</v>
       </c>
     </row>
     <row r="428">
@@ -5140,10 +5140,10 @@
         <v>45646</v>
       </c>
       <c r="B428" t="n">
-        <v>22319.4</v>
+        <v>35082.25</v>
       </c>
       <c r="C428" t="n">
-        <v>-0.01902018051041332</v>
+        <v>-0.01902598435743186</v>
       </c>
     </row>
     <row r="429">
@@ -5151,10 +5151,10 @@
         <v>45649</v>
       </c>
       <c r="B429" t="n">
-        <v>22412.3</v>
+        <v>35231.44</v>
       </c>
       <c r="C429" t="n">
-        <v>0.004162298269666742</v>
+        <v>0.004252577870575536</v>
       </c>
     </row>
     <row r="430">
@@ -5162,10 +5162,10 @@
         <v>45650</v>
       </c>
       <c r="B430" t="n">
-        <v>22402.7</v>
+        <v>35222.65</v>
       </c>
       <c r="C430" t="n">
-        <v>-0.0004283362260900647</v>
+        <v>-0.0002494930664201922</v>
       </c>
     </row>
     <row r="431">
@@ -5173,10 +5173,10 @@
         <v>45652</v>
       </c>
       <c r="B431" t="n">
-        <v>22430.35</v>
+        <v>35265.03</v>
       </c>
       <c r="C431" t="n">
-        <v>0.001234226231659585</v>
+        <v>0.001203203052581259</v>
       </c>
     </row>
     <row r="432">
@@ -5184,10 +5184,10 @@
         <v>45653</v>
       </c>
       <c r="B432" t="n">
-        <v>22445.2</v>
+        <v>35291.42</v>
       </c>
       <c r="C432" t="n">
-        <v>0.0006620494107314467</v>
+        <v>0.0007483334056428426</v>
       </c>
     </row>
     <row r="433">
@@ -5195,10 +5195,10 @@
         <v>45656</v>
       </c>
       <c r="B433" t="n">
-        <v>22357.15</v>
+        <v>35178.37</v>
       </c>
       <c r="C433" t="n">
-        <v>-0.003922887744372883</v>
+        <v>-0.003203328174383291</v>
       </c>
     </row>
     <row r="434">
@@ -5206,10 +5206,10 @@
         <v>45657</v>
       </c>
       <c r="B434" t="n">
-        <v>22375.4</v>
+        <v>35189.03</v>
       </c>
       <c r="C434" t="n">
-        <v>0.0008162936689157796</v>
+        <v>0.000303027115809984</v>
       </c>
     </row>
     <row r="435">
@@ -5217,10 +5217,10 @@
         <v>45658</v>
       </c>
       <c r="B435" t="n">
-        <v>22481.8</v>
+        <v>35352.14</v>
       </c>
       <c r="C435" t="n">
-        <v>0.004755222253009839</v>
+        <v>0.004635251383740879</v>
       </c>
     </row>
     <row r="436">
@@ -5228,10 +5228,10 @@
         <v>45659</v>
       </c>
       <c r="B436" t="n">
-        <v>22819.75</v>
+        <v>35878.66</v>
       </c>
       <c r="C436" t="n">
-        <v>0.01503215934667157</v>
+        <v>0.01489358211412384</v>
       </c>
     </row>
     <row r="437">
@@ -5239,10 +5239,10 @@
         <v>45660</v>
       </c>
       <c r="B437" t="n">
-        <v>22708.15</v>
+        <v>35702.07</v>
       </c>
       <c r="C437" t="n">
-        <v>-0.0048905005532488</v>
+        <v>-0.004921867204628172</v>
       </c>
     </row>
     <row r="438">
@@ -5250,10 +5250,10 @@
         <v>45663</v>
       </c>
       <c r="B438" t="n">
-        <v>22225.4</v>
+        <v>34951.07</v>
       </c>
       <c r="C438" t="n">
-        <v>-0.02125888722771341</v>
+        <v>-0.02103519487805605</v>
       </c>
     </row>
     <row r="439">
@@ -5261,10 +5261,10 @@
         <v>45664</v>
       </c>
       <c r="B439" t="n">
-        <v>22341.65</v>
+        <v>35135.64</v>
       </c>
       <c r="C439" t="n">
-        <v>0.005230502038208629</v>
+        <v>0.005280811145409903</v>
       </c>
     </row>
     <row r="440">
@@ -5272,10 +5272,10 @@
         <v>45665</v>
       </c>
       <c r="B440" t="n">
-        <v>22231.8</v>
+        <v>34958.85</v>
       </c>
       <c r="C440" t="n">
-        <v>-0.004916825749217368</v>
+        <v>-0.005031643083774795</v>
       </c>
     </row>
     <row r="441">
@@ -5283,10 +5283,10 @@
         <v>45666</v>
       </c>
       <c r="B441" t="n">
-        <v>22046.55</v>
+        <v>34678.2</v>
       </c>
       <c r="C441" t="n">
-        <v>-0.008332658624133016</v>
+        <v>-0.008028010074702108</v>
       </c>
     </row>
     <row r="442">
@@ -5294,10 +5294,10 @@
         <v>45667</v>
       </c>
       <c r="B442" t="n">
-        <v>21799</v>
+        <v>34287.66</v>
       </c>
       <c r="C442" t="n">
-        <v>-0.01122851421197413</v>
+        <v>-0.01126183019879912</v>
       </c>
     </row>
     <row r="443">
@@ -5305,10 +5305,10 @@
         <v>45670</v>
       </c>
       <c r="B443" t="n">
-        <v>21243.45</v>
+        <v>33413.46</v>
       </c>
       <c r="C443" t="n">
-        <v>-0.0254851139960548</v>
+        <v>-0.02549605309898673</v>
       </c>
     </row>
     <row r="444">
@@ -5316,10 +5316,10 @@
         <v>45671</v>
       </c>
       <c r="B444" t="n">
-        <v>21481.05</v>
+        <v>33776.55</v>
       </c>
       <c r="C444" t="n">
-        <v>0.01118462396644615</v>
+        <v>0.0108665789175979</v>
       </c>
     </row>
     <row r="445">
@@ -5327,10 +5327,10 @@
         <v>45672</v>
       </c>
       <c r="B445" t="n">
-        <v>21551.2</v>
+        <v>33877.55</v>
       </c>
       <c r="C445" t="n">
-        <v>0.003265669043180042</v>
+        <v>0.002990240270246636</v>
       </c>
     </row>
     <row r="446">
@@ -5338,10 +5338,10 @@
         <v>45673</v>
       </c>
       <c r="B446" t="n">
-        <v>21714.55</v>
+        <v>34136.78</v>
       </c>
       <c r="C446" t="n">
-        <v>0.007579624336463864</v>
+        <v>0.007651970109999073</v>
       </c>
     </row>
     <row r="447">
@@ -5349,10 +5349,10 @@
         <v>45674</v>
       </c>
       <c r="B447" t="n">
-        <v>21680.25</v>
+        <v>34083.34</v>
       </c>
       <c r="C447" t="n">
-        <v>-0.001579586037933067</v>
+        <v>-0.0015654669245313</v>
       </c>
     </row>
     <row r="448">
@@ -5360,10 +5360,10 @@
         <v>45677</v>
       </c>
       <c r="B448" t="n">
-        <v>21809</v>
+        <v>34279.07</v>
       </c>
       <c r="C448" t="n">
-        <v>0.00593858465654229</v>
+        <v>0.005742688363288506</v>
       </c>
     </row>
     <row r="449">
@@ -5371,10 +5371,10 @@
         <v>45678</v>
       </c>
       <c r="B449" t="n">
-        <v>21433.2</v>
+        <v>33693.47</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.01723141822183494</v>
+        <v>-0.01708331060323398</v>
       </c>
     </row>
     <row r="450">
@@ -5382,10 +5382,10 @@
         <v>45679</v>
       </c>
       <c r="B450" t="n">
-        <v>21396.55</v>
+        <v>33650.82</v>
       </c>
       <c r="C450" t="n">
-        <v>-0.001709963981113449</v>
+        <v>-0.001265823911873798</v>
       </c>
     </row>
     <row r="451">
@@ -5393,10 +5393,10 @@
         <v>45680</v>
       </c>
       <c r="B451" t="n">
-        <v>21538.05</v>
+        <v>33870.03</v>
       </c>
       <c r="C451" t="n">
-        <v>0.006613215681967377</v>
+        <v>0.006514254333178204</v>
       </c>
     </row>
     <row r="452">
@@ -5404,10 +5404,10 @@
         <v>45681</v>
       </c>
       <c r="B452" t="n">
-        <v>21318.9</v>
+        <v>33525.19</v>
       </c>
       <c r="C452" t="n">
-        <v>-0.01017501584405267</v>
+        <v>-0.01018127235198774</v>
       </c>
     </row>
     <row r="453">
@@ -5415,10 +5415,10 @@
         <v>45684</v>
       </c>
       <c r="B453" t="n">
-        <v>20910.95</v>
+        <v>32903.27</v>
       </c>
       <c r="C453" t="n">
-        <v>-0.01913560268118908</v>
+        <v>-0.01855082700500743</v>
       </c>
     </row>
     <row r="454">
@@ -5426,10 +5426,10 @@
         <v>45685</v>
       </c>
       <c r="B454" t="n">
-        <v>20924.75</v>
+        <v>32930.85</v>
       </c>
       <c r="C454" t="n">
-        <v>0.0006599413226084927</v>
+        <v>0.0008382145604373115</v>
       </c>
     </row>
     <row r="455">
@@ -5437,10 +5437,10 @@
         <v>45686</v>
       </c>
       <c r="B455" t="n">
-        <v>21245.5</v>
+        <v>33434.59</v>
       </c>
       <c r="C455" t="n">
-        <v>0.01532873749985075</v>
+        <v>0.01529690244861581</v>
       </c>
     </row>
     <row r="456">
@@ -5448,10 +5448,10 @@
         <v>45687</v>
       </c>
       <c r="B456" t="n">
-        <v>21297.5</v>
+        <v>33520.73</v>
       </c>
       <c r="C456" t="n">
-        <v>0.00244757713398136</v>
+        <v>0.002576373749461514</v>
       </c>
     </row>
     <row r="457">
@@ -5459,10 +5459,10 @@
         <v>45688</v>
       </c>
       <c r="B457" t="n">
-        <v>21580.9</v>
+        <v>33962.66</v>
       </c>
       <c r="C457" t="n">
-        <v>0.01330672614156603</v>
+        <v>0.01318378209543769</v>
       </c>
     </row>
     <row r="458">
@@ -5470,10 +5470,10 @@
         <v>45689</v>
       </c>
       <c r="B458" t="n">
-        <v>21577.15</v>
+        <v>33953.6</v>
       </c>
       <c r="C458" t="n">
-        <v>-0.0001737647642128248</v>
+        <v>-0.0002667635573893046</v>
       </c>
     </row>
     <row r="459">
@@ -5481,10 +5481,10 @@
         <v>45691</v>
       </c>
       <c r="B459" t="n">
-        <v>21402.55</v>
+        <v>33685.04</v>
       </c>
       <c r="C459" t="n">
-        <v>-0.008091893507715442</v>
+        <v>-0.007909617831393323</v>
       </c>
     </row>
     <row r="460">
@@ -5492,10 +5492,10 @@
         <v>45692</v>
       </c>
       <c r="B460" t="n">
-        <v>21727.45</v>
+        <v>34197.57</v>
       </c>
       <c r="C460" t="n">
-        <v>0.01518043410715086</v>
+        <v>0.01521535969676746</v>
       </c>
     </row>
     <row r="461">
@@ -5503,10 +5503,10 @@
         <v>45693</v>
       </c>
       <c r="B461" t="n">
-        <v>21784.25</v>
+        <v>34267.23</v>
       </c>
       <c r="C461" t="n">
-        <v>0.002614204612138016</v>
+        <v>0.00203698683853859</v>
       </c>
     </row>
     <row r="462">
@@ -5514,10 +5514,10 @@
         <v>45694</v>
       </c>
       <c r="B462" t="n">
-        <v>21672.45</v>
+        <v>34100.23</v>
       </c>
       <c r="C462" t="n">
-        <v>-0.005132148226356215</v>
+        <v>-0.004873460737853663</v>
       </c>
     </row>
     <row r="463">
@@ -5525,10 +5525,10 @@
         <v>45695</v>
       </c>
       <c r="B463" t="n">
-        <v>21646.15</v>
+        <v>34049.02</v>
       </c>
       <c r="C463" t="n">
-        <v>-0.001213522236756748</v>
+        <v>-0.001501749401690455</v>
       </c>
     </row>
     <row r="464">
@@ -5536,10 +5536,10 @@
         <v>45698</v>
       </c>
       <c r="B464" t="n">
-        <v>21371.3</v>
+        <v>33615.47</v>
       </c>
       <c r="C464" t="n">
-        <v>-0.01269740808411668</v>
+        <v>-0.01273311243612874</v>
       </c>
     </row>
     <row r="465">
@@ -5547,10 +5547,10 @@
         <v>45699</v>
       </c>
       <c r="B465" t="n">
-        <v>20950.45</v>
+        <v>32969.92</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.01969229761408986</v>
+        <v>-0.01920395579773249</v>
       </c>
     </row>
     <row r="466">
@@ -5558,10 +5558,10 @@
         <v>45700</v>
       </c>
       <c r="B466" t="n">
-        <v>20907.85</v>
+        <v>32902.92</v>
       </c>
       <c r="C466" t="n">
-        <v>-0.00203336921163999</v>
+        <v>-0.002032155370713662</v>
       </c>
     </row>
     <row r="467">
@@ -5569,10 +5569,10 @@
         <v>45701</v>
       </c>
       <c r="B467" t="n">
-        <v>20904.35</v>
+        <v>32894.16</v>
       </c>
       <c r="C467" t="n">
-        <v>-0.0001674012392474111</v>
+        <v>-0.0002662377685626049</v>
       </c>
     </row>
     <row r="468">
@@ -5580,10 +5580,10 @@
         <v>45702</v>
       </c>
       <c r="B468" t="n">
-        <v>20633.1</v>
+        <v>32465.88</v>
       </c>
       <c r="C468" t="n">
-        <v>-0.01297576820135526</v>
+        <v>-0.01301994031767351</v>
       </c>
     </row>
     <row r="469">
@@ -5591,10 +5591,10 @@
         <v>45705</v>
       </c>
       <c r="B469" t="n">
-        <v>20652.35</v>
+        <v>32504.98</v>
       </c>
       <c r="C469" t="n">
-        <v>0.0009329669317745815</v>
+        <v>0.001204341296154654</v>
       </c>
     </row>
     <row r="470">
@@ -5602,10 +5602,10 @@
         <v>45706</v>
       </c>
       <c r="B470" t="n">
-        <v>20611.4</v>
+        <v>32433.14</v>
       </c>
       <c r="C470" t="n">
-        <v>-0.001982825199069227</v>
+        <v>-0.002210122879632626</v>
       </c>
     </row>
     <row r="471">
@@ -5613,10 +5613,10 @@
         <v>45707</v>
       </c>
       <c r="B471" t="n">
-        <v>20731.45</v>
+        <v>32607.77</v>
       </c>
       <c r="C471" t="n">
-        <v>0.005824446665437577</v>
+        <v>0.005384307532357413</v>
       </c>
     </row>
     <row r="472">
@@ -5624,10 +5624,10 @@
         <v>45708</v>
       </c>
       <c r="B472" t="n">
-        <v>20831.1</v>
+        <v>32757.57</v>
       </c>
       <c r="C472" t="n">
-        <v>0.004806706718536224</v>
+        <v>0.004593997074930245</v>
       </c>
     </row>
     <row r="473">
@@ -5635,10 +5635,10 @@
         <v>45709</v>
       </c>
       <c r="B473" t="n">
-        <v>20690.25</v>
+        <v>32535.94</v>
       </c>
       <c r="C473" t="n">
-        <v>-0.006761524835462329</v>
+        <v>-0.006765764371410965</v>
       </c>
     </row>
     <row r="474">
@@ -5646,10 +5646,10 @@
         <v>45712</v>
       </c>
       <c r="B474" t="n">
-        <v>20468.45</v>
+        <v>32193.81</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.01072002513261072</v>
+        <v>-0.01051544845484709</v>
       </c>
     </row>
     <row r="475">
@@ -5657,10 +5657,10 @@
         <v>45713</v>
       </c>
       <c r="B475" t="n">
-        <v>20418.75</v>
+        <v>32122.71</v>
       </c>
       <c r="C475" t="n">
-        <v>-0.00242812719087182</v>
+        <v>-0.002208499087246962</v>
       </c>
     </row>
     <row r="476">
@@ -5668,10 +5668,10 @@
         <v>45715</v>
       </c>
       <c r="B476" t="n">
-        <v>20315.55</v>
+        <v>31964.79</v>
       </c>
       <c r="C476" t="n">
-        <v>-0.00505417814508724</v>
+        <v>-0.004916148108300877</v>
       </c>
     </row>
     <row r="477">
@@ -5679,10 +5679,10 @@
         <v>45716</v>
       </c>
       <c r="B477" t="n">
-        <v>19880.9</v>
+        <v>31296.85</v>
       </c>
       <c r="C477" t="n">
-        <v>-0.02139494131342734</v>
+        <v>-0.02089611725902163</v>
       </c>
     </row>
     <row r="478">
@@ -5690,10 +5690,10 @@
         <v>45719</v>
       </c>
       <c r="B478" t="n">
-        <v>19896.95</v>
+        <v>31335.96</v>
       </c>
       <c r="C478" t="n">
-        <v>0.0008073075162593479</v>
+        <v>0.001249646529922321</v>
       </c>
     </row>
     <row r="479">
@@ -5701,10 +5701,10 @@
         <v>45720</v>
       </c>
       <c r="B479" t="n">
-        <v>19917.85</v>
+        <v>31369.65</v>
       </c>
       <c r="C479" t="n">
-        <v>0.001050412249113508</v>
+        <v>0.00107512263865539</v>
       </c>
     </row>
     <row r="480">
@@ -5712,10 +5712,10 @@
         <v>45721</v>
       </c>
       <c r="B480" t="n">
-        <v>20256.5</v>
+        <v>31906.57</v>
       </c>
       <c r="C480" t="n">
-        <v>0.01700233709963683</v>
+        <v>0.01711590661674567</v>
       </c>
     </row>
     <row r="481">
@@ -5723,10 +5723,10 @@
         <v>45722</v>
       </c>
       <c r="B481" t="n">
-        <v>20447.1</v>
+        <v>32200.42</v>
       </c>
       <c r="C481" t="n">
-        <v>0.009409325401722901</v>
+        <v>0.009209701951667038</v>
       </c>
     </row>
     <row r="482">
@@ -5734,10 +5734,10 @@
         <v>45723</v>
       </c>
       <c r="B482" t="n">
-        <v>20443.4</v>
+        <v>32198.93</v>
       </c>
       <c r="C482" t="n">
-        <v>-0.0001809547564201042</v>
+        <v>-4.62726883685427e-05</v>
       </c>
     </row>
     <row r="483">
@@ -5745,10 +5745,10 @@
         <v>45726</v>
       </c>
       <c r="B483" t="n">
-        <v>20266.5</v>
+        <v>31922.79</v>
       </c>
       <c r="C483" t="n">
-        <v>-0.008653159454885317</v>
+        <v>-0.008576061378437139</v>
       </c>
     </row>
     <row r="484">
@@ -5756,10 +5756,10 @@
         <v>45727</v>
       </c>
       <c r="B484" t="n">
-        <v>20302.5</v>
+        <v>31991.6</v>
       </c>
       <c r="C484" t="n">
-        <v>0.00177633039745384</v>
+        <v>0.002155513349553662</v>
       </c>
     </row>
     <row r="485">
@@ -5767,10 +5767,10 @@
         <v>45728</v>
       </c>
       <c r="B485" t="n">
-        <v>20264.35</v>
+        <v>31919.62</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.001879078931166234</v>
+        <v>-0.002249965615974125</v>
       </c>
     </row>
     <row r="486">
@@ -5778,10 +5778,10 @@
         <v>45729</v>
       </c>
       <c r="B486" t="n">
-        <v>20176.05</v>
+        <v>31785.9</v>
       </c>
       <c r="C486" t="n">
-        <v>-0.004357405986375018</v>
+        <v>-0.004189272929940868</v>
       </c>
     </row>
     <row r="487">
@@ -5789,10 +5789,10 @@
         <v>45733</v>
       </c>
       <c r="B487" t="n">
-        <v>20288.3</v>
+        <v>31966.21</v>
       </c>
       <c r="C487" t="n">
-        <v>0.005563527053114914</v>
+        <v>0.005672641013782842</v>
       </c>
     </row>
     <row r="488">
@@ -5800,10 +5800,10 @@
         <v>45734</v>
       </c>
       <c r="B488" t="n">
-        <v>20657.2</v>
+        <v>32543.43</v>
       </c>
       <c r="C488" t="n">
-        <v>0.01818289358891589</v>
+        <v>0.01805719226645897</v>
       </c>
     </row>
     <row r="489">
@@ -5811,10 +5811,10 @@
         <v>45735</v>
       </c>
       <c r="B489" t="n">
-        <v>20864.5</v>
+        <v>32852.82</v>
       </c>
       <c r="C489" t="n">
-        <v>0.0100352419495382</v>
+        <v>0.009506988046435128</v>
       </c>
     </row>
     <row r="490">
@@ -5822,10 +5822,10 @@
         <v>45736</v>
       </c>
       <c r="B490" t="n">
-        <v>21070.05</v>
+        <v>33171.19</v>
       </c>
       <c r="C490" t="n">
-        <v>0.009851661913776955</v>
+        <v>0.009690796710906557</v>
       </c>
     </row>
     <row r="491">
@@ -5833,10 +5833,10 @@
         <v>45737</v>
       </c>
       <c r="B491" t="n">
-        <v>21273.9</v>
+        <v>33487.78</v>
       </c>
       <c r="C491" t="n">
-        <v>0.009674870254223533</v>
+        <v>0.009544125489619137</v>
       </c>
     </row>
     <row r="492">
@@ -5844,10 +5844,10 @@
         <v>45740</v>
       </c>
       <c r="B492" t="n">
-        <v>21538.1</v>
+        <v>33913.46</v>
       </c>
       <c r="C492" t="n">
-        <v>0.01241897348394039</v>
+        <v>0.01271150252420439</v>
       </c>
     </row>
     <row r="493">
@@ -5855,10 +5855,10 @@
         <v>45741</v>
       </c>
       <c r="B493" t="n">
-        <v>21437.75</v>
+        <v>33761.03</v>
       </c>
       <c r="C493" t="n">
-        <v>-0.004659185350611161</v>
+        <v>-0.004494675565394957</v>
       </c>
     </row>
     <row r="494">
@@ -5866,10 +5866,10 @@
         <v>45742</v>
       </c>
       <c r="B494" t="n">
-        <v>21275.45</v>
+        <v>33495.53</v>
       </c>
       <c r="C494" t="n">
-        <v>-0.007570757192335908</v>
+        <v>-0.007864096563404588</v>
       </c>
     </row>
     <row r="495">
@@ -5877,10 +5877,10 @@
         <v>45743</v>
       </c>
       <c r="B495" t="n">
-        <v>21407.95</v>
+        <v>33711.61</v>
       </c>
       <c r="C495" t="n">
-        <v>0.006227835368934675</v>
+        <v>0.006451010030293691</v>
       </c>
     </row>
     <row r="496">
@@ -5888,10 +5888,10 @@
         <v>45744</v>
       </c>
       <c r="B496" t="n">
-        <v>21339.55</v>
+        <v>33579.22</v>
       </c>
       <c r="C496" t="n">
-        <v>-0.003195074726912273</v>
+        <v>-0.003927133708535369</v>
       </c>
     </row>
     <row r="497">
@@ -5899,10 +5899,10 @@
         <v>45748</v>
       </c>
       <c r="B497" t="n">
-        <v>21070.75</v>
+        <v>33153.99</v>
       </c>
       <c r="C497" t="n">
-        <v>-0.01259632935090005</v>
+        <v>-0.01266348652529758</v>
       </c>
     </row>
     <row r="498">
@@ -5910,10 +5910,10 @@
         <v>45749</v>
       </c>
       <c r="B498" t="n">
-        <v>21265.65</v>
+        <v>33459.65</v>
       </c>
       <c r="C498" t="n">
-        <v>0.009249789399997654</v>
+        <v>0.009219403154793859</v>
       </c>
     </row>
     <row r="499">
@@ -5921,10 +5921,10 @@
         <v>45750</v>
       </c>
       <c r="B499" t="n">
-        <v>21243.4</v>
+        <v>33420.86</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.001046288262996908</v>
+        <v>-0.001159306806855498</v>
       </c>
     </row>
     <row r="500">
@@ -5932,10 +5932,10 @@
         <v>45751</v>
       </c>
       <c r="B500" t="n">
-        <v>20805.35</v>
+        <v>32739.88</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.02062052213864085</v>
+        <v>-0.02037589696973685</v>
       </c>
     </row>
     <row r="501">
@@ -5943,10 +5943,10 @@
         <v>45754</v>
       </c>
       <c r="B501" t="n">
-        <v>20105.7</v>
+        <v>31664.36</v>
       </c>
       <c r="C501" t="n">
-        <v>-0.03362836962608162</v>
+        <v>-0.03285045638530137</v>
       </c>
     </row>
     <row r="502">
@@ -5954,10 +5954,10 @@
         <v>45755</v>
       </c>
       <c r="B502" t="n">
-        <v>20480.8</v>
+        <v>32233.7</v>
       </c>
       <c r="C502" t="n">
-        <v>0.01865640092113185</v>
+        <v>0.01798046762985273</v>
       </c>
     </row>
     <row r="503">
@@ -5965,10 +5965,10 @@
         <v>45756</v>
       </c>
       <c r="B503" t="n">
-        <v>20356.75</v>
+        <v>32044.58</v>
       </c>
       <c r="C503" t="n">
-        <v>-0.006056892308894168</v>
+        <v>-0.005867151459497344</v>
       </c>
     </row>
     <row r="504">
@@ -5976,10 +5976,10 @@
         <v>45758</v>
       </c>
       <c r="B504" t="n">
-        <v>20752.85</v>
+        <v>32666.11</v>
       </c>
       <c r="C504" t="n">
-        <v>0.01945791936335617</v>
+        <v>0.0193957917376355</v>
       </c>
     </row>
     <row r="505">
@@ -5987,10 +5987,10 @@
         <v>45762</v>
       </c>
       <c r="B505" t="n">
-        <v>21279.4</v>
+        <v>33482.62</v>
       </c>
       <c r="C505" t="n">
-        <v>0.0253724187280302</v>
+        <v>0.02499563002757288</v>
       </c>
     </row>
     <row r="506">
@@ -5998,10 +5998,10 @@
         <v>45763</v>
       </c>
       <c r="B506" t="n">
-        <v>21404.35</v>
+        <v>33670.31</v>
       </c>
       <c r="C506" t="n">
-        <v>0.005871876086731564</v>
+        <v>0.005605594783203882</v>
       </c>
     </row>
     <row r="507">
@@ -6009,10 +6009,10 @@
         <v>45764</v>
       </c>
       <c r="B507" t="n">
-        <v>21681.55</v>
+        <v>34109.67</v>
       </c>
       <c r="C507" t="n">
-        <v>0.01295063853842793</v>
+        <v>0.01304888490780165</v>
       </c>
     </row>
     <row r="508">
@@ -6020,10 +6020,10 @@
         <v>45768</v>
       </c>
       <c r="B508" t="n">
-        <v>22005.75</v>
+        <v>34609.7</v>
       </c>
       <c r="C508" t="n">
-        <v>0.01495280549591715</v>
+        <v>0.01465947926203914</v>
       </c>
     </row>
     <row r="509">
@@ -6031,10 +6031,10 @@
         <v>45769</v>
       </c>
       <c r="B509" t="n">
-        <v>22085.15</v>
+        <v>34730.29</v>
       </c>
       <c r="C509" t="n">
-        <v>0.003608147870443057</v>
+        <v>0.003484283307858993</v>
       </c>
     </row>
     <row r="510">
@@ -6042,10 +6042,10 @@
         <v>45770</v>
       </c>
       <c r="B510" t="n">
-        <v>22237.6</v>
+        <v>34962.78</v>
       </c>
       <c r="C510" t="n">
-        <v>0.006902828371099901</v>
+        <v>0.006694156599325707</v>
       </c>
     </row>
     <row r="511">
@@ -6053,10 +6053,10 @@
         <v>45771</v>
       </c>
       <c r="B511" t="n">
-        <v>22180.65</v>
+        <v>34880.67</v>
       </c>
       <c r="C511" t="n">
-        <v>-0.002560977803359954</v>
+        <v>-0.002348497459298216</v>
       </c>
     </row>
     <row r="512">
@@ -6064,10 +6064,10 @@
         <v>45772</v>
       </c>
       <c r="B512" t="n">
-        <v>21848.15</v>
+        <v>34359.02</v>
       </c>
       <c r="C512" t="n">
-        <v>-0.01499054355936369</v>
+        <v>-0.01495527465498803</v>
       </c>
     </row>
     <row r="513">
@@ -6075,10 +6075,10 @@
         <v>45775</v>
       </c>
       <c r="B513" t="n">
-        <v>22101.85</v>
+        <v>34765.79</v>
       </c>
       <c r="C513" t="n">
-        <v>0.01161196714595958</v>
+        <v>0.01183881263202524</v>
       </c>
     </row>
     <row r="514">
@@ -6086,10 +6086,10 @@
         <v>45776</v>
       </c>
       <c r="B514" t="n">
-        <v>22112.4</v>
+        <v>34785.55</v>
       </c>
       <c r="C514" t="n">
-        <v>0.0004773356076528401</v>
+        <v>0.0005683748305447267</v>
       </c>
     </row>
     <row r="515">
@@ -6097,10 +6097,10 @@
         <v>45777</v>
       </c>
       <c r="B515" t="n">
-        <v>22030.05</v>
+        <v>34640.35</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.003724154772887678</v>
+        <v>-0.004174147023692454</v>
       </c>
     </row>
     <row r="516">
@@ -6108,10 +6108,10 @@
         <v>45779</v>
       </c>
       <c r="B516" t="n">
-        <v>22006</v>
+        <v>34623.5</v>
       </c>
       <c r="C516" t="n">
-        <v>-0.001091690667973988</v>
+        <v>-0.000486426955847663</v>
       </c>
     </row>
     <row r="517">
@@ -6119,10 +6119,10 @@
         <v>45782</v>
       </c>
       <c r="B517" t="n">
-        <v>22195.15</v>
+        <v>34918.71</v>
       </c>
       <c r="C517" t="n">
-        <v>0.008595383077342644</v>
+        <v>0.008526289947578869</v>
       </c>
     </row>
     <row r="518">
@@ -6130,10 +6130,10 @@
         <v>45783</v>
       </c>
       <c r="B518" t="n">
-        <v>21956.6</v>
+        <v>34548.63</v>
       </c>
       <c r="C518" t="n">
-        <v>-0.01074784356041758</v>
+        <v>-0.01059832966338103</v>
       </c>
     </row>
     <row r="519">
@@ -6141,10 +6141,10 @@
         <v>45784</v>
       </c>
       <c r="B519" t="n">
-        <v>22072.45</v>
+        <v>34722.2</v>
       </c>
       <c r="C519" t="n">
-        <v>0.005276317826986121</v>
+        <v>0.005023932931638608</v>
       </c>
     </row>
     <row r="520">
@@ -6152,10 +6152,10 @@
         <v>45785</v>
       </c>
       <c r="B520" t="n">
-        <v>21843.05</v>
+        <v>34339.7</v>
       </c>
       <c r="C520" t="n">
-        <v>-0.01039304653538697</v>
+        <v>-0.01101600705024453</v>
       </c>
     </row>
     <row r="521">
@@ -6163,10 +6163,10 @@
         <v>45786</v>
       </c>
       <c r="B521" t="n">
-        <v>21675.55</v>
+        <v>34105.3</v>
       </c>
       <c r="C521" t="n">
-        <v>-0.007668343019862189</v>
+        <v>-0.006825918688864285</v>
       </c>
     </row>
     <row r="522">
@@ -6174,10 +6174,10 @@
         <v>45789</v>
       </c>
       <c r="B522" t="n">
-        <v>22511.4</v>
+        <v>35412.4</v>
       </c>
       <c r="C522" t="n">
-        <v>0.03856188193609866</v>
+        <v>0.03832542156204455</v>
       </c>
     </row>
     <row r="523">
@@ -6185,10 +6185,10 @@
         <v>45790</v>
       </c>
       <c r="B523" t="n">
-        <v>22349.4</v>
+        <v>35144.23</v>
       </c>
       <c r="C523" t="n">
-        <v>-0.00719635384738404</v>
+        <v>-0.007572771119720767</v>
       </c>
     </row>
     <row r="524">
@@ -6196,10 +6196,10 @@
         <v>45791</v>
       </c>
       <c r="B524" t="n">
-        <v>22499.5</v>
+        <v>35374.47</v>
       </c>
       <c r="C524" t="n">
-        <v>0.006716063965922947</v>
+        <v>0.006551288789084175</v>
       </c>
     </row>
     <row r="525">
@@ -6207,10 +6207,10 @@
         <v>45792</v>
       </c>
       <c r="B525" t="n">
-        <v>22773.9</v>
+        <v>35836.63</v>
       </c>
       <c r="C525" t="n">
-        <v>0.01219582657392393</v>
+        <v>0.01306478938058997</v>
       </c>
     </row>
     <row r="526">
@@ -6218,10 +6218,10 @@
         <v>45793</v>
       </c>
       <c r="B526" t="n">
-        <v>22870.9</v>
+        <v>35957.63</v>
       </c>
       <c r="C526" t="n">
-        <v>0.004259261698698946</v>
+        <v>0.003376433554159508</v>
       </c>
     </row>
     <row r="527">
@@ -6229,10 +6229,10 @@
         <v>45796</v>
       </c>
       <c r="B527" t="n">
-        <v>22861.2</v>
+        <v>35953.27</v>
       </c>
       <c r="C527" t="n">
-        <v>-0.0004241197329357682</v>
+        <v>-0.00012125382012107</v>
       </c>
     </row>
     <row r="528">
@@ -6240,10 +6240,10 @@
         <v>45797</v>
       </c>
       <c r="B528" t="n">
-        <v>22585.6</v>
+        <v>35513.57</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.01205536017356934</v>
+        <v>-0.01222976380173479</v>
       </c>
     </row>
     <row r="529">
@@ -6251,10 +6251,10 @@
         <v>45798</v>
       </c>
       <c r="B529" t="n">
-        <v>22730.65</v>
+        <v>35742.34</v>
       </c>
       <c r="C529" t="n">
-        <v>0.006422233635591024</v>
+        <v>0.006441762965536668</v>
       </c>
     </row>
     <row r="530">
@@ -6262,10 +6262,10 @@
         <v>45799</v>
       </c>
       <c r="B530" t="n">
-        <v>22595</v>
+        <v>35542.53</v>
       </c>
       <c r="C530" t="n">
-        <v>-0.005967713197818858</v>
+        <v>-0.005590288716407432</v>
       </c>
     </row>
     <row r="531">
@@ -6273,10 +6273,10 @@
         <v>45800</v>
       </c>
       <c r="B531" t="n">
-        <v>22781.05</v>
+        <v>35813.43</v>
       </c>
       <c r="C531" t="n">
-        <v>0.008234122593494098</v>
+        <v>0.007621854718839804</v>
       </c>
     </row>
     <row r="532">
@@ -6284,10 +6284,10 @@
         <v>45803</v>
       </c>
       <c r="B532" t="n">
-        <v>22908.3</v>
+        <v>36008.3</v>
       </c>
       <c r="C532" t="n">
-        <v>0.00558578292045353</v>
+        <v>0.005441254858861599</v>
       </c>
     </row>
     <row r="533">
@@ -6295,10 +6295,10 @@
         <v>45804</v>
       </c>
       <c r="B533" t="n">
-        <v>22816.5</v>
+        <v>35874.97</v>
       </c>
       <c r="C533" t="n">
-        <v>-0.004007281203755819</v>
+        <v>-0.003702757419817182</v>
       </c>
     </row>
     <row r="534">
@@ -6306,10 +6306,10 @@
         <v>45805</v>
       </c>
       <c r="B534" t="n">
-        <v>22779.4</v>
+        <v>35804.71</v>
       </c>
       <c r="C534" t="n">
-        <v>-0.001626016260162566</v>
+        <v>-0.001958468536698454</v>
       </c>
     </row>
     <row r="535">
@@ -6317,10 +6317,10 @@
         <v>45806</v>
       </c>
       <c r="B535" t="n">
-        <v>22861.35</v>
+        <v>35933.41</v>
       </c>
       <c r="C535" t="n">
-        <v>0.003597548662387817</v>
+        <v>0.003594499159468301</v>
       </c>
     </row>
     <row r="536">
@@ -6328,10 +6328,10 @@
         <v>45807</v>
       </c>
       <c r="B536" t="n">
-        <v>22801.95</v>
+        <v>35815.16</v>
       </c>
       <c r="C536" t="n">
-        <v>-0.002598271755604897</v>
+        <v>-0.003290809305323328</v>
       </c>
     </row>
     <row r="537">
@@ -6339,10 +6339,10 @@
         <v>45810</v>
       </c>
       <c r="B537" t="n">
-        <v>22834.5</v>
+        <v>35857.9</v>
       </c>
       <c r="C537" t="n">
-        <v>0.001427509489319911</v>
+        <v>0.001193349408462829</v>
       </c>
     </row>
     <row r="538">
@@ -6350,10 +6350,10 @@
         <v>45811</v>
       </c>
       <c r="B538" t="n">
-        <v>22711.3</v>
+        <v>35647.66</v>
       </c>
       <c r="C538" t="n">
-        <v>-0.005395344763406307</v>
+        <v>-0.005863143128850168</v>
       </c>
     </row>
     <row r="539">
@@ -6361,10 +6361,10 @@
         <v>45812</v>
       </c>
       <c r="B539" t="n">
-        <v>22807.85</v>
+        <v>35791.49</v>
       </c>
       <c r="C539" t="n">
-        <v>0.004251187734739981</v>
+        <v>0.004034766938418866</v>
       </c>
     </row>
     <row r="540">
@@ -6372,10 +6372,10 @@
         <v>45813</v>
       </c>
       <c r="B540" t="n">
-        <v>22934.5</v>
+        <v>35984.22</v>
       </c>
       <c r="C540" t="n">
-        <v>0.005552912703301827</v>
+        <v>0.005384799571071408</v>
       </c>
     </row>
     <row r="541">
@@ -6383,10 +6383,10 @@
         <v>45814</v>
       </c>
       <c r="B541" t="n">
-        <v>23165.1</v>
+        <v>36338.97</v>
       </c>
       <c r="C541" t="n">
-        <v>0.01005472105343475</v>
+        <v>0.009858487970560326</v>
       </c>
     </row>
     <row r="542">
@@ -6394,10 +6394,10 @@
         <v>45817</v>
       </c>
       <c r="B542" t="n">
-        <v>23329.4</v>
+        <v>36596.56</v>
       </c>
       <c r="C542" t="n">
-        <v>0.007092565972087517</v>
+        <v>0.00708853332937065</v>
       </c>
     </row>
     <row r="543">
@@ -6405,10 +6405,10 @@
         <v>45818</v>
       </c>
       <c r="B543" t="n">
-        <v>23339.95</v>
+        <v>36608.83</v>
       </c>
       <c r="C543" t="n">
-        <v>0.0004522190883606836</v>
+        <v>0.0003352774140521486</v>
       </c>
     </row>
     <row r="544">
@@ -6416,10 +6416,10 @@
         <v>45819</v>
       </c>
       <c r="B544" t="n">
-        <v>23337.85</v>
+        <v>36606.02</v>
       </c>
       <c r="C544" t="n">
-        <v>-8.997448580660983e-05</v>
+        <v>-7.675743802804114e-05</v>
       </c>
     </row>
     <row r="545">
@@ -6427,10 +6427,10 @@
         <v>45820</v>
       </c>
       <c r="B545" t="n">
-        <v>23046.45</v>
+        <v>36153.5</v>
       </c>
       <c r="C545" t="n">
-        <v>-0.01248615446581403</v>
+        <v>-0.0123619011299233</v>
       </c>
     </row>
     <row r="546">
@@ -6438,10 +6438,10 @@
         <v>45821</v>
       </c>
       <c r="B546" t="n">
-        <v>22906.2</v>
+        <v>35946.69</v>
       </c>
       <c r="C546" t="n">
-        <v>-0.006085535950222321</v>
+        <v>-0.005720331364874709</v>
       </c>
     </row>
     <row r="547">
@@ -6449,10 +6449,10 @@
         <v>45824</v>
       </c>
       <c r="B547" t="n">
-        <v>23095.05</v>
+        <v>36241.28</v>
       </c>
       <c r="C547" t="n">
-        <v>0.008244492757419231</v>
+        <v>0.008195191267958091</v>
       </c>
     </row>
     <row r="548">
@@ -6460,10 +6460,10 @@
         <v>45825</v>
       </c>
       <c r="B548" t="n">
-        <v>22964.8</v>
+        <v>36071.37</v>
       </c>
       <c r="C548" t="n">
-        <v>-0.005639736653525351</v>
+        <v>-0.00468830019248756</v>
       </c>
     </row>
     <row r="549">
@@ -6471,10 +6471,10 @@
         <v>45826</v>
       </c>
       <c r="B549" t="n">
-        <v>22925.2</v>
+        <v>35982.58</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.001724378178777908</v>
+        <v>-0.002461508947400715</v>
       </c>
     </row>
     <row r="550">
@@ -6482,10 +6482,10 @@
         <v>45827</v>
       </c>
       <c r="B550" t="n">
-        <v>22763.5</v>
+        <v>35733.89</v>
       </c>
       <c r="C550" t="n">
-        <v>-0.007053373580165112</v>
+        <v>-0.006911399905176419</v>
       </c>
     </row>
     <row r="551">
@@ -6493,10 +6493,10 @@
         <v>45828</v>
       </c>
       <c r="B551" t="n">
-        <v>23041.1</v>
+        <v>36157.56</v>
       </c>
       <c r="C551" t="n">
-        <v>0.01219496123179642</v>
+        <v>0.01185625186622552</v>
       </c>
     </row>
     <row r="552">
@@ -6504,10 +6504,10 @@
         <v>45831</v>
       </c>
       <c r="B552" t="n">
-        <v>23001.5</v>
+        <v>36088.23</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.001718667945540764</v>
+        <v>-0.001917441331771075</v>
       </c>
     </row>
     <row r="553">
@@ -6515,10 +6515,10 @@
         <v>45832</v>
       </c>
       <c r="B553" t="n">
-        <v>23128.9</v>
+        <v>36254.9</v>
       </c>
       <c r="C553" t="n">
-        <v>0.00553876921070362</v>
+        <v>0.004618403285503225</v>
       </c>
     </row>
     <row r="554">
@@ -6526,10 +6526,10 @@
         <v>45833</v>
       </c>
       <c r="B554" t="n">
-        <v>23296.85</v>
+        <v>36545.02</v>
       </c>
       <c r="C554" t="n">
-        <v>0.007261478064239935</v>
+        <v>0.008002228664263145</v>
       </c>
     </row>
     <row r="555">
@@ -6537,10 +6537,10 @@
         <v>45834</v>
       </c>
       <c r="B555" t="n">
-        <v>23517.55</v>
+        <v>36895.95</v>
       </c>
       <c r="C555" t="n">
-        <v>0.009473383740720376</v>
+        <v>0.009602676370132013</v>
       </c>
     </row>
     <row r="556">
@@ -6548,10 +6548,10 @@
         <v>45835</v>
       </c>
       <c r="B556" t="n">
-        <v>23620.45</v>
+        <v>37060.93</v>
       </c>
       <c r="C556" t="n">
-        <v>0.004375455776643555</v>
+        <v>0.004471493483702238</v>
       </c>
     </row>
     <row r="557">
@@ -6559,10 +6559,10 @@
         <v>45838</v>
       </c>
       <c r="B557" t="n">
-        <v>23617.2</v>
+        <v>37043.16</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.0001375926368888392</v>
+        <v>-0.0004794806822170372</v>
       </c>
     </row>
     <row r="558">
@@ -6570,10 +6570,10 @@
         <v>45839</v>
       </c>
       <c r="B558" t="n">
-        <v>23615.45</v>
+        <v>37042.95</v>
       </c>
       <c r="C558" t="n">
-        <v>-7.409853835338431e-05</v>
+        <v>-5.669062790758517e-06</v>
       </c>
     </row>
     <row r="559">
@@ -6581,10 +6581,10 @@
         <v>45840</v>
       </c>
       <c r="B559" t="n">
-        <v>23547.25</v>
+        <v>36936</v>
       </c>
       <c r="C559" t="n">
-        <v>-0.002887939886811464</v>
+        <v>-0.002887189060266415</v>
       </c>
     </row>
     <row r="560">
@@ -6592,10 +6592,10 @@
         <v>45841</v>
       </c>
       <c r="B560" t="n">
-        <v>23521.85</v>
+        <v>36890.97</v>
       </c>
       <c r="C560" t="n">
-        <v>-0.001078682224038952</v>
+        <v>-0.001219135802469129</v>
       </c>
     </row>
     <row r="561">
@@ -6603,10 +6603,10 @@
         <v>45842</v>
       </c>
       <c r="B561" t="n">
-        <v>23562.45</v>
+        <v>36967.25</v>
       </c>
       <c r="C561" t="n">
-        <v>0.001726054710832869</v>
+        <v>0.00206771467380773</v>
       </c>
     </row>
     <row r="562">
@@ -6614,10 +6614,10 @@
         <v>45845</v>
       </c>
       <c r="B562" t="n">
-        <v>23551.2</v>
+        <v>36948.2</v>
       </c>
       <c r="C562" t="n">
-        <v>-0.0004774545940681163</v>
+        <v>-0.0005153209935822023</v>
       </c>
     </row>
     <row r="563">
@@ -6625,10 +6625,10 @@
         <v>45846</v>
       </c>
       <c r="B563" t="n">
-        <v>23572.55</v>
+        <v>36999.02</v>
       </c>
       <c r="C563" t="n">
-        <v>0.0009065355480823989</v>
+        <v>0.001375439128293188</v>
       </c>
     </row>
     <row r="564">
@@ -6636,10 +6636,10 @@
         <v>45847</v>
       </c>
       <c r="B564" t="n">
-        <v>23557.45</v>
+        <v>36963.79</v>
       </c>
       <c r="C564" t="n">
-        <v>-0.0006405755847372907</v>
+        <v>-0.0009521873822603277</v>
       </c>
     </row>
     <row r="565">
@@ -6647,10 +6647,10 @@
         <v>45848</v>
       </c>
       <c r="B565" t="n">
-        <v>23471.4</v>
+        <v>36838.75</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.003652772265249404</v>
+        <v>-0.003382770002751334</v>
       </c>
     </row>
     <row r="566">
@@ -6658,10 +6658,10 @@
         <v>45849</v>
       </c>
       <c r="B566" t="n">
-        <v>23282.7</v>
+        <v>36545.58</v>
       </c>
       <c r="C566" t="n">
-        <v>-0.008039571563690284</v>
+        <v>-0.007958196192867528</v>
       </c>
     </row>
     <row r="567">
@@ -6669,10 +6669,10 @@
         <v>45852</v>
       </c>
       <c r="B567" t="n">
-        <v>23309.05</v>
+        <v>36582.53</v>
       </c>
       <c r="C567" t="n">
-        <v>0.001131741593543678</v>
+        <v>0.001011066180917064</v>
       </c>
     </row>
     <row r="568">
@@ -6680,10 +6680,10 @@
         <v>45853</v>
       </c>
       <c r="B568" t="n">
-        <v>23449.15</v>
+        <v>36799.23</v>
       </c>
       <c r="C568" t="n">
-        <v>0.006010540970138312</v>
+        <v>0.005923592490732821</v>
       </c>
     </row>
     <row r="569">
@@ -6691,10 +6691,10 @@
         <v>45854</v>
       </c>
       <c r="B569" t="n">
-        <v>23472.5</v>
+        <v>36827.24</v>
       </c>
       <c r="C569" t="n">
-        <v>0.0009957717017461398</v>
+        <v>0.000761157230735332</v>
       </c>
     </row>
     <row r="570">
@@ -6702,10 +6702,10 @@
         <v>45855</v>
       </c>
       <c r="B570" t="n">
-        <v>23419.7</v>
+        <v>36752.95</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.002249440835019656</v>
+        <v>-0.002017256791440269</v>
       </c>
     </row>
     <row r="571">
@@ -6713,10 +6713,10 @@
         <v>45856</v>
       </c>
       <c r="B571" t="n">
-        <v>23275.15</v>
+        <v>36532.54</v>
       </c>
       <c r="C571" t="n">
-        <v>-0.006172154212052194</v>
+        <v>-0.00599706962298252</v>
       </c>
     </row>
     <row r="572">
@@ -6724,10 +6724,10 @@
         <v>45859</v>
       </c>
       <c r="B572" t="n">
-        <v>23378.45</v>
+        <v>36688.2</v>
       </c>
       <c r="C572" t="n">
-        <v>0.004438209850419872</v>
+        <v>0.004260858949309165</v>
       </c>
     </row>
     <row r="573">
@@ -6735,10 +6735,10 @@
         <v>45860</v>
       </c>
       <c r="B573" t="n">
-        <v>23320.9</v>
+        <v>36600.07</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.002461668759049407</v>
+        <v>-0.002402134746321671</v>
       </c>
     </row>
     <row r="574">
@@ -6746,10 +6746,10 @@
         <v>45861</v>
       </c>
       <c r="B574" t="n">
-        <v>23428.4</v>
+        <v>36765.36</v>
       </c>
       <c r="C574" t="n">
-        <v>0.004609599114957064</v>
+        <v>0.004516111581207349</v>
       </c>
     </row>
     <row r="575">
@@ -6757,10 +6757,10 @@
         <v>45862</v>
       </c>
       <c r="B575" t="n">
-        <v>23301.1</v>
+        <v>36563.21</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.005433576343241708</v>
+        <v>-0.005498382172784422</v>
       </c>
     </row>
     <row r="576">
@@ -6768,10 +6768,10 @@
         <v>45863</v>
       </c>
       <c r="B576" t="n">
-        <v>23014.8</v>
+        <v>36129.89</v>
       </c>
       <c r="C576" t="n">
-        <v>-0.01228697357635478</v>
+        <v>-0.01185125704225642</v>
       </c>
     </row>
     <row r="577">
@@ -6779,10 +6779,10 @@
         <v>45866</v>
       </c>
       <c r="B577" t="n">
-        <v>22846.95</v>
+        <v>35869.97</v>
       </c>
       <c r="C577" t="n">
-        <v>-0.007293133114343764</v>
+        <v>-0.007194043491413837</v>
       </c>
     </row>
     <row r="578">
@@ -6790,10 +6790,10 @@
         <v>45867</v>
       </c>
       <c r="B578" t="n">
-        <v>23007.35</v>
+        <v>36126.52</v>
       </c>
       <c r="C578" t="n">
-        <v>0.007020630762530677</v>
+        <v>0.007152222318557611</v>
       </c>
     </row>
     <row r="579">
@@ -6801,10 +6801,10 @@
         <v>45868</v>
       </c>
       <c r="B579" t="n">
-        <v>23033.55</v>
+        <v>36167.15</v>
       </c>
       <c r="C579" t="n">
-        <v>0.001138766524610535</v>
+        <v>0.00112465856107935</v>
       </c>
     </row>
     <row r="580">
@@ -6812,10 +6812,10 @@
         <v>45869</v>
       </c>
       <c r="B580" t="n">
-        <v>22914.95</v>
+        <v>35981.74</v>
       </c>
       <c r="C580" t="n">
-        <v>-0.005149010899318518</v>
+        <v>-0.00512647526830301</v>
       </c>
     </row>
     <row r="581">
@@ -6823,10 +6823,10 @@
         <v>45870</v>
       </c>
       <c r="B581" t="n">
-        <v>22673.65</v>
+        <v>35598.07</v>
       </c>
       <c r="C581" t="n">
-        <v>-0.0105302433564114</v>
+        <v>-0.01066290846412643</v>
       </c>
     </row>
     <row r="582">
@@ -6834,10 +6834,10 @@
         <v>45873</v>
       </c>
       <c r="B582" t="n">
-        <v>22860.4</v>
+        <v>35889.79</v>
       </c>
       <c r="C582" t="n">
-        <v>0.008236433040114788</v>
+        <v>0.008194826292549084</v>
       </c>
     </row>
     <row r="583">
@@ -6845,10 +6845,10 @@
         <v>45874</v>
       </c>
       <c r="B583" t="n">
-        <v>22798.5</v>
+        <v>35792.76</v>
       </c>
       <c r="C583" t="n">
-        <v>-0.002707739147171595</v>
+        <v>-0.002703554409206554</v>
       </c>
     </row>
     <row r="584">
@@ -6856,10 +6856,10 @@
         <v>45875</v>
       </c>
       <c r="B584" t="n">
-        <v>22666.85</v>
+        <v>35587.67</v>
       </c>
       <c r="C584" t="n">
-        <v>-0.005774502708511542</v>
+        <v>-0.005729929739980988</v>
       </c>
     </row>
     <row r="585">
@@ -6867,10 +6867,10 @@
         <v>45876</v>
       </c>
       <c r="B585" t="n">
-        <v>22694.1</v>
+        <v>35634.06</v>
       </c>
       <c r="C585" t="n">
-        <v>0.001202196158707647</v>
+        <v>0.001303541366995953</v>
       </c>
     </row>
     <row r="586">
@@ -6878,10 +6878,10 @@
         <v>45877</v>
       </c>
       <c r="B586" t="n">
-        <v>22443.15</v>
+        <v>35228.64</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.01105794016947126</v>
+        <v>-0.01137731709493661</v>
       </c>
     </row>
     <row r="587">
@@ -6889,10 +6889,10 @@
         <v>45880</v>
       </c>
       <c r="B587" t="n">
-        <v>22633.45</v>
+        <v>35539.33</v>
       </c>
       <c r="C587" t="n">
-        <v>0.008479201894564747</v>
+        <v>0.00881924479627938</v>
       </c>
     </row>
     <row r="588">
@@ -6900,10 +6900,10 @@
         <v>45881</v>
       </c>
       <c r="B588" t="n">
-        <v>22568.6</v>
+        <v>35437.06</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.002865228235200634</v>
+        <v>-0.002877656950764251</v>
       </c>
     </row>
     <row r="589">
@@ -6911,10 +6911,10 @@
         <v>45882</v>
       </c>
       <c r="B589" t="n">
-        <v>22698.1</v>
+        <v>35631.91</v>
       </c>
       <c r="C589" t="n">
-        <v>0.005738060845599691</v>
+        <v>0.005498480968793906</v>
       </c>
     </row>
     <row r="590">
@@ -6922,10 +6922,10 @@
         <v>45883</v>
       </c>
       <c r="B590" t="n">
-        <v>22680.25</v>
+        <v>35604.49</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.0007864094351508477</v>
+        <v>-0.0007695349477477853</v>
       </c>
     </row>
     <row r="591">
@@ -6933,10 +6933,10 @@
         <v>45887</v>
       </c>
       <c r="B591" t="n">
-        <v>22931.5</v>
+        <v>36001.36</v>
       </c>
       <c r="C591" t="n">
-        <v>0.01107792021692888</v>
+        <v>0.01114662785508247</v>
       </c>
     </row>
     <row r="592">
@@ -6944,10 +6944,10 @@
         <v>45888</v>
       </c>
       <c r="B592" t="n">
-        <v>23066.6</v>
+        <v>36211.33</v>
       </c>
       <c r="C592" t="n">
-        <v>0.005891459346313965</v>
+        <v>0.005832279669434781</v>
       </c>
     </row>
     <row r="593">
@@ -6955,10 +6955,10 @@
         <v>45889</v>
       </c>
       <c r="B593" t="n">
-        <v>23143.15</v>
+        <v>36323.56</v>
       </c>
       <c r="C593" t="n">
-        <v>0.003318651209974766</v>
+        <v>0.003099306211619357</v>
       </c>
     </row>
     <row r="594">
@@ -6966,10 +6966,10 @@
         <v>45890</v>
       </c>
       <c r="B594" t="n">
-        <v>23137.15</v>
+        <v>36328.71</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.0002592559785509208</v>
+        <v>0.0001417812571236077</v>
       </c>
     </row>
     <row r="595">
@@ -6977,10 +6977,10 @@
         <v>45891</v>
       </c>
       <c r="B595" t="n">
-        <v>22991.3</v>
+        <v>36089.64</v>
       </c>
       <c r="C595" t="n">
-        <v>-0.006303715021080958</v>
+        <v>-0.006580745641670216</v>
       </c>
     </row>
     <row r="596">
@@ -6988,10 +6988,10 @@
         <v>45894</v>
       </c>
       <c r="B596" t="n">
-        <v>23052</v>
+        <v>36194.34</v>
       </c>
       <c r="C596" t="n">
-        <v>0.002640129092308818</v>
+        <v>0.002901109570502713</v>
       </c>
     </row>
     <row r="597">
@@ -6999,10 +6999,10 @@
         <v>45895</v>
       </c>
       <c r="B597" t="n">
-        <v>22768.65</v>
+        <v>35755.99</v>
       </c>
       <c r="C597" t="n">
-        <v>-0.01229177511712642</v>
+        <v>-0.01211100962194633</v>
       </c>
     </row>
     <row r="598">
@@ -7010,10 +7010,10 @@
         <v>45897</v>
       </c>
       <c r="B598" t="n">
-        <v>22541.65</v>
+        <v>35409.72</v>
       </c>
       <c r="C598" t="n">
-        <v>-0.00996984889310526</v>
+        <v>-0.00968425150583152</v>
       </c>
     </row>
     <row r="599">
@@ -7021,10 +7021,10 @@
         <v>45898</v>
       </c>
       <c r="B599" t="n">
-        <v>22462.95</v>
+        <v>35287.71</v>
       </c>
       <c r="C599" t="n">
-        <v>-0.003491314965852088</v>
+        <v>-0.003445664071898946</v>
       </c>
     </row>
     <row r="600">
@@ -7032,10 +7032,10 @@
         <v>45901</v>
       </c>
       <c r="B600" t="n">
-        <v>22713.55</v>
+        <v>35679.52</v>
       </c>
       <c r="C600" t="n">
-        <v>0.01115614823520494</v>
+        <v>0.01110329913729169</v>
       </c>
     </row>
     <row r="601">
@@ -7043,10 +7043,10 @@
         <v>45902</v>
       </c>
       <c r="B601" t="n">
-        <v>22724.4</v>
+        <v>35693.62</v>
       </c>
       <c r="C601" t="n">
-        <v>0.0004776884282731153</v>
+        <v>0.0003951846885834609</v>
       </c>
     </row>
     <row r="602">
@@ -7054,10 +7054,10 @@
         <v>45903</v>
       </c>
       <c r="B602" t="n">
-        <v>22864.65</v>
+        <v>35905.15</v>
       </c>
       <c r="C602" t="n">
-        <v>0.006171780113006342</v>
+        <v>0.005926269176396159</v>
       </c>
     </row>
     <row r="603">
@@ -7065,10 +7065,10 @@
         <v>45904</v>
       </c>
       <c r="B603" t="n">
-        <v>22819.65</v>
+        <v>35845.46</v>
       </c>
       <c r="C603" t="n">
-        <v>-0.001968103600973548</v>
+        <v>-0.001662435611604507</v>
       </c>
     </row>
     <row r="604">
@@ -7076,10 +7076,10 @@
         <v>45905</v>
       </c>
       <c r="B604" t="n">
-        <v>22829.15</v>
+        <v>35842.34</v>
       </c>
       <c r="C604" t="n">
-        <v>0.0004163078750112348</v>
+        <v>-8.704031138118129e-05</v>
       </c>
     </row>
     <row r="605">
@@ -7087,10 +7087,10 @@
         <v>45908</v>
       </c>
       <c r="B605" t="n">
-        <v>22878.65</v>
+        <v>35916.19</v>
       </c>
       <c r="C605" t="n">
-        <v>0.002168280465983274</v>
+        <v>0.002060412350309848</v>
       </c>
     </row>
     <row r="606">
@@ -7098,10 +7098,10 @@
         <v>45909</v>
       </c>
       <c r="B606" t="n">
-        <v>22949.1</v>
+        <v>36032.5</v>
       </c>
       <c r="C606" t="n">
-        <v>0.003079290080489683</v>
+        <v>0.003238372444293258</v>
       </c>
     </row>
     <row r="607">
@@ -7109,10 +7109,10 @@
         <v>45910</v>
       </c>
       <c r="B607" t="n">
-        <v>23079.95</v>
+        <v>36235.46</v>
       </c>
       <c r="C607" t="n">
-        <v>0.005701748652452654</v>
+        <v>0.005632692707971954</v>
       </c>
     </row>
     <row r="608">
@@ -7120,10 +7120,10 @@
         <v>45911</v>
       </c>
       <c r="B608" t="n">
-        <v>23102.65</v>
+        <v>36287.91</v>
       </c>
       <c r="C608" t="n">
-        <v>0.0009835376593103629</v>
+        <v>0.001447477139796316</v>
       </c>
     </row>
     <row r="609">
@@ -7131,10 +7131,10 @@
         <v>45912</v>
       </c>
       <c r="B609" t="n">
-        <v>23190.25</v>
+        <v>36418.62</v>
       </c>
       <c r="C609" t="n">
-        <v>0.003791772805284088</v>
+        <v>0.003602026129363667</v>
       </c>
     </row>
     <row r="610">
@@ -7142,10 +7142,10 @@
         <v>45915</v>
       </c>
       <c r="B610" t="n">
-        <v>23215.85</v>
+        <v>36452.98</v>
       </c>
       <c r="C610" t="n">
-        <v>0.001103912204482471</v>
+        <v>0.0009434734210138629</v>
       </c>
     </row>
     <row r="611">
@@ -7153,10 +7153,10 @@
         <v>45916</v>
       </c>
       <c r="B611" t="n">
-        <v>23369.3</v>
+        <v>36697.39</v>
       </c>
       <c r="C611" t="n">
-        <v>0.006609708453491958</v>
+        <v>0.006704801637616331</v>
       </c>
     </row>
     <row r="612">
@@ -7164,10 +7164,10 @@
         <v>45917</v>
       </c>
       <c r="B612" t="n">
-        <v>23445.2</v>
+        <v>36813.13</v>
       </c>
       <c r="C612" t="n">
-        <v>0.003247850812818642</v>
+        <v>0.003153902770741901</v>
       </c>
     </row>
     <row r="613">
@@ -7175,10 +7175,10 @@
         <v>45918</v>
       </c>
       <c r="B613" t="n">
-        <v>23518.9</v>
+        <v>36930.41</v>
       </c>
       <c r="C613" t="n">
-        <v>0.003143500588606685</v>
+        <v>0.003185819841996729</v>
       </c>
     </row>
     <row r="614">
@@ -7186,10 +7186,10 @@
         <v>45919</v>
       </c>
       <c r="B614" t="n">
-        <v>23486.65</v>
+        <v>36878.84</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.001371237600397923</v>
+        <v>-0.001396410167122664</v>
       </c>
     </row>
     <row r="615">
@@ -7197,10 +7197,10 @@
         <v>45922</v>
       </c>
       <c r="B615" t="n">
-        <v>23381.45</v>
+        <v>36707.87</v>
       </c>
       <c r="C615" t="n">
-        <v>-0.00447914027756191</v>
+        <v>-0.004635991804514239</v>
       </c>
     </row>
     <row r="616">
@@ -7208,10 +7208,10 @@
         <v>45923</v>
       </c>
       <c r="B616" t="n">
-        <v>23325.25</v>
+        <v>36631.9</v>
       </c>
       <c r="C616" t="n">
-        <v>-0.00240361483141549</v>
+        <v>-0.00206958344355046</v>
       </c>
     </row>
     <row r="617">
@@ -7219,10 +7219,10 @@
         <v>45924</v>
       </c>
       <c r="B617" t="n">
-        <v>23178.25</v>
+        <v>36398.48</v>
       </c>
       <c r="C617" t="n">
-        <v>-0.006302183256342353</v>
+        <v>-0.006372041854230792</v>
       </c>
     </row>
     <row r="618">
@@ -7230,10 +7230,10 @@
         <v>45925</v>
       </c>
       <c r="B618" t="n">
-        <v>23022.4</v>
+        <v>36156.07</v>
       </c>
       <c r="C618" t="n">
-        <v>-0.006723976141425614</v>
+        <v>-0.006659893490057911</v>
       </c>
     </row>
     <row r="619">
@@ -7241,10 +7241,10 @@
         <v>45926</v>
       </c>
       <c r="B619" t="n">
-        <v>22713.15</v>
+        <v>35673.24</v>
       </c>
       <c r="C619" t="n">
-        <v>-0.0134325700187643</v>
+        <v>-0.01335405092422937</v>
       </c>
     </row>
     <row r="620">
@@ -7252,10 +7252,10 @@
         <v>45929</v>
       </c>
       <c r="B620" t="n">
-        <v>22739.1</v>
+        <v>35717.08</v>
       </c>
       <c r="C620" t="n">
-        <v>0.001142509955686322</v>
+        <v>0.001228932387414394</v>
       </c>
     </row>
     <row r="621">
@@ -7263,10 +7263,10 @@
         <v>45930</v>
       </c>
       <c r="B621" t="n">
-        <v>22734.1</v>
+        <v>35714.1</v>
       </c>
       <c r="C621" t="n">
-        <v>-0.000219885571548617</v>
+        <v>-8.343347216521746e-05</v>
       </c>
     </row>
     <row r="622">
@@ -7274,10 +7274,10 @@
         <v>45931</v>
       </c>
       <c r="B622" t="n">
-        <v>22928.3</v>
+        <v>36014.32</v>
       </c>
       <c r="C622" t="n">
-        <v>0.008542233912932629</v>
+        <v>0.008406203712259419</v>
       </c>
     </row>
     <row r="623">
@@ -7285,10 +7285,10 @@
         <v>45933</v>
       </c>
       <c r="B623" t="n">
-        <v>23027.7</v>
+        <v>36164.94</v>
       </c>
       <c r="C623" t="n">
-        <v>0.004335253812973505</v>
+        <v>0.004182225292605812</v>
       </c>
     </row>
     <row r="624">
@@ -7296,10 +7296,10 @@
         <v>45936</v>
       </c>
       <c r="B624" t="n">
-        <v>23169.65</v>
+        <v>36376.26</v>
       </c>
       <c r="C624" t="n">
-        <v>0.006164315150883448</v>
+        <v>0.005843228275783208</v>
       </c>
     </row>
     <row r="625">
@@ -7307,10 +7307,10 @@
         <v>45937</v>
       </c>
       <c r="B625" t="n">
-        <v>23212.8</v>
+        <v>36437.08</v>
       </c>
       <c r="C625" t="n">
-        <v>0.00186235010023883</v>
+        <v>0.001671969575761656</v>
       </c>
     </row>
     <row r="626">
@@ -7318,10 +7318,10 @@
         <v>45938</v>
       </c>
       <c r="B626" t="n">
-        <v>23109.35</v>
+        <v>36278</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.004456592914254265</v>
+        <v>-0.004365882227664875</v>
       </c>
     </row>
     <row r="627">
@@ -7329,10 +7329,10 @@
         <v>45939</v>
       </c>
       <c r="B627" t="n">
-        <v>23241.75</v>
+        <v>36486.65</v>
       </c>
       <c r="C627" t="n">
-        <v>0.005729282736208541</v>
+        <v>0.005751419593141849</v>
       </c>
     </row>
     <row r="628">
@@ -7340,10 +7340,10 @@
         <v>45940</v>
       </c>
       <c r="B628" t="n">
-        <v>23337.55</v>
+        <v>36630.27</v>
       </c>
       <c r="C628" t="n">
-        <v>0.004121892714619158</v>
+        <v>0.003936234211691092</v>
       </c>
     </row>
     <row r="629">
@@ -7351,10 +7351,10 @@
         <v>45943</v>
       </c>
       <c r="B629" t="n">
-        <v>23294.8</v>
+        <v>36560.05</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.001831811822577745</v>
+        <v>-0.001916993786832411</v>
       </c>
     </row>
     <row r="630">
@@ -7362,10 +7362,10 @@
         <v>45944</v>
       </c>
       <c r="B630" t="n">
-        <v>23160.7</v>
+        <v>36381.72</v>
       </c>
       <c r="C630" t="n">
-        <v>-0.005756649552689841</v>
+        <v>-0.004877728558905225</v>
       </c>
     </row>
     <row r="631">
@@ -7373,10 +7373,10 @@
         <v>45945</v>
       </c>
       <c r="B631" t="n">
-        <v>23377.35</v>
+        <v>36693.62</v>
       </c>
       <c r="C631" t="n">
-        <v>0.009354207774376233</v>
+        <v>0.00857298665373718</v>
       </c>
     </row>
     <row r="632">
@@ -7384,10 +7384,10 @@
         <v>45946</v>
       </c>
       <c r="B632" t="n">
-        <v>23563.8</v>
+        <v>36984.53</v>
       </c>
       <c r="C632" t="n">
-        <v>0.007975668756296184</v>
+        <v>0.007928081230469841</v>
       </c>
     </row>
     <row r="633">
@@ -7395,10 +7395,10 @@
         <v>45947</v>
       </c>
       <c r="B633" t="n">
-        <v>23593.5</v>
+        <v>37039.14</v>
       </c>
       <c r="C633" t="n">
-        <v>0.001260407913833861</v>
+        <v>0.001476563309037671</v>
       </c>
     </row>
     <row r="634">
@@ -7406,10 +7406,10 @@
         <v>45950</v>
       </c>
       <c r="B634" t="n">
-        <v>23716.1</v>
+        <v>37223.4</v>
       </c>
       <c r="C634" t="n">
-        <v>0.00519634645135314</v>
+        <v>0.004974737534402918</v>
       </c>
     </row>
     <row r="635">
@@ -7417,10 +7417,10 @@
         <v>45951</v>
       </c>
       <c r="B635" t="n">
-        <v>23759.2</v>
+        <v>37286.13</v>
       </c>
       <c r="C635" t="n">
-        <v>0.001817330842760922</v>
+        <v>0.00168523025838585</v>
       </c>
     </row>
     <row r="636">
@@ -7428,10 +7428,10 @@
         <v>45953</v>
       </c>
       <c r="B636" t="n">
-        <v>23755.9</v>
+        <v>37285.19</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.0001388935654398349</v>
+        <v>-2.521044688719165e-05</v>
       </c>
     </row>
     <row r="637">
@@ -7439,10 +7439,10 @@
         <v>45954</v>
       </c>
       <c r="B637" t="n">
-        <v>23686.6</v>
+        <v>37171.91</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.002917170050387607</v>
+        <v>-0.003038203640641224</v>
       </c>
     </row>
     <row r="638">
@@ -7450,10 +7450,10 @@
         <v>45957</v>
       </c>
       <c r="B638" t="n">
-        <v>23840.9</v>
+        <v>37421.12</v>
       </c>
       <c r="C638" t="n">
-        <v>0.006514231675293303</v>
+        <v>0.006704255982541651</v>
       </c>
     </row>
     <row r="639">
@@ -7461,10 +7461,10 @@
         <v>45958</v>
       </c>
       <c r="B639" t="n">
-        <v>23812.55</v>
+        <v>37380.76</v>
       </c>
       <c r="C639" t="n">
-        <v>-0.001189132960584649</v>
+        <v>-0.001078535329781749</v>
       </c>
     </row>
     <row r="640">
@@ -7472,10 +7472,10 @@
         <v>45959</v>
       </c>
       <c r="B640" t="n">
-        <v>23952.4</v>
+        <v>37598.65</v>
       </c>
       <c r="C640" t="n">
-        <v>0.005872953547604087</v>
+        <v>0.005828934457191348</v>
       </c>
     </row>
     <row r="641">
@@ -7483,10 +7483,10 @@
         <v>45960</v>
       </c>
       <c r="B641" t="n">
-        <v>23841.3</v>
+        <v>37420.19</v>
       </c>
       <c r="C641" t="n">
-        <v>-0.004638366092750701</v>
+        <v>-0.004746447013390109</v>
       </c>
     </row>
     <row r="642">
@@ -7494,10 +7494,10 @@
         <v>45961</v>
       </c>
       <c r="B642" t="n">
-        <v>23710.4</v>
+        <v>37214.04</v>
       </c>
       <c r="C642" t="n">
-        <v>-0.005490472415514147</v>
+        <v>-0.005509058078005502</v>
       </c>
     </row>
     <row r="643">
@@ -7505,10 +7505,10 @@
         <v>45964</v>
       </c>
       <c r="B643" t="n">
-        <v>23810.7</v>
+        <v>37361.96</v>
       </c>
       <c r="C643" t="n">
-        <v>0.004230211215331625</v>
+        <v>0.003974843903000069</v>
       </c>
     </row>
     <row r="644">
@@ -7516,10 +7516,10 @@
         <v>45965</v>
       </c>
       <c r="B644" t="n">
-        <v>23675.45</v>
+        <v>37147.34</v>
       </c>
       <c r="C644" t="n">
-        <v>-0.00568021939716179</v>
+        <v>-0.005744345318072219</v>
       </c>
     </row>
     <row r="645">
@@ -7527,10 +7527,10 @@
         <v>45967</v>
       </c>
       <c r="B645" t="n">
-        <v>23513.15</v>
+        <v>36900.24</v>
       </c>
       <c r="C645" t="n">
-        <v>-0.006855202329839494</v>
+        <v>-0.006651889475800865</v>
       </c>
     </row>
     <row r="646">
@@ -7538,10 +7538,10 @@
         <v>45968</v>
       </c>
       <c r="B646" t="n">
-        <v>23521.5</v>
+        <v>36900.76</v>
       </c>
       <c r="C646" t="n">
-        <v>0.0003551204326088797</v>
+        <v>1.409204926594576e-05</v>
       </c>
     </row>
     <row r="647">
@@ -7549,10 +7549,10 @@
         <v>45971</v>
       </c>
       <c r="B647" t="n">
-        <v>23596.9</v>
+        <v>37024.12</v>
       </c>
       <c r="C647" t="n">
-        <v>0.003205577875560639</v>
+        <v>0.003343020577353917</v>
       </c>
     </row>
     <row r="648">
@@ -7560,10 +7560,10 @@
         <v>45972</v>
       </c>
       <c r="B648" t="n">
-        <v>23682.65</v>
+        <v>37157.16</v>
       </c>
       <c r="C648" t="n">
-        <v>0.003633951917412892</v>
+        <v>0.003593333210890615</v>
       </c>
     </row>
     <row r="649">
@@ -7571,10 +7571,10 @@
         <v>45973</v>
       </c>
       <c r="B649" t="n">
-        <v>23836.9</v>
+        <v>37385.63</v>
       </c>
       <c r="C649" t="n">
-        <v>0.006513206925745196</v>
+        <v>0.006148747643791808</v>
       </c>
     </row>
     <row r="650">
@@ -7582,10 +7582,10 @@
         <v>45974</v>
       </c>
       <c r="B650" t="n">
-        <v>23816</v>
+        <v>37354.83</v>
       </c>
       <c r="C650" t="n">
-        <v>-0.0008767918647140105</v>
+        <v>-0.0008238459536457077</v>
       </c>
     </row>
     <row r="651">
@@ -7593,10 +7593,10 @@
         <v>45975</v>
       </c>
       <c r="B651" t="n">
-        <v>23836.35</v>
+        <v>37369.13</v>
       </c>
       <c r="C651" t="n">
-        <v>0.000854467584816776</v>
+        <v>0.0003828152878755375</v>
       </c>
     </row>
     <row r="652">
@@ -7604,10 +7604,10 @@
         <v>45978</v>
       </c>
       <c r="B652" t="n">
-        <v>23954.55</v>
+        <v>37570.78</v>
       </c>
       <c r="C652" t="n">
-        <v>0.004958812905499377</v>
+        <v>0.005396165230499017</v>
       </c>
     </row>
     <row r="653">
@@ -7615,10 +7615,10 @@
         <v>45979</v>
       </c>
       <c r="B653" t="n">
-        <v>23824.65</v>
+        <v>37360.86</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.005422769369493374</v>
+        <v>-0.005587320784929073</v>
       </c>
     </row>
     <row r="654">
@@ -7626,10 +7626,10 @@
         <v>45980</v>
       </c>
       <c r="B654" t="n">
-        <v>23906.3</v>
+        <v>37485.82</v>
       </c>
       <c r="C654" t="n">
-        <v>0.003427122748917544</v>
+        <v>0.003344676755299592</v>
       </c>
     </row>
     <row r="655">
@@ -7637,10 +7637,10 @@
         <v>45981</v>
       </c>
       <c r="B655" t="n">
-        <v>23975.45</v>
+        <v>37596.71</v>
       </c>
       <c r="C655" t="n">
-        <v>0.002892542969844758</v>
+        <v>0.002958185255117707</v>
       </c>
     </row>
     <row r="656">
@@ -7648,10 +7648,10 @@
         <v>45982</v>
       </c>
       <c r="B656" t="n">
-        <v>23790.25</v>
+        <v>37312.99</v>
       </c>
       <c r="C656" t="n">
-        <v>-0.007724568256278874</v>
+        <v>-0.007546404991287781</v>
       </c>
     </row>
     <row r="657">
@@ -7659,10 +7659,10 @@
         <v>45985</v>
       </c>
       <c r="B657" t="n">
-        <v>23674.55</v>
+        <v>37140.83</v>
       </c>
       <c r="C657" t="n">
-        <v>-0.004863336871197221</v>
+        <v>-0.004613942758272538</v>
       </c>
     </row>
     <row r="658">
@@ -7670,10 +7670,10 @@
         <v>45986</v>
       </c>
       <c r="B658" t="n">
-        <v>23655.05</v>
+        <v>37102.42</v>
       </c>
       <c r="C658" t="n">
-        <v>-0.0008236692988884409</v>
+        <v>-0.001034171826531649</v>
       </c>
     </row>
     <row r="659">
@@ -7681,10 +7681,10 @@
         <v>45987</v>
       </c>
       <c r="B659" t="n">
-        <v>23955.2</v>
+        <v>37569.64</v>
       </c>
       <c r="C659" t="n">
-        <v>0.0126886225140086</v>
+        <v>0.0125927095860594</v>
       </c>
     </row>
     <row r="660">
@@ -7692,10 +7692,10 @@
         <v>45988</v>
       </c>
       <c r="B660" t="n">
-        <v>23947.75</v>
+        <v>37554.39</v>
       </c>
       <c r="C660" t="n">
-        <v>-0.0003109971947635737</v>
+        <v>-0.0004059128594258166</v>
       </c>
     </row>
     <row r="661">
@@ -7703,10 +7703,10 @@
         <v>45989</v>
       </c>
       <c r="B661" t="n">
-        <v>23933.2</v>
+        <v>37535.84</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.0006075727364783789</v>
+        <v>-0.0004939502412368846</v>
       </c>
     </row>
     <row r="662">
@@ -7714,10 +7714,10 @@
         <v>45992</v>
       </c>
       <c r="B662" t="n">
-        <v>23918.55</v>
+        <v>37524.59</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.0006121204017850435</v>
+        <v>-0.0002997135537662343</v>
       </c>
     </row>
     <row r="663">
@@ -7725,10 +7725,10 @@
         <v>45993</v>
       </c>
       <c r="B663" t="n">
-        <v>23822.25</v>
+        <v>37370.65</v>
       </c>
       <c r="C663" t="n">
-        <v>-0.004026163793373727</v>
+        <v>-0.004102376601582969</v>
       </c>
     </row>
     <row r="664">
@@ -7736,10 +7736,10 @@
         <v>45994</v>
       </c>
       <c r="B664" t="n">
-        <v>23716.3</v>
+        <v>37210.2</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.004447522799063908</v>
+        <v>-0.004293476297575927</v>
       </c>
     </row>
     <row r="665">
@@ -7747,10 +7747,10 @@
         <v>45995</v>
       </c>
       <c r="B665" t="n">
-        <v>23741.1</v>
+        <v>37250.59</v>
       </c>
       <c r="C665" t="n">
-        <v>0.001045694311507139</v>
+        <v>0.001085455063396523</v>
       </c>
     </row>
     <row r="666">
@@ -7758,10 +7758,10 @@
         <v>45996</v>
       </c>
       <c r="B666" t="n">
-        <v>23835.25</v>
+        <v>37394.44</v>
       </c>
       <c r="C666" t="n">
-        <v>0.003965696618943637</v>
+        <v>0.003861683801518412</v>
       </c>
     </row>
     <row r="667">
@@ -7769,10 +7769,10 @@
         <v>45999</v>
       </c>
       <c r="B667" t="n">
-        <v>23526.2</v>
+        <v>36907.63</v>
       </c>
       <c r="C667" t="n">
-        <v>-0.01296609013960415</v>
+        <v>-0.01301824549318042</v>
       </c>
     </row>
     <row r="668">
@@ -7780,10 +7780,10 @@
         <v>46000</v>
       </c>
       <c r="B668" t="n">
-        <v>23516.25</v>
+        <v>36899.81</v>
       </c>
       <c r="C668" t="n">
-        <v>-0.0004229327303176822</v>
+        <v>-0.00021188030767616</v>
       </c>
     </row>
     <row r="669">
@@ -7791,10 +7791,10 @@
         <v>46001</v>
       </c>
       <c r="B669" t="n">
-        <v>23408.8</v>
+        <v>36743.25</v>
       </c>
       <c r="C669" t="n">
-        <v>-0.004569180885557911</v>
+        <v>-0.004242840274787274</v>
       </c>
     </row>
     <row r="670">
@@ -7802,10 +7802,10 @@
         <v>46002</v>
       </c>
       <c r="B670" t="n">
-        <v>23550.85</v>
+        <v>36963.1</v>
       </c>
       <c r="C670" t="n">
-        <v>0.006068230750828629</v>
+        <v>0.005983411919195936</v>
       </c>
     </row>
     <row r="671">
@@ -7813,10 +7813,10 @@
         <v>46003</v>
       </c>
       <c r="B671" t="n">
-        <v>23726.2</v>
+        <v>37228.82</v>
       </c>
       <c r="C671" t="n">
-        <v>0.007445591135776475</v>
+        <v>0.007188790983440274</v>
       </c>
     </row>
     <row r="672">
@@ -7824,10 +7824,10 @@
         <v>46006</v>
       </c>
       <c r="B672" t="n">
-        <v>23725.2</v>
+        <v>37232.38</v>
       </c>
       <c r="C672" t="n">
-        <v>-4.214749938891149e-05</v>
+        <v>9.562484118474934e-05</v>
       </c>
     </row>
     <row r="673">
@@ -7835,10 +7835,10 @@
         <v>46007</v>
       </c>
       <c r="B673" t="n">
-        <v>23570.15</v>
+        <v>36986.1</v>
       </c>
       <c r="C673" t="n">
-        <v>-0.006535245224487007</v>
+        <v>-0.006614672497433638</v>
       </c>
     </row>
     <row r="674">
@@ -7846,10 +7846,10 @@
         <v>46008</v>
       </c>
       <c r="B674" t="n">
-        <v>23496.05</v>
+        <v>36870.7</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.003143806891343637</v>
+        <v>-0.003120091061236563</v>
       </c>
     </row>
     <row r="675">
@@ -7857,10 +7857,10 @@
         <v>46009</v>
       </c>
       <c r="B675" t="n">
-        <v>23491.5</v>
+        <v>36853.5</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.0001936495708853014</v>
+        <v>-0.000466495076035911</v>
       </c>
     </row>
     <row r="676">
@@ -7868,10 +7868,10 @@
         <v>46010</v>
       </c>
       <c r="B676" t="n">
-        <v>23677.55</v>
+        <v>37143.96</v>
       </c>
       <c r="C676" t="n">
-        <v>0.007919885916182423</v>
+        <v>0.007881476657576547</v>
       </c>
     </row>
     <row r="677">
@@ -7879,10 +7879,10 @@
         <v>46013</v>
       </c>
       <c r="B677" t="n">
-        <v>23867.65</v>
+        <v>37430.94</v>
       </c>
       <c r="C677" t="n">
-        <v>0.008028702293945145</v>
+        <v>0.007726155208007013</v>
       </c>
     </row>
     <row r="678">
@@ -7890,10 +7890,10 @@
         <v>46014</v>
       </c>
       <c r="B678" t="n">
-        <v>23895.15</v>
+        <v>37471.84</v>
       </c>
       <c r="C678" t="n">
-        <v>0.00115218716547294</v>
+        <v>0.001092678944210279</v>
       </c>
     </row>
     <row r="679">
@@ -7901,10 +7901,10 @@
         <v>46015</v>
       </c>
       <c r="B679" t="n">
-        <v>23850.25</v>
+        <v>37408.07</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.001879042399817621</v>
+        <v>-0.001701811280150567</v>
       </c>
     </row>
     <row r="680">
@@ -7912,10 +7912,10 @@
         <v>46017</v>
       </c>
       <c r="B680" t="n">
-        <v>23780.25</v>
+        <v>37294.67</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.002934979717193698</v>
+        <v>-0.003031431453159761</v>
       </c>
     </row>
     <row r="681">
@@ -7923,10 +7923,10 @@
         <v>46020</v>
       </c>
       <c r="B681" t="n">
-        <v>23682.1</v>
+        <v>37140.23</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.004127374607079459</v>
+        <v>-0.004141074314372384</v>
       </c>
     </row>
     <row r="682">
@@ -7934,10 +7934,10 @@
         <v>46021</v>
       </c>
       <c r="B682" t="n">
-        <v>23668.8</v>
+        <v>37135.83</v>
       </c>
       <c r="C682" t="n">
-        <v>-0.0005616056008546089</v>
+        <v>-0.0001184699179299642</v>
       </c>
     </row>
     <row r="683">
@@ -7945,10 +7945,10 @@
         <v>46022</v>
       </c>
       <c r="B683" t="n">
-        <v>23871.55</v>
+        <v>37443.41</v>
       </c>
       <c r="C683" t="n">
-        <v>0.008566129250321186</v>
+        <v>0.008282566997964036</v>
       </c>
     </row>
     <row r="684">
@@ -7956,10 +7956,10 @@
         <v>46023</v>
       </c>
       <c r="B684" t="n">
-        <v>23909.55</v>
+        <v>37497.1</v>
       </c>
       <c r="C684" t="n">
-        <v>0.001591853063584114</v>
+        <v>0.001433897179770716</v>
       </c>
     </row>
     <row r="685">
@@ -7967,10 +7967,10 @@
         <v>46024</v>
       </c>
       <c r="B685" t="n">
-        <v>24099</v>
+        <v>37799.57</v>
       </c>
       <c r="C685" t="n">
-        <v>0.007923612113151401</v>
+        <v>0.008066490475263421</v>
       </c>
     </row>
     <row r="686">
@@ -7978,10 +7978,10 @@
         <v>46027</v>
       </c>
       <c r="B686" t="n">
-        <v>24058.45</v>
+        <v>37730.95</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.001682642433295967</v>
+        <v>-0.001815364566316591</v>
       </c>
     </row>
     <row r="687">
@@ -7989,10 +7989,10 @@
         <v>46028</v>
       </c>
       <c r="B687" t="n">
-        <v>24010.5</v>
+        <v>37657.7</v>
       </c>
       <c r="C687" t="n">
-        <v>-0.001993062728480099</v>
+        <v>-0.001941377039274106</v>
       </c>
     </row>
     <row r="688">
@@ -8000,10 +8000,10 @@
         <v>46029</v>
       </c>
       <c r="B688" t="n">
-        <v>24016.6</v>
+        <v>37669.63</v>
       </c>
       <c r="C688" t="n">
-        <v>0.0002540555173777825</v>
+        <v>0.0003168010791949616</v>
       </c>
     </row>
     <row r="689">
@@ -8011,10 +8011,10 @@
         <v>46030</v>
       </c>
       <c r="B689" t="n">
-        <v>23680.1</v>
+        <v>37137.33</v>
       </c>
       <c r="C689" t="n">
-        <v>-0.01401114229324718</v>
+        <v>-0.0141307467049715</v>
       </c>
     </row>
     <row r="690">
@@ -8022,10 +8022,10 @@
         <v>46031</v>
       </c>
       <c r="B690" t="n">
-        <v>23467.35</v>
+        <v>36807.62</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.008984337059387393</v>
+        <v>-0.008878128826170339</v>
       </c>
     </row>
     <row r="691">
@@ -8033,10 +8033,10 @@
         <v>46034</v>
       </c>
       <c r="B691" t="n">
-        <v>23527.55</v>
+        <v>36864.27</v>
       </c>
       <c r="C691" t="n">
-        <v>0.002565266210287964</v>
+        <v>0.001539083483256931</v>
       </c>
     </row>
     <row r="692">
@@ -8044,10 +8044,10 @@
         <v>46035</v>
       </c>
       <c r="B692" t="n">
-        <v>23480.65</v>
+        <v>36806.21</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.001993407728386409</v>
+        <v>-0.001574966763209895</v>
       </c>
     </row>
     <row r="693">
@@ -8055,10 +8055,10 @@
         <v>46036</v>
       </c>
       <c r="B693" t="n">
-        <v>23475.85</v>
+        <v>36805.06</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.0002044236424461054</v>
+        <v>-3.124472745230644e-05</v>
       </c>
     </row>
     <row r="694">
@@ -8066,10 +8066,10 @@
         <v>46038</v>
       </c>
       <c r="B694" t="n">
-        <v>23485.3</v>
+        <v>36829.93</v>
       </c>
       <c r="C694" t="n">
-        <v>0.000402541335031481</v>
+        <v>0.0006757223055744443</v>
       </c>
     </row>
     <row r="695">
@@ -8077,10 +8077,10 @@
         <v>46041</v>
       </c>
       <c r="B695" t="n">
-        <v>23373.75</v>
+        <v>36650.97</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.004749779649397712</v>
+        <v>-0.004859091505196922</v>
       </c>
     </row>
     <row r="696">
@@ -8088,10 +8088,10 @@
         <v>46042</v>
       </c>
       <c r="B696" t="n">
-        <v>22946.65</v>
+        <v>35984.65</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.01827263490026199</v>
+        <v>-0.01818014639175991</v>
       </c>
     </row>
     <row r="697">
@@ -8099,10 +8099,10 @@
         <v>46043</v>
       </c>
       <c r="B697" t="n">
-        <v>22835.15</v>
+        <v>35815.26</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.004859097079530139</v>
+        <v>-0.004707284911760978</v>
       </c>
     </row>
     <row r="698">
@@ -8110,10 +8110,10 @@
         <v>46044</v>
       </c>
       <c r="B698" t="n">
-        <v>23008.75</v>
+        <v>36088.66</v>
       </c>
       <c r="C698" t="n">
-        <v>0.007602314852321879</v>
+        <v>0.007633617625559586</v>
       </c>
     </row>
     <row r="699">
@@ -8121,10 +8121,373 @@
         <v>46045</v>
       </c>
       <c r="B699" t="n">
-        <v>23021.9</v>
+        <v>35609.9</v>
       </c>
       <c r="C699" t="n">
-        <v>0.0005715217036996734</v>
+        <v>-0.01326621714411125</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B700" t="n">
+        <v>35786.84</v>
+      </c>
+      <c r="C700" t="n">
+        <v>0.004968842934127693</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B701" t="n">
+        <v>36188.16</v>
+      </c>
+      <c r="C701" t="n">
+        <v>0.0112141781727586</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B702" t="n">
+        <v>36266.59</v>
+      </c>
+      <c r="C702" t="n">
+        <v>0.002167283442982226</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B703" t="n">
+        <v>36185.03</v>
+      </c>
+      <c r="C703" t="n">
+        <v>-0.0022489018129358</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B704" t="n">
+        <v>35462.81</v>
+      </c>
+      <c r="C704" t="n">
+        <v>-0.01995908252666923</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B705" t="n">
+        <v>35814.09</v>
+      </c>
+      <c r="C705" t="n">
+        <v>0.009905588417838285</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B706" t="n">
+        <v>36755.96</v>
+      </c>
+      <c r="C706" t="n">
+        <v>0.02629886728938247</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B707" t="n">
+        <v>36890.21</v>
+      </c>
+      <c r="C707" t="n">
+        <v>0.003652468878516668</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B708" t="n">
+        <v>36695.11</v>
+      </c>
+      <c r="C708" t="n">
+        <v>-0.005288666017352561</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B709" t="n">
+        <v>36730.2</v>
+      </c>
+      <c r="C709" t="n">
+        <v>0.0009562582044309043</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B710" t="n">
+        <v>37113.23</v>
+      </c>
+      <c r="C710" t="n">
+        <v>0.01042820349467211</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B711" t="n">
+        <v>37207.34</v>
+      </c>
+      <c r="C711" t="n">
+        <v>0.00253575342270107</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B712" t="n">
+        <v>37256.72</v>
+      </c>
+      <c r="C712" t="n">
+        <v>0.001327157490968345</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B713" t="n">
+        <v>37049.4</v>
+      </c>
+      <c r="C713" t="n">
+        <v>-0.005564633709032929</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B714" t="n">
+        <v>36532.48</v>
+      </c>
+      <c r="C714" t="n">
+        <v>-0.01395218276139421</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B715" t="n">
+        <v>36787.89</v>
+      </c>
+      <c r="C715" t="n">
+        <v>0.006991312935776595</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B716" t="n">
+        <v>36904.38</v>
+      </c>
+      <c r="C716" t="n">
+        <v>0.003166531160118113</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B717" t="n">
+        <v>37062.35</v>
+      </c>
+      <c r="C717" t="n">
+        <v>0.004280521715850583</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B718" t="n">
+        <v>36523.88</v>
+      </c>
+      <c r="C718" t="n">
+        <v>-0.01452876031876016</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B719" t="n">
+        <v>36674.32</v>
+      </c>
+      <c r="C719" t="n">
+        <v>0.004118949027321461</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B720" t="n">
+        <v>36817.86</v>
+      </c>
+      <c r="C720" t="n">
+        <v>0.003913910332897785</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B721" t="n">
+        <v>36530.09</v>
+      </c>
+      <c r="C721" t="n">
+        <v>-0.007816043626653002</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B722" t="n">
+        <v>36679.75</v>
+      </c>
+      <c r="C722" t="n">
+        <v>0.004096896558426266</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B723" t="n">
+        <v>36748.49</v>
+      </c>
+      <c r="C723" t="n">
+        <v>0.001874058574554027</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B724" t="n">
+        <v>36322.56</v>
+      </c>
+      <c r="C724" t="n">
+        <v>-0.01159040820452761</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B725" t="n">
+        <v>35812.02</v>
+      </c>
+      <c r="C725" t="n">
+        <v>-0.01405572734961413</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B726" t="n">
+        <v>35125.64</v>
+      </c>
+      <c r="C726" t="n">
+        <v>-0.01916619056953495</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B727" t="n">
+        <v>35579.03</v>
+      </c>
+      <c r="C727" t="n">
+        <v>0.01290766516994424</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B728" t="n">
+        <v>35232.05</v>
+      </c>
+      <c r="C728" t="n">
+        <v>-0.00975237379996019</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B729" t="n">
+        <v>34557.39</v>
+      </c>
+      <c r="C729" t="n">
+        <v>-0.01914904185251787</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B730" t="n">
+        <v>35005.2</v>
+      </c>
+      <c r="C730" t="n">
+        <v>0.01295844391026058</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B731" t="n">
+        <v>34529.78</v>
+      </c>
+      <c r="C731" t="n">
+        <v>-0.01358141076182962</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B732" t="n">
+        <v>34252.84</v>
+      </c>
+      <c r="C732" t="n">
+        <v>-0.008020323326705325</v>
       </c>
     </row>
   </sheetData>
